--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>101.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-687.4%</t>
+          <t>-688.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.2%</t>
+          <t>-173.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-300.4%</t>
+          <t>-301.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.2%</t>
+          <t>-182.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
     </row>
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.674059067795874</v>
+        <v>2.602956060044375</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.320325955756101</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9455722611796862</v>
+        <v>0.8744692534281873</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.822596138290807</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.602036536784485</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.337135253906603</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9379290186595957</v>
+        <v>0.8668260109080967</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.811591036140616</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.668372090581306</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.274837255130481</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.029183771966866</v>
+        <v>0.9580807642153666</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.905103148502102</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.470664092295433</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.073047057465323</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9121918527470556</v>
+        <v>0.8410888449955567</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.826206065517721</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.540954324617609</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.123933770151518</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9621273999947531</v>
+        <v>0.8910243922432541</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.86596427022818</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.555582060733652</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.037323027501711</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.011399433170719</v>
+        <v>0.9402964254192205</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.927767445067319</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.554118041558324</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.097532325506996</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9858516947932772</v>
+        <v>0.9147486870417783</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.89017784708882</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.552609659598252</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.021110279075069</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.014912131405976</v>
+        <v>0.9438091236544774</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.888669465128748</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.552472527033689</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.9767371474365</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.03252425149684</v>
+        <v>0.9614212437453411</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.915156211547326</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.546866321172279</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.999217498295385</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.017925905291877</v>
+        <v>0.9468228975403776</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.909550005685916</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.553248078200084</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.951561767734329</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.043369954544104</v>
+        <v>0.9722669467926046</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>2.944525201050354</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.558140451574809</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.851043609235575</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.08846959131833</v>
+        <v>1.017366583566831</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.009728469524332</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.544895124050681</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.835138279803222</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.081586395567144</v>
+        <v>1.010483387815645</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>2.949015545574661</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.548992826661309</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.790299878194824</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.103619458821131</v>
+        <v>1.032516451069633</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>2.955839307952211</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.553153766292387</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.809798334436832</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.099981015955406</v>
+        <v>1.028878008203907</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.931149462815346</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.559033368820224</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.765595497350932</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.123541753317603</v>
+        <v>1.052438745566104</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>2.963550767594723</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.557443369289472</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.773155163187979</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.118927887452032</v>
+        <v>1.047824879700533</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>2.994842810469863</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.608691134472512</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.614863745648706</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.233492219650781</v>
+        <v>1.162389211899282</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.046090575652903</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.607131839066765</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.40722174201423</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.314989725698824</v>
+        <v>1.243886717947325</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.169116482427841</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.602080067305035</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.356189649291702</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.330350791026106</v>
+        <v>1.259247783274607</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.194683966299628</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.61926747139774</v>
       </c>
       <c r="D1988" t="n">
         <v>-3.290965468164496</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.373627867569693</v>
+        <v>1.302524859818194</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.251005879068656</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.61522844369702</v>
       </c>
       <c r="D1989" t="n">
         <v>-3.253538448093363</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.384559647897427</v>
+        <v>1.313456640145928</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.250117774185445</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.61648523602826</v>
       </c>
       <c r="D1990" t="n">
         <v>-3.273650104128071</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.377771777814784</v>
+        <v>1.306668770063285</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.257990973515137</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.777043007049471</v>
       </c>
       <c r="D1991" t="n">
         <v>-3.245236841028187</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.549694854075948</v>
+        <v>1.478591846324449</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.383163406888491</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>2.897155916267288</v>
       </c>
       <c r="D1992" t="n">
         <v>-3.170454580003175</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.69972066770377</v>
+        <v>1.628617659952271</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.548145672721316</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>2.888863892281147</v>
       </c>
       <c r="D1993" t="n">
         <v>-3.144370495739367</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.701862277423152</v>
+        <v>1.630759269671653</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.539853648735175</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>2.887057087864927</v>
       </c>
       <c r="D1994" t="n">
         <v>-3.056492582630246</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.73520663825058</v>
+        <v>1.664103630499081</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.607602229772965</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>2.904611493591718</v>
       </c>
       <c r="D1995" t="n">
         <v>-3.047600121236963</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.756318028534685</v>
+        <v>1.685215020783186</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.625156635499756</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>2.896466540996302</v>
       </c>
       <c r="D1996" t="n">
         <v>-3.216076238206841</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.680782629151317</v>
+        <v>1.609679621399819</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.600242981474392</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>2.877736238184164</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.769820045577401</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.840554803390955</v>
+        <v>1.769451795639456</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.524681476860474</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>2.868400260681069</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.747098941894248</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.840307267361121</v>
+        <v>1.769204259609622</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.515345499357379</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>3.027306386532238</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.876300755188291</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.947532667894673</v>
+        <v>1.876429660143174</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.596730537232122</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>3.064384209025884</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.902175153662316</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.974260730998709</v>
+        <v>1.90315772324721</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.660755324952813</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>3.061059565015429</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.895120463447143</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.973757963074324</v>
+        <v>1.902654955322825</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.661663495071463</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>3.071065718660171</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.868169239120655</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.994544606449661</v>
+        <v>1.923441598698162</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.680597856332836</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.255168850805131</v>
       </c>
       <c r="D2003" t="n">
         <v>-3.004122247176971</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.124266535372094</v>
+        <v>2.053163527620595</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.864700988477796</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.247285545708124</v>
       </c>
       <c r="D2004" t="n">
         <v>-3.026530364981843</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.107419983153138</v>
+        <v>2.036316975401639</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.856817683380789</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.249339545257761</v>
       </c>
       <c r="D2005" t="n">
         <v>-3.054754600559443</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.098184288471735</v>
+        <v>2.027081280720236</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.869657734401211</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.305593262979608</v>
       </c>
       <c r="D2006" t="n">
         <v>-3.064195526447973</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.15066163583817</v>
+        <v>2.079558628086672</v>
       </c>
       <c r="F2006" t="n">
         <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>3.999367722649094</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.308484357524909</v>
       </c>
       <c r="D2007" t="n">
         <v>-3.116469133783615</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.132643287449215</v>
+        <v>2.061540279697716</v>
       </c>
       <c r="F2007" t="n">
         <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>3.970894652793009</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.306596170418684</v>
       </c>
       <c r="D2008" t="n">
         <v>-3.192799111384521</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.100223109302628</v>
+        <v>2.029120101551129</v>
       </c>
       <c r="F2008" t="n">
         <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>3.969006465686785</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.301416400021547</v>
       </c>
       <c r="D2009" t="n">
         <v>-3.395052831708874</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.014141850775749</v>
+        <v>1.94303884302425</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9017634384558131</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.913577470846533</v>
+        <v>3.842474463095035</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.299850410231699</v>
       </c>
       <c r="D2010" t="n">
         <v>-3.556621257236129</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.947948490774999</v>
+        <v>1.8768454830235</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7749805146579337</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.835941726777958</v>
+        <v>3.764838719026459</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.312923817097618</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.664921919106249</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.91770163289287</v>
+        <v>1.846598625141371</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7749805146579337</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.849015133643877</v>
+        <v>3.777912125892378</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.304929013880558</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.758069390409615</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.872447841154463</v>
+        <v>1.801344833402964</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6521513033754009</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.767322803657297</v>
+        <v>3.696219795905798</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.30345305500756</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.785970177519088</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.859811567437676</v>
+        <v>1.788708559686177</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6175543792324661</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.745088690298538</v>
+        <v>3.673985682547039</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.300217498984758</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.908496280221982</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.807565570333717</v>
+        <v>1.736462562582218</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4950282765295723</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.668337472654001</v>
+        <v>3.597234464902502</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.366923458575262</v>
       </c>
       <c r="D2015" t="n">
         <v>-4.139010776407571</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.782065731449985</v>
+        <v>1.710962723698486</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2645137803439835</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.596734734533151</v>
+        <v>3.525631726781652</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.507235177577109</v>
       </c>
       <c r="D2016" t="n">
         <v>-4.487755861632015</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.782879416362055</v>
+        <v>1.711776408610556</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.67179768118366</v>
+        <v>3.600694673432161</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.576215446722749</v>
       </c>
       <c r="D2017" t="n">
         <v>-4.641742279408155</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.790265118397238</v>
+        <v>1.71916211064574</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.7407779503293</v>
+        <v>3.669674942577801</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.56226664884287</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.591220375580489</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.796525082048426</v>
+        <v>1.725422074296927</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.726829152449421</v>
+        <v>3.655726144697922</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.574137137898284</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.843695529588214</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.70740550950075</v>
+        <v>1.636302501749251</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.738699641504835</v>
+        <v>3.667596633753336</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.575347672417228</v>
       </c>
       <c r="D2020" t="n">
         <v>-5.136591286067626</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.591457741427929</v>
+        <v>1.52035473367643</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.739910176023778</v>
+        <v>3.668807168272279</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.579469414644549</v>
       </c>
       <c r="D2021" t="n">
         <v>-5.323255414202434</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.520913832401327</v>
+        <v>1.449810824649828</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1290268556005258</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.727988535756364</v>
+        <v>3.656885528004865</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.574547267380738</v>
       </c>
       <c r="D2022" t="n">
         <v>-5.469276101116396</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.457583410371932</v>
+        <v>1.386480402620433</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1199437638066689</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.717616533416239</v>
+        <v>3.64651352566474</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.736751324079782</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.560990110225982</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.583101863427141</v>
+        <v>1.511998855675643</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1199437638066689</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.879820590115283</v>
+        <v>3.808717582363784</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.731597962043597</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.592641769285951</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.565287837766968</v>
+        <v>1.494184830015469</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1147753065622287</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.871566153732433</v>
+        <v>3.800463145980934</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.741827379612088</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.674576587554834</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.542743328027906</v>
+        <v>1.471640320276407</v>
       </c>
       <c r="F2025" t="n">
         <v>0.1048405609751485</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.875834723948676</v>
+        <v>3.804731716197177</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.75075301806799</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.776552709803242</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.510878517584445</v>
+        <v>1.439775509832946</v>
       </c>
       <c r="F2026" t="n">
         <v>0.002864438726740914</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.823574689055534</v>
+        <v>3.752471681304035</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.742905905312166</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.66654642632602</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.547033918219509</v>
+        <v>1.47593091046801</v>
       </c>
       <c r="F2027" t="n">
         <v>0.02606901064401612</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.829650319450074</v>
+        <v>3.758547311698575</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.74715591603414</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.523486850585094</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.608507759237854</v>
+        <v>1.537404751486355</v>
       </c>
       <c r="F2028" t="n">
         <v>0.0340824372339954</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.838708386126036</v>
+        <v>3.767605378374538</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.754416798916676</v>
       </c>
       <c r="D2029" t="n">
         <v>-5.222040125113256</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.736347332309125</v>
+        <v>1.665244324557626</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3355291627058327</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.026837304291675</v>
+        <v>3.955734296540176</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.755387976669387</v>
       </c>
       <c r="D2030" t="n">
         <v>-5.24663036934844</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.727482412367762</v>
+        <v>1.656379404616263</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3355291627058327</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.027808482044385</v>
+        <v>3.956705474292886</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.756230881049142</v>
       </c>
       <c r="D2031" t="n">
         <v>-5.19559199334192</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.748740667150126</v>
+        <v>1.677637659398627</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3355291627058327</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.028651386424141</v>
+        <v>3.957548378672642</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.775268979923287</v>
       </c>
       <c r="D2032" t="n">
         <v>-5.154452698475289</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.784234483970923</v>
+        <v>1.713131476219425</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3766684575724635</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.072373062218265</v>
+        <v>4.001270054466766</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.591452976047222</v>
       </c>
       <c r="D2033" t="n">
         <v>-5.057817786456649</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.639072444902314</v>
+        <v>1.567969437150815</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4733033695911034</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.946538005553383</v>
+        <v>3.875434997801884</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.594955020121186</v>
       </c>
       <c r="D2034" t="n">
         <v>-5.188398520987492</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.590342195163941</v>
+        <v>1.519239187412442</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3427226350602609</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.871691608908842</v>
+        <v>3.800588601157343</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.579381839197269</v>
       </c>
       <c r="D2035" t="n">
         <v>-5.02390218679653</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.640567547916409</v>
+        <v>1.56946454016491</v>
       </c>
       <c r="F2035" t="n">
         <v>0.5072189692512228</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.954816228499501</v>
+        <v>3.883713220748003</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.578569549633698</v>
       </c>
       <c r="D2036" t="n">
         <v>-5.051272119480962</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.628807285279065</v>
+        <v>1.557704277527566</v>
       </c>
       <c r="F2036" t="n">
         <v>0.5072189692512228</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.954003938935931</v>
+        <v>3.882900931184432</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.588438328758771</v>
       </c>
       <c r="D2037" t="n">
         <v>-5.061657314370851</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.634521986448182</v>
+        <v>1.563418978696683</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4968337743613335</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.957641601127071</v>
+        <v>3.886538593375571</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.659275334535196</v>
       </c>
       <c r="D2038" t="n">
         <v>-5.080245473093076</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.697923728735717</v>
+        <v>1.626820720984218</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4782456156391081</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01732571167016</v>
+        <v>3.946222703918661</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.656144345353495</v>
       </c>
       <c r="D2039" t="n">
         <v>-5.080544019789112</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.694673320875601</v>
+        <v>1.623570313124102</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4779470689430722</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.014015594470837</v>
+        <v>3.942912586719338</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.660675240292886</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.979720886098685</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.739533469291164</v>
+        <v>1.668430461539665</v>
       </c>
       <c r="F2040" t="n">
         <v>0.490411284427426</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.026025018700841</v>
+        <v>3.954922010949342</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.660804493771429</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.788939525346278</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.81597526707067</v>
+        <v>1.744872259319171</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6811926451798334</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.140623088630829</v>
+        <v>4.06952008087933</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.640641339509026</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.770422671304457</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.803218854424995</v>
+        <v>1.732115846673496</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6941227746050416</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.12821801202355</v>
+        <v>4.057115004272051</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.675608276121084</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.715092083402695</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.860318026197758</v>
+        <v>1.789215018446259</v>
       </c>
       <c r="F2043" t="n">
         <v>0.7494533625068037</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.196383301376666</v>
+        <v>4.125280293625167</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.669294844022522</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.703037956489732</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.858826244864381</v>
+        <v>1.787723237112882</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7615074894197665</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.197302345425881</v>
+        <v>4.126199337674382</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.671175474206658</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.744193076057953</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.844244827221228</v>
+        <v>1.773141819469729</v>
       </c>
       <c r="F2045" t="n">
         <v>0.7203523698515456</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.174489903869084</v>
+        <v>4.103386896117585</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.68402650008454</v>
       </c>
       <c r="D2046" t="n">
         <v>-4.64131248652936</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.898248088910548</v>
+        <v>1.827145081159049</v>
       </c>
       <c r="F2046" t="n">
         <v>0.8232329593801385</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.249069283464123</v>
+        <v>4.177966275712624</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.704229170258134</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.872912879698861</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.825810601816342</v>
+        <v>1.754707594064843</v>
       </c>
       <c r="F2047" t="n">
         <v>0.8232329593801385</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.269271953637717</v>
+        <v>4.198168945886218</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.775332178009633</v>
+        <v>3.704229170258134</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.890985387990472</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.818581598499697</v>
+        <v>1.747478590748198</v>
       </c>
       <c r="F2048" t="n">
         <v>0.8232329593801385</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.269271953637717</v>
+        <v>4.198168945886218</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.7355840916031</v>
+        <v>3.664481083851601</v>
       </c>
       <c r="D2049" t="n">
         <v>-5.066092220566917</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.708790779062586</v>
+        <v>1.637687771311087</v>
       </c>
       <c r="F2049" t="n">
         <v>0.8232329593801385</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.229523867231183</v>
+        <v>4.158420859479684</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943584</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.74260671060004</v>
+        <v>3.671503702848541</v>
       </c>
       <c r="D2050" t="n">
         <v>-5.034806200026462</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.728327806275708</v>
+        <v>1.657224798524209</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8545189799205939</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.255318098552396</v>
+        <v>4.184215090800897</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.841777710172944</v>
+        <v>3.770674702421446</v>
       </c>
       <c r="D2051" t="n">
         <v>-4.881780807913177</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.888708962693926</v>
+        <v>1.817605954942427</v>
       </c>
       <c r="F2051" t="n">
         <v>1.007544372033878</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.446304333393272</v>
+        <v>4.375201325641773</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.029243935081237</v>
+        <v>3.958140927329738</v>
       </c>
       <c r="D2052" t="n">
         <v>-4.910088121786448</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.06485226205291</v>
+        <v>1.993749254301411</v>
       </c>
       <c r="F2052" t="n">
         <v>1.007544372033878</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.633770558301563</v>
+        <v>4.562667550550064</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.998646886435319</v>
+        <v>3.92754387868382</v>
       </c>
       <c r="D2053" t="n">
         <v>-5.07668134689997</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.967617923361584</v>
+        <v>1.896514915610085</v>
       </c>
       <c r="F2053" t="n">
         <v>0.8409511469203557</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.503217574587532</v>
+        <v>4.432114566836034</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.002323289097037</v>
+        <v>3.931220281345538</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.90361696751767</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.040520077776221</v>
+        <v>1.969417070024722</v>
       </c>
       <c r="F2054" t="n">
         <v>0.8409511469203557</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.50689397724925</v>
+        <v>4.435790969497751</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.999941344220532</v>
+        <v>3.928838336469033</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.874370987061973</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.049836525081995</v>
+        <v>1.978733517330496</v>
       </c>
       <c r="F2055" t="n">
         <v>0.8409511469203557</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.504512032372745</v>
+        <v>4.433409024621247</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.997234583378167</v>
+        <v>3.926131575626668</v>
       </c>
       <c r="D2056" t="n">
         <v>-4.981296534939824</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.00435954508849</v>
+        <v>1.933256537336991</v>
       </c>
       <c r="F2056" t="n">
         <v>0.7340255990425043</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.437649942803669</v>
+        <v>4.36654693505217</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.998663385521401</v>
+        <v>3.927560377769902</v>
       </c>
       <c r="D2057" t="n">
         <v>-5.126315093447073</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.947780923828824</v>
+        <v>1.876677916077325</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5890070405352558</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.352067609842555</v>
+        <v>4.280964602091056</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.098594624779154</v>
+        <v>4.027491617027655</v>
       </c>
       <c r="D2058" t="n">
         <v>-5.244656859231791</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.00037545677269</v>
+        <v>1.929272449021191</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5996930790981458</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.458410472238042</v>
+        <v>4.387307464486543</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.096380321905093</v>
+        <v>4.025277314153594</v>
       </c>
       <c r="D2059" t="n">
         <v>-5.296067281552499</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.977596984970346</v>
+        <v>1.906493977218847</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5996930790981458</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.456196169363981</v>
+        <v>4.385093161612482</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.096283449979382</v>
+        <v>4.025180442227883</v>
       </c>
       <c r="D2060" t="n">
         <v>-5.37548673276025</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.945732332561535</v>
+        <v>1.874629324810036</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5996930790981458</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.45609929743827</v>
+        <v>4.384996289686772</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.096277343537426</v>
+        <v>4.025174335785927</v>
       </c>
       <c r="D2061" t="n">
         <v>-5.470949730677468</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.907541026952691</v>
+        <v>1.836438019201192</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5996930790981458</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.456093190996314</v>
+        <v>4.384990183244815</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.094373740100036</v>
+        <v>4.023270732348537</v>
       </c>
       <c r="D2062" t="n">
         <v>-5.510969728721252</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.889629424297789</v>
+        <v>1.81852641654629</v>
       </c>
       <c r="F2062" t="n">
         <v>0.559673081054362</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.430177588732654</v>
+        <v>4.359074580981155</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.100107557847763</v>
+        <v>4.029004550096264</v>
       </c>
       <c r="D2063" t="n">
         <v>-5.566338890853445</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.873215577192638</v>
+        <v>1.802112569441139</v>
       </c>
       <c r="F2063" t="n">
         <v>0.559673081054362</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.435911406480381</v>
+        <v>4.364808398728882</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.099645921190696</v>
+        <v>4.028542913439196</v>
       </c>
       <c r="D2064" t="n">
         <v>-5.611776670684272</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.85457882860324</v>
+        <v>1.78347582085174</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5168280903762024</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.409742775416418</v>
+        <v>4.338639767664918</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.119520314041015</v>
+        <v>4.048417306289515</v>
       </c>
       <c r="D2065" t="n">
         <v>-5.528551213836608</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.907743404192625</v>
+        <v>1.836640396441125</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5168280903762024</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.429617168266737</v>
+        <v>4.358514160515237</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794507029299175</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.103221014565743</v>
+        <v>4.032118006814243</v>
       </c>
       <c r="D2066" t="n">
         <v>-5.352260989231301</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.961960194559475</v>
+        <v>1.890857186807975</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5168280903762024</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.413317868791465</v>
+        <v>4.342214861039965</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.105651964029788</v>
+        <v>4.034548956278289</v>
       </c>
       <c r="D2067" t="n">
         <v>-5.169049326098206</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.037675809276759</v>
+        <v>1.966572801525259</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5168280903762024</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.41574881825551</v>
+        <v>4.34464581050401</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.071443149877678</v>
+        <v>4.000340142126178</v>
       </c>
       <c r="D2068" t="n">
         <v>-5.097327879084355</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.032155573930189</v>
+        <v>1.961052566178689</v>
       </c>
       <c r="F2068" t="n">
         <v>0.588549537390053</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.424572872311709</v>
+        <v>4.35346986456021</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.018358895798849</v>
+        <v>3.94725588804735</v>
       </c>
       <c r="D2069" t="n">
         <v>-5.226706661724132</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.927319806795449</v>
+        <v>1.85621679904395</v>
       </c>
       <c r="F2069" t="n">
         <v>0.5464477646828496</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.34622755460856</v>
+        <v>4.27512454685706</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.847826539620038</v>
+        <v>3.845735107949446</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.203557100684205</v>
+        <v>4.132454092932705</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.258106350618531</v>
+        <v>-5.269663951597441</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.099958136123045</v>
+        <v>2.024232087979982</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4777262899507192</v>
+        <v>0.4202114645960814</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.490192874654637</v>
+        <v>4.384580971690355</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>101.6%</t>
+          <t>108.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.5%</t>
+          <t>-685.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-173.8%</t>
+          <t>-165.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.5%</t>
+          <t>590.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-301.3%</t>
+          <t>-306.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.0%</t>
+          <t>-169.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.602956060044375</v>
+        <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.320325955756101</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8744692534281873</v>
+        <v>0.9455722611796862</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.822596138290807</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.602036536784485</v>
+        <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.337135253906603</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8668260109080967</v>
+        <v>0.9379290186595957</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.811591036140616</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.668372090581306</v>
+        <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.274837255130481</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9580807642153666</v>
+        <v>1.029183771966866</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.905103148502102</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.470664092295433</v>
+        <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.073047057465323</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8410888449955567</v>
+        <v>0.9121918527470556</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.826206065517721</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.540954324617609</v>
+        <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.123933770151518</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8910243922432541</v>
+        <v>0.9621273999947531</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.86596427022818</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.555582060733652</v>
+        <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.037323027501711</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9402964254192205</v>
+        <v>1.011399433170719</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.927767445067319</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.554118041558324</v>
+        <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.097532325506996</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9147486870417783</v>
+        <v>0.9858516947932772</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.89017784708882</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.552609659598252</v>
+        <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.021110279075069</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9438091236544774</v>
+        <v>1.014912131405976</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.888669465128748</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.552472527033689</v>
+        <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.9767371474365</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9614212437453411</v>
+        <v>1.03252425149684</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.915156211547326</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.546866321172279</v>
+        <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.999217498295385</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9468228975403776</v>
+        <v>1.017925905291877</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.909550005685916</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.553248078200084</v>
+        <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.951561767734329</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9722669467926046</v>
+        <v>1.043369954544104</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.944525201050354</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.558140451574809</v>
+        <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.851043609235575</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.017366583566831</v>
+        <v>1.08846959131833</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.009728469524332</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.544895124050681</v>
+        <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.835138279803222</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.010483387815645</v>
+        <v>1.081586395567144</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.949015545574661</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.548992826661309</v>
+        <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.790299878194824</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.032516451069633</v>
+        <v>1.103619458821131</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.955839307952211</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.553153766292387</v>
+        <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.809798334436832</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.028878008203907</v>
+        <v>1.099981015955406</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.931149462815346</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.559033368820224</v>
+        <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.765595497350932</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.052438745566104</v>
+        <v>1.123541753317603</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.963550767594723</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.557443369289472</v>
+        <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.773155163187979</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.047824879700533</v>
+        <v>1.118927887452032</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.994842810469863</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.608691134472512</v>
+        <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.614863745648706</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.162389211899282</v>
+        <v>1.233492219650781</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.046090575652903</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.607131839066765</v>
+        <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.40722174201423</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.243886717947325</v>
+        <v>1.314989725698824</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.169116482427841</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.602080067305035</v>
+        <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.356189649291702</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.259247783274607</v>
+        <v>1.330350791026106</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.194683966299628</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.61926747139774</v>
+        <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
         <v>-3.290965468164496</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.302524859818194</v>
+        <v>1.373627867569693</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.251005879068656</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.61522844369702</v>
+        <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
         <v>-3.253538448093363</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.313456640145928</v>
+        <v>1.384559647897427</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.250117774185445</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.61648523602826</v>
+        <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.273650104128071</v>
+        <v>-3.250083485184799</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.306668770063285</v>
+        <v>1.387198425392092</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.133182609741145</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.257990973515137</v>
+        <v>3.367497809624446</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.777043007049471</v>
+        <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.245236841028187</v>
+        <v>-3.221670222084915</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.478591846324449</v>
+        <v>1.559121501653257</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>1.074207046994716</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.383163406888491</v>
+        <v>3.4926702429978</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.897155916267288</v>
+        <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.170454580003175</v>
+        <v>-3.146887961059903</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.628617659952271</v>
+        <v>1.709147315281079</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.148989308019729</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.548145672721316</v>
+        <v>3.657652508830625</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.888863892281147</v>
+        <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.144370495739367</v>
+        <v>-3.120803876796095</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.630759269671653</v>
+        <v>1.711288925000461</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.148989308019729</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.539853648735175</v>
+        <v>3.649360484844484</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.887057087864927</v>
+        <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.056492582630246</v>
+        <v>-3.032925963686974</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.664103630499081</v>
+        <v>1.744633285827889</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.26491495044308</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.607602229772965</v>
+        <v>3.717109065882274</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.904611493591718</v>
+        <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.047600121236963</v>
+        <v>-3.024033502293691</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.685215020783186</v>
+        <v>1.765744676111993</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.26491495044308</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.625156635499756</v>
+        <v>3.734663471609065</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.896466540996302</v>
+        <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.216076238206841</v>
+        <v>-3.192509619263569</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.609679621399819</v>
+        <v>1.690209276728626</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.236967114726499</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.600242981474392</v>
+        <v>3.709749817583701</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.877736238184164</v>
+        <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.769820045577401</v>
+        <v>-2.746253426634129</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.769451795639456</v>
+        <v>1.849981450968264</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.142248445056866</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.524681476860474</v>
+        <v>3.634188312969783</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.868400260681069</v>
+        <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.747098941894248</v>
+        <v>-2.723532322950977</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.769204259609622</v>
+        <v>1.84973391493843</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.142248445056866</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.515345499357379</v>
+        <v>3.624852335466688</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.027306386532238</v>
+        <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.876300755188291</v>
+        <v>-2.852734136245019</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.876429660143174</v>
+        <v>1.956959315471981</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>1.013046631762824</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.596730537232122</v>
+        <v>3.706237373341431</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.064384209025884</v>
+        <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.902175153662316</v>
+        <v>-2.878608534719045</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.90315772324721</v>
+        <v>1.983687378576018</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>1.057958240474565</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.660755324952813</v>
+        <v>3.770262161062123</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.061059565015429</v>
+        <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.895120463447143</v>
+        <v>-2.871553844503871</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.902654955322825</v>
+        <v>1.983184610651632</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>1.065012930689739</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.661663495071463</v>
+        <v>3.771170331180772</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.071065718660171</v>
+        <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.868169239120655</v>
+        <v>-2.844602620177383</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.923441598698162</v>
+        <v>2.003971254026969</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.079893276717458</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.680597856332836</v>
+        <v>3.790104692442145</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.255168850805131</v>
+        <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.004122247176971</v>
+        <v>-2.9805556282337</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.053163527620595</v>
+        <v>2.133693182949402</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.079893276717458</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.864700988477796</v>
+        <v>3.974207824587105</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.247285545708124</v>
+        <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.026530364981843</v>
+        <v>-3.002963746038572</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.036316975401639</v>
+        <v>2.116846630730447</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.079893276717458</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.856817683380789</v>
+        <v>3.966324519490098</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.249339545257761</v>
+        <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.054754600559443</v>
+        <v>-3.031187981616172</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.027081280720236</v>
+        <v>2.107610936049044</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.097870029168767</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.869657734401211</v>
+        <v>3.979164570510521</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.305593262979608</v>
+        <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.064195526447973</v>
+        <v>-3.040628907504702</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.079558628086672</v>
+        <v>2.160088283415479</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.220297146712158</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.999367722649094</v>
+        <v>4.108874558758402</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.308484357524909</v>
+        <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.116469133783615</v>
+        <v>-3.092902514840343</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.061540279697716</v>
+        <v>2.142069935026524</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.168023539376517</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.970894652793009</v>
+        <v>4.080401488902319</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.306596170418684</v>
+        <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.192799111384521</v>
+        <v>-3.169232492441249</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.029120101551129</v>
+        <v>2.109649756879937</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.168023539376517</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.969006465686785</v>
+        <v>4.078513301796094</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.301416400021547</v>
+        <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.395052831708874</v>
+        <v>-3.371486212765602</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.94303884302425</v>
+        <v>2.023568498353058</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9017634384558131</v>
+        <v>0.9657698190521635</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.842474463095035</v>
+        <v>3.951981299204344</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.299850410231699</v>
+        <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.556621257236129</v>
+        <v>-3.533054638292858</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.8768454830235</v>
+        <v>1.957375138352308</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7749805146579337</v>
+        <v>0.8389868952542842</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.764838719026459</v>
+        <v>3.874345555135768</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.312923817097618</v>
+        <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.664921919106249</v>
+        <v>-3.641355300162977</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.846598625141371</v>
+        <v>1.927128280470178</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7749805146579337</v>
+        <v>0.8389868952542842</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.777912125892378</v>
+        <v>3.887418962001687</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.304929013880558</v>
+        <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.758069390409615</v>
+        <v>-3.734502771466344</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.801344833402964</v>
+        <v>1.881874488731772</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6521513033754009</v>
+        <v>0.7161576839717514</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.696219795905798</v>
+        <v>3.805726632015108</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.30345305500756</v>
+        <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.785970177519088</v>
+        <v>-3.762403558575817</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.788708559686177</v>
+        <v>1.869238215014985</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6175543792324661</v>
+        <v>0.6815607598288166</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.673985682547039</v>
+        <v>3.783492518656349</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.300217498984758</v>
+        <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.908496280221982</v>
+        <v>-3.884929661278711</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.736462562582218</v>
+        <v>1.816992217911026</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4950282765295723</v>
+        <v>0.5590346571259227</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.597234464902502</v>
+        <v>3.706741301011811</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.366923458575262</v>
+        <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.139010776407571</v>
+        <v>-4.115444157464299</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.710962723698486</v>
+        <v>1.791492379027294</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2645137803439835</v>
+        <v>0.328520160940334</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.525631726781652</v>
+        <v>3.635138562890962</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.507235177577109</v>
+        <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.487755861632015</v>
+        <v>-4.464189242688743</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.711776408610556</v>
+        <v>1.792306063939364</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.2197722070214362</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.600694673432161</v>
+        <v>3.71020150954147</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.576215446722749</v>
+        <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.641742279408155</v>
+        <v>-4.618175660464884</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.71916211064574</v>
+        <v>1.799691765974547</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.2197722070214362</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.669674942577801</v>
+        <v>3.77918177868711</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.56226664884287</v>
+        <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.591220375580489</v>
+        <v>-4.567653756637218</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.725422074296927</v>
+        <v>1.805951729625734</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.2197722070214362</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.655726144697922</v>
+        <v>3.765232980807231</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.574137137898284</v>
+        <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.843695529588214</v>
+        <v>-4.820128910644942</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.636302501749251</v>
+        <v>1.716832157078059</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.2197722070214362</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.667596633753336</v>
+        <v>3.777103469862645</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.575347672417228</v>
+        <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.136591286067626</v>
+        <v>-5.113024667124354</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.52035473367643</v>
+        <v>1.600884389005238</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1557658264250857</v>
+        <v>0.2197722070214362</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.668807168272279</v>
+        <v>3.778314004381588</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.579469414644549</v>
+        <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.323255414202434</v>
+        <v>-5.299688795259162</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.449810824649828</v>
+        <v>1.530340479978636</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1290268556005258</v>
+        <v>0.1930332361968763</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.656885528004865</v>
+        <v>3.766392364114174</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.574547267380738</v>
+        <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.469276101116396</v>
+        <v>-5.445709482173124</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.386480402620433</v>
+        <v>1.46701005794924</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1199437638066689</v>
+        <v>0.1839501444030193</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.64651352566474</v>
+        <v>3.756020361774049</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.736751324079782</v>
+        <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.560990110225982</v>
+        <v>-5.537423491282709</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.511998855675643</v>
+        <v>1.59252851100445</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1199437638066689</v>
+        <v>0.1839501444030193</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.808717582363784</v>
+        <v>3.918224418473093</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.731597962043597</v>
+        <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.592641769285951</v>
+        <v>-5.569075150342679</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.494184830015469</v>
+        <v>1.574714485344277</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1147753065622287</v>
+        <v>0.1787816871585791</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.800463145980934</v>
+        <v>3.909969982090243</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.741827379612088</v>
+        <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.674576587554834</v>
+        <v>-5.651009968611562</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.471640320276407</v>
+        <v>1.552169975605215</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1048405609751485</v>
+        <v>0.1688469415714989</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.804731716197177</v>
+        <v>3.914238552306486</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.75075301806799</v>
+        <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.776552709803242</v>
+        <v>-5.752986090859969</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.439775509832946</v>
+        <v>1.520305165161754</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.002864438726740914</v>
+        <v>0.06687081932309136</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.752471681304035</v>
+        <v>3.861978517413344</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.742905905312166</v>
+        <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.66654642632602</v>
+        <v>-5.642979807382748</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.47593091046801</v>
+        <v>1.556460565796818</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.02606901064401612</v>
+        <v>0.09007539124036656</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.758547311698575</v>
+        <v>3.868054147807885</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.74715591603414</v>
+        <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.523486850585094</v>
+        <v>-5.499920231641822</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.537404751486355</v>
+        <v>1.617934406815163</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.0340824372339954</v>
+        <v>0.09808881783034584</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.767605378374538</v>
+        <v>3.877112214483847</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.754416798916676</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.222040125113256</v>
+        <v>-5.198473506169984</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.665244324557626</v>
+        <v>1.745773979886434</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.3995355433021831</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.955734296540176</v>
+        <v>4.065241132649485</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.755387976669387</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.24663036934844</v>
+        <v>-5.223063750405168</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.656379404616263</v>
+        <v>1.736909059945071</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.3995355433021831</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.956705474292886</v>
+        <v>4.066212310402196</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.756230881049142</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.19559199334192</v>
+        <v>-5.172025374398648</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.677637659398627</v>
+        <v>1.758167314727435</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.3995355433021831</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.957548378672642</v>
+        <v>4.067055214781951</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.775268979923287</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.154452698475289</v>
+        <v>-5.130886079532017</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.713131476219425</v>
+        <v>1.793661131548232</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3766684575724635</v>
+        <v>0.4406748381688139</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.001270054466766</v>
+        <v>4.110776890576075</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.591452976047222</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.057817786456649</v>
+        <v>-5.034251167513377</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.567969437150815</v>
+        <v>1.648499092479623</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4733033695911034</v>
+        <v>0.5373097501874539</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.875434997801884</v>
+        <v>3.984941833911193</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.594955020121186</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.188398520987492</v>
+        <v>-5.164831902044219</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.519239187412442</v>
+        <v>1.59976884274125</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3427226350602609</v>
+        <v>0.4067290156566113</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.800588601157343</v>
+        <v>3.910095437266652</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.579381839197269</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.02390218679653</v>
+        <v>-5.000335567853258</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.56946454016491</v>
+        <v>1.649994195493717</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5072189692512228</v>
+        <v>0.5712253498475732</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.883713220748003</v>
+        <v>3.993220056857312</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.578569549633698</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.051272119480962</v>
+        <v>-5.02770550053769</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.557704277527566</v>
+        <v>1.638233932856374</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5072189692512228</v>
+        <v>0.5712253498475732</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.882900931184432</v>
+        <v>3.992407767293741</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.588438328758771</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.061657314370851</v>
+        <v>-5.038090695427579</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.563418978696683</v>
+        <v>1.643948634025491</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4968337743613335</v>
+        <v>0.5608401549576839</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.886538593375571</v>
+        <v>3.99604542948488</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.659275334535196</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.080245473093076</v>
+        <v>-5.056678854149804</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.626820720984218</v>
+        <v>1.707350376313026</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4782456156391081</v>
+        <v>0.5422519962354586</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.946222703918661</v>
+        <v>4.05572954002797</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.656144345353495</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.080544019789112</v>
+        <v>-5.05697740084584</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.623570313124102</v>
+        <v>1.70409996845291</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4779470689430722</v>
+        <v>0.5419534495394227</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.942912586719338</v>
+        <v>4.052419422828647</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.660675240292886</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.979720886098685</v>
+        <v>-4.956154267155412</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.668430461539665</v>
+        <v>1.748960116868473</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.490411284427426</v>
+        <v>0.5544176650237765</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.954922010949342</v>
+        <v>4.064428847058651</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.660804493771429</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.788939525346278</v>
+        <v>-4.765372906403005</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.744872259319171</v>
+        <v>1.825401914647979</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6811926451798334</v>
+        <v>0.7451990257761839</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.06952008087933</v>
+        <v>4.179026916988639</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.640641339509026</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.770422671304457</v>
+        <v>-4.746856052361185</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.732115846673496</v>
+        <v>1.812645502002304</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6941227746050416</v>
+        <v>0.7581291552013921</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.057115004272051</v>
+        <v>4.16662184038136</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.675608276121084</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.715092083402695</v>
+        <v>-4.691525464459422</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.789215018446259</v>
+        <v>1.869744673775067</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7494533625068037</v>
+        <v>0.8134597431031543</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.125280293625167</v>
+        <v>4.234787129734476</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.669294844022522</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.703037956489732</v>
+        <v>-4.67947133754646</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.787723237112882</v>
+        <v>1.86825289244169</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7615074894197665</v>
+        <v>0.8255138700161171</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.126199337674382</v>
+        <v>4.235706173783691</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.671175474206658</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.744193076057953</v>
+        <v>-4.720626457114681</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.773141819469729</v>
+        <v>1.853671474798537</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7203523698515456</v>
+        <v>0.7843587504478962</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.103386896117585</v>
+        <v>4.212893732226894</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.68402650008454</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.64131248652936</v>
+        <v>-4.617745867586088</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.827145081159049</v>
+        <v>1.907674736487857</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.8872393399764891</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.177966275712624</v>
+        <v>4.287473111821932</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.704229170258134</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.872912879698861</v>
+        <v>-4.849346260755588</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.754707594064843</v>
+        <v>1.835237249393651</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.8872393399764891</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.198168945886218</v>
+        <v>4.307675781995527</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.704229170258134</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.890985387990472</v>
+        <v>-4.8674187690472</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.747478590748198</v>
+        <v>1.828008246077006</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.8872393399764891</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.198168945886218</v>
+        <v>4.307675781995527</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.664481083851601</v>
+        <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.066092220566917</v>
+        <v>-5.042525601623645</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.637687771311087</v>
+        <v>1.718217426639895</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8232329593801385</v>
+        <v>0.8872393399764891</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.158420859479684</v>
+        <v>4.267927695588994</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943584</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.671503702848541</v>
+        <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.034806200026462</v>
+        <v>-5.011239581083189</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.657224798524209</v>
+        <v>1.737754453853017</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8545189799205939</v>
+        <v>0.9185253605169444</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.184215090800897</v>
+        <v>4.293721926910207</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.770674702421446</v>
+        <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.881780807913177</v>
+        <v>-4.858214188969905</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.817605954942427</v>
+        <v>1.898135610271235</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.007544372033878</v>
+        <v>1.071550752630229</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.375201325641773</v>
+        <v>4.484708161751082</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.958140927329738</v>
+        <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.910088121786448</v>
+        <v>-4.886521502843175</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.993749254301411</v>
+        <v>2.074278909630219</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.007544372033878</v>
+        <v>1.071550752630229</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.562667550550064</v>
+        <v>4.672174386659374</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.92754387868382</v>
+        <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.07668134689997</v>
+        <v>-5.053114727956697</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.896514915610085</v>
+        <v>1.977044570938892</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.9049575275167061</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.432114566836034</v>
+        <v>4.541621402945343</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.931220281345538</v>
+        <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.90361696751767</v>
+        <v>-4.880050348574398</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.969417070024722</v>
+        <v>2.04994672535353</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.9049575275167061</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.435790969497751</v>
+        <v>4.545297805607061</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.928838336469033</v>
+        <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.874370987061973</v>
+        <v>-4.850804368118701</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.978733517330496</v>
+        <v>2.059263172659304</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8409511469203557</v>
+        <v>0.9049575275167061</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.433409024621247</v>
+        <v>4.542915860730556</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.926131575626668</v>
+        <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.981296534939824</v>
+        <v>-4.957729915996552</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.933256537336991</v>
+        <v>2.013786192665799</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7340255990425043</v>
+        <v>0.7980319796388547</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.36654693505217</v>
+        <v>4.47605377116148</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.927560377769902</v>
+        <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.126315093447073</v>
+        <v>-5.102748474503801</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.876677916077325</v>
+        <v>1.957207571406133</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5890070405352558</v>
+        <v>0.6530134211316062</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.280964602091056</v>
+        <v>4.390471438200365</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.027491617027655</v>
+        <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.244656859231791</v>
+        <v>-5.221090240288518</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.929272449021191</v>
+        <v>2.009802104349999</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.6636994596944963</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.387307464486543</v>
+        <v>4.496814300595852</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.025277314153594</v>
+        <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.296067281552499</v>
+        <v>-5.272500662609226</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.906493977218847</v>
+        <v>1.987023632547655</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.6636994596944963</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.385093161612482</v>
+        <v>4.494599997721791</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.025180442227883</v>
+        <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.37548673276025</v>
+        <v>-5.351920113816978</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.874629324810036</v>
+        <v>1.955158980138844</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.6636994596944963</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.384996289686772</v>
+        <v>4.49450312579608</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.025174335785927</v>
+        <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.470949730677468</v>
+        <v>-5.447383111734196</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.836438019201192</v>
+        <v>1.91696767453</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5996930790981458</v>
+        <v>0.6636994596944963</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.384990183244815</v>
+        <v>4.494497019354124</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.023270732348537</v>
+        <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.510969728721252</v>
+        <v>-5.487403109777979</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.81852641654629</v>
+        <v>1.899056071875097</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.559673081054362</v>
+        <v>0.6236794616507124</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.359074580981155</v>
+        <v>4.468581417090464</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.029004550096264</v>
+        <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.566338890853445</v>
+        <v>-5.542772271910173</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.802112569441139</v>
+        <v>1.882642224769947</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.559673081054362</v>
+        <v>0.6236794616507124</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.364808398728882</v>
+        <v>4.47431523483819</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.028542913439196</v>
+        <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.611776670684272</v>
+        <v>-5.588210051741</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.78347582085174</v>
+        <v>1.864005476180548</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.5808344709725528</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.338639767664918</v>
+        <v>4.448146603774228</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.048417306289515</v>
+        <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.528551213836608</v>
+        <v>-5.504984594893336</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.836640396441125</v>
+        <v>1.917170051769933</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.5808344709725528</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.358514160515237</v>
+        <v>4.468020996624547</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794507029299175</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.032118006814243</v>
+        <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.352260989231301</v>
+        <v>-5.328694370288028</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.890857186807975</v>
+        <v>1.971386842136784</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.5808344709725528</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.342214861039965</v>
+        <v>4.451721697149274</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.034548956278289</v>
+        <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.169049326098206</v>
+        <v>-5.145482707154933</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.966572801525259</v>
+        <v>2.047102456854068</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5168280903762024</v>
+        <v>0.5808344709725528</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.34464581050401</v>
+        <v>4.45415264661332</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.000340142126178</v>
+        <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.097327879084355</v>
+        <v>-5.073761260141082</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.961052566178689</v>
+        <v>2.041582221507498</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.588549537390053</v>
+        <v>0.6525559179864034</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.35346986456021</v>
+        <v>4.46297670066952</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.94725588804735</v>
+        <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.226706661724132</v>
+        <v>-5.20314004278086</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.85621679904395</v>
+        <v>1.936746454372758</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5464477646828496</v>
+        <v>0.6104541452792001</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.27512454685706</v>
+        <v>4.384631382966369</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.845735107949446</v>
+        <v>3.863685598826284</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.132454092932705</v>
+        <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.269663951597441</v>
+        <v>-5.236156338691605</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.024232087979982</v>
+        <v>2.108738140893816</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4202114645960814</v>
+        <v>0.5410167686124485</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.384580971690355</v>
+        <v>4.528167161851674</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>424.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-685.2%</t>
+          <t>-662.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.3%</t>
+          <t>-156.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.7%</t>
+          <t>587.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-306.2%</t>
+          <t>-313.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-169.9%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.041748155587813</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>1.03613232637035</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.5043777192648173</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.955814644478113</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.142945937024986</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.9948571356919822</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.4359689057194981</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.913973278247423</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.136434970410673</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.995061483892024</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.4359689057194981</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.91157323980174</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.117396842703376</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.9992014541831877</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.3777852943883036</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.873187792211268</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.169912644978196</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>1.09748953490745</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.3777852943883036</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.992482193845458</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.183779406312114</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>1.092776159360016</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.3399273776544807</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.970600772791298</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.39040041076919</v>
+        <v>-4.138975234772184</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.016136287974112</v>
+        <v>1.116706358372914</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.3399273776544807</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.976609303188224</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.242657440534187</v>
+        <v>-3.991232264537182</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9731836973453125</v>
+        <v>1.073753767744114</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.5077347348893638</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.975243938806353</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.326478661808886</v>
+        <v>-4.07505348581188</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9424488303669141</v>
+        <v>1.043018900765716</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.5077347348893638</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.978037560337834</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.320325955756101</v>
+        <v>-4.068900779759096</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9455722611796862</v>
+        <v>1.046142331578488</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.5138874409421481</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.982391532361163</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.337135253906603</v>
+        <v>-4.085710077909598</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9379290186595957</v>
+        <v>1.038499089058398</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.4970781427916464</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.971386430210972</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.274837255130481</v>
+        <v>-4.023412079133475</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.029183771966866</v>
+        <v>1.129753842365668</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.5423724070660885</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>3.064898542572458</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.073047057465323</v>
+        <v>-3.821621881468317</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9121918527470556</v>
+        <v>1.012761923145858</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.7403905992352429</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.986001459588078</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.123933770151518</v>
+        <v>-3.872508594154512</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9621273999947531</v>
+        <v>1.062697470393555</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.6895038865490484</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>3.025759664298537</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.037323027501711</v>
+        <v>-3.785897851504705</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.011399433170719</v>
+        <v>1.111969503569522</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.7681296177542066</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>3.087562839137675</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.097532325506996</v>
+        <v>-3.846107149509989</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9858516947932772</v>
+        <v>1.08642176519208</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.7079203197489221</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>3.049973241159176</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.021110279075069</v>
+        <v>-3.769685103078062</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.014912131405976</v>
+        <v>1.115482201804779</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.7079203197489221</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>3.048464859199105</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.9767371474365</v>
+        <v>-3.725311971439494</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.03252425149684</v>
+        <v>1.133094321895643</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.7522934513874907</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>3.074951605617682</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.999217498295385</v>
+        <v>-3.747792322298379</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.017925905291877</v>
+        <v>1.118495975690679</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.7522934513874907</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>3.069345399756273</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.951561767734329</v>
+        <v>-3.700136591737323</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.043369954544104</v>
+        <v>1.143940024942906</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.7999491819485464</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>3.10432059512071</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.851043609235575</v>
+        <v>-3.599618433238568</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.08846959131833</v>
+        <v>1.189039661717133</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.9004673404473009</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.169523863594688</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.835138279803222</v>
+        <v>-3.583713103806216</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.081586395567144</v>
+        <v>1.182156465965946</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.821354679738062</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>3.108810939645017</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.790299878194824</v>
+        <v>-3.538874702197818</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.103619458821131</v>
+        <v>1.204189529219934</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.8258981126829315</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>3.115634702022567</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.809798334436832</v>
+        <v>-3.558373158439826</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.099981015955406</v>
+        <v>1.200551086354209</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.7778134714030271</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>3.090944856885703</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.765595497350932</v>
+        <v>-3.514170321353925</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.123541753317603</v>
+        <v>1.224111823716406</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.8220163084889276</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>3.12334616166508</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.773155163187979</v>
+        <v>-3.521729987190972</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.118927887452032</v>
+        <v>1.219497957850835</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.8768197124987469</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.154638204540219</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.614863745648706</v>
+        <v>-3.3634385696517</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.233492219650781</v>
+        <v>1.334062290049583</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.8768197124987469</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.205885969723259</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.40722174201423</v>
+        <v>-3.155796566017224</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.314989725698824</v>
+        <v>1.415559796097627</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>1.084461716133223</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.328911876498198</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.356189649291702</v>
+        <v>-3.104764473294696</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.330350791026106</v>
+        <v>1.430920861424908</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>1.135493808855751</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.354479360369985</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.290965468164496</v>
+        <v>-3.03954029216749</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.373627867569693</v>
+        <v>1.474197937968496</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>1.200717989982957</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.410801273139013</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.253538448093363</v>
+        <v>-3.002113272096356</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.384559647897427</v>
+        <v>1.485129718296229</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.205969528012139</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.409913168255803</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.250083485184799</v>
+        <v>-3.022224928131064</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.387198425392092</v>
+        <v>1.478341848213586</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.133182609741145</v>
+        <v>1.216996873009558</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.367497809624446</v>
+        <v>3.417786367585494</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.221670222084915</v>
+        <v>-2.993811665031181</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.559121501653257</v>
+        <v>1.65026492447475</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.074207046994716</v>
+        <v>1.158021310263129</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.4926702429978</v>
+        <v>3.542958800958848</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.146887961059903</v>
+        <v>-2.919029404006168</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.709147315281079</v>
+        <v>1.800290738102573</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.148989308019729</v>
+        <v>1.232803571288142</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.657652508830625</v>
+        <v>3.707941066791673</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.120803876796095</v>
+        <v>-2.89294531974236</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.711288925000461</v>
+        <v>1.802432347821955</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.148989308019729</v>
+        <v>1.232803571288142</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.649360484844484</v>
+        <v>3.699649042805532</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.032925963686974</v>
+        <v>-2.80506740663324</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.744633285827889</v>
+        <v>1.835776708649383</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.26491495044308</v>
+        <v>1.348729213711493</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.717109065882274</v>
+        <v>3.767397623843322</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.024033502293691</v>
+        <v>-2.796174945239956</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.765744676111993</v>
+        <v>1.856888098933487</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.26491495044308</v>
+        <v>1.348729213711493</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.734663471609065</v>
+        <v>3.784952029570113</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.192509619263569</v>
+        <v>-2.964651062209834</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.690209276728626</v>
+        <v>1.78135269955012</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.236967114726499</v>
+        <v>1.320781377994912</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.709749817583701</v>
+        <v>3.760038375544748</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.746253426634129</v>
+        <v>-2.518394869580394</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.849981450968264</v>
+        <v>1.941124873789758</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.142248445056866</v>
+        <v>1.226062708325279</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.634188312969783</v>
+        <v>3.684476870930831</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.723532322950977</v>
+        <v>-2.495673765897242</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.84973391493843</v>
+        <v>1.940877337759924</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.142248445056866</v>
+        <v>1.226062708325279</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.624852335466688</v>
+        <v>3.675140893427735</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.852734136245019</v>
+        <v>-2.624875579191284</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.956959315471981</v>
+        <v>2.048102738293475</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.013046631762824</v>
+        <v>1.096860895031237</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.706237373341431</v>
+        <v>3.756525931302479</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.878608534719045</v>
+        <v>-2.65074997766531</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.983687378576018</v>
+        <v>2.074830801397512</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.057958240474565</v>
+        <v>1.141772503742978</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.770262161062123</v>
+        <v>3.82055071902317</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.871553844503871</v>
+        <v>-2.643695287450136</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.983184610651632</v>
+        <v>2.074328033473126</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.065012930689739</v>
+        <v>1.148827193958152</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.771170331180772</v>
+        <v>3.82145888914182</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.844602620177383</v>
+        <v>-2.616744063123648</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.003971254026969</v>
+        <v>2.095114676848463</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.079893276717458</v>
+        <v>1.163707539985871</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.790104692442145</v>
+        <v>3.840393250403193</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.9805556282337</v>
+        <v>-2.752697071179965</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.133693182949402</v>
+        <v>2.224836605770896</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.079893276717458</v>
+        <v>1.163707539985871</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.974207824587105</v>
+        <v>4.024496382548152</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.002963746038572</v>
+        <v>-2.775105188984837</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.116846630730447</v>
+        <v>2.207990053551941</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.079893276717458</v>
+        <v>1.163707539985871</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.966324519490098</v>
+        <v>4.016613077451145</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.031187981616172</v>
+        <v>-2.803329424562437</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.107610936049044</v>
+        <v>2.198754358870538</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.097870029168767</v>
+        <v>1.18168429243718</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.979164570510521</v>
+        <v>4.029453128471568</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.040628907504702</v>
+        <v>-2.812770350450967</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.160088283415479</v>
+        <v>2.251231706236974</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.220297146712158</v>
+        <v>1.304111409980571</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.108874558758402</v>
+        <v>4.15916311671945</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.092902514840343</v>
+        <v>-2.865043957786608</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.142069935026524</v>
+        <v>2.233213357848018</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.168023539376517</v>
+        <v>1.25183780264493</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.080401488902319</v>
+        <v>4.130690046863366</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.169232492441249</v>
+        <v>-2.941373935387514</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.109649756879937</v>
+        <v>2.200793179701431</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.168023539376517</v>
+        <v>1.25183780264493</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.078513301796094</v>
+        <v>4.128801859757141</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.371486212765602</v>
+        <v>-3.143627655711867</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.023568498353058</v>
+        <v>2.114711921174552</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9657698190521635</v>
+        <v>1.049584082320576</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.951981299204344</v>
+        <v>4.002269857165391</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.533054638292858</v>
+        <v>-3.305196081239123</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.957375138352308</v>
+        <v>2.048518561173802</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8389868952542842</v>
+        <v>0.9228011585226968</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.874345555135768</v>
+        <v>3.924634113096817</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.641355300162977</v>
+        <v>-3.413496743109242</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.927128280470178</v>
+        <v>2.018271703291672</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8389868952542842</v>
+        <v>0.9228011585226968</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.887418962001687</v>
+        <v>3.937707519962735</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.734502771466344</v>
+        <v>-3.506644214412609</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.881874488731772</v>
+        <v>1.973017911553266</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7161576839717514</v>
+        <v>0.7999719472401641</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.805726632015108</v>
+        <v>3.856015189976155</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.762403558575817</v>
+        <v>-3.534545001522082</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.869238215014985</v>
+        <v>1.960381637836479</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6815607598288166</v>
+        <v>0.7653750230972293</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.783492518656349</v>
+        <v>3.833781076617396</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.884929661278711</v>
+        <v>-3.657071104224975</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.816992217911026</v>
+        <v>1.90813564073252</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5590346571259227</v>
+        <v>0.6428489203943354</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.706741301011811</v>
+        <v>3.757029858972859</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.115444157464299</v>
+        <v>-3.887585600410564</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.791492379027294</v>
+        <v>1.882635801848788</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.328520160940334</v>
+        <v>0.4123344242087467</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.635138562890962</v>
+        <v>3.685427120852009</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.464189242688743</v>
+        <v>-4.236330685635008</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.792306063939364</v>
+        <v>1.883449486760858</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2197722070214362</v>
+        <v>0.3035864702898489</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.71020150954147</v>
+        <v>3.760490067502518</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.618175660464884</v>
+        <v>-4.390317103411149</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.799691765974547</v>
+        <v>1.890835188796041</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2197722070214362</v>
+        <v>0.3035864702898489</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.77918177868711</v>
+        <v>3.829470336648158</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.567653756637218</v>
+        <v>-4.339795199583483</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.805951729625734</v>
+        <v>1.897095152447228</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2197722070214362</v>
+        <v>0.3035864702898489</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.765232980807231</v>
+        <v>3.815521538768278</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.820128910644942</v>
+        <v>-4.592270353591207</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.716832157078059</v>
+        <v>1.807975579899553</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2197722070214362</v>
+        <v>0.3035864702898489</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.777103469862645</v>
+        <v>3.827392027823692</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.113024667124354</v>
+        <v>-4.885166110070619</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.600884389005238</v>
+        <v>1.692027811826732</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2197722070214362</v>
+        <v>0.3035864702898489</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.778314004381588</v>
+        <v>3.828602562342636</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.299688795259162</v>
+        <v>-5.071830238205427</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.530340479978636</v>
+        <v>1.62148390280013</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1930332361968763</v>
+        <v>0.276847499465289</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.766392364114174</v>
+        <v>3.816680922075221</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.445709482173124</v>
+        <v>-5.217850925119389</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.46701005794924</v>
+        <v>1.558153480770734</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1839501444030193</v>
+        <v>0.267764407671432</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.756020361774049</v>
+        <v>3.806308919735097</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.537423491282709</v>
+        <v>-5.309564934228975</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.59252851100445</v>
+        <v>1.683671933825944</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1839501444030193</v>
+        <v>0.267764407671432</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.918224418473093</v>
+        <v>3.968512976434141</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.569075150342679</v>
+        <v>-5.341216593288944</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.574714485344277</v>
+        <v>1.665857908165771</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1787816871585791</v>
+        <v>0.2625959504269918</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.909969982090243</v>
+        <v>3.960258540051291</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.651009968611562</v>
+        <v>-5.423151411557828</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.552169975605215</v>
+        <v>1.643313398426709</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1688469415714989</v>
+        <v>0.2526612048399116</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.914238552306486</v>
+        <v>3.964527110267534</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.752986090859969</v>
+        <v>-5.525127533806235</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.520305165161754</v>
+        <v>1.611448587983248</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.06687081932309136</v>
+        <v>0.150685082591504</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.861978517413344</v>
+        <v>3.912267075374392</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.642979807382748</v>
+        <v>-5.415121250329014</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.556460565796818</v>
+        <v>1.647603988618312</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09007539124036656</v>
+        <v>0.1738896545087792</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.868054147807885</v>
+        <v>3.918342705768932</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.499920231641822</v>
+        <v>-5.272061674588087</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.617934406815163</v>
+        <v>1.709077829636656</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.09808881783034584</v>
+        <v>0.1819030810987585</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.877112214483847</v>
+        <v>3.927400772444894</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.198473506169984</v>
+        <v>-4.97061494911625</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.745773979886434</v>
+        <v>1.836917402707928</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3995355433021831</v>
+        <v>0.4833498065705958</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.065241132649485</v>
+        <v>4.115529690610533</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.223063750405168</v>
+        <v>-4.995205193351434</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.736909059945071</v>
+        <v>1.828052482766565</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3995355433021831</v>
+        <v>0.4833498065705958</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.066212310402196</v>
+        <v>4.116500868363243</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.172025374398648</v>
+        <v>-4.944166817344914</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.758167314727435</v>
+        <v>1.849310737548928</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3995355433021831</v>
+        <v>0.4833498065705958</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.067055214781951</v>
+        <v>4.117343772742998</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.130886079532017</v>
+        <v>-4.903027522478283</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.793661131548232</v>
+        <v>1.884804554369726</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4406748381688139</v>
+        <v>0.5244891014372266</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.110776890576075</v>
+        <v>4.161065448537123</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.034251167513377</v>
+        <v>-4.806392610459643</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.648499092479623</v>
+        <v>1.739642515301117</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5373097501874539</v>
+        <v>0.6211240134558665</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.984941833911193</v>
+        <v>4.035230391872241</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.164831902044219</v>
+        <v>-4.936973344990485</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.59976884274125</v>
+        <v>1.690912265562744</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4067290156566113</v>
+        <v>0.490543278925024</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.910095437266652</v>
+        <v>3.9603839952277</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.000335567853258</v>
+        <v>-4.772477010799523</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.649994195493717</v>
+        <v>1.741137618315211</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5712253498475732</v>
+        <v>0.6550396131159859</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.993220056857312</v>
+        <v>4.043508614818359</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.02770550053769</v>
+        <v>-4.799846943483955</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.638233932856374</v>
+        <v>1.729377355677868</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5712253498475732</v>
+        <v>0.6550396131159859</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.992407767293741</v>
+        <v>4.04269632525479</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.038090695427579</v>
+        <v>-4.810232138373845</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.643948634025491</v>
+        <v>1.735092056846985</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5608401549576839</v>
+        <v>0.6446544182260966</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.99604542948488</v>
+        <v>4.046333987445928</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.056678854149804</v>
+        <v>-4.82882029709607</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.707350376313026</v>
+        <v>1.79849379913452</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5422519962354586</v>
+        <v>0.6260662595038713</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.05572954002797</v>
+        <v>4.106018097989018</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.05697740084584</v>
+        <v>-4.829118843792106</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.70409996845291</v>
+        <v>1.795243391274404</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5419534495394227</v>
+        <v>0.6257677128078354</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.052419422828647</v>
+        <v>4.102707980789695</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.956154267155412</v>
+        <v>-4.728295710101678</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.748960116868473</v>
+        <v>1.840103539689966</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5544176650237765</v>
+        <v>0.6382319282921892</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.064428847058651</v>
+        <v>4.114717405019698</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.765372906403005</v>
+        <v>-4.537514349349271</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.825401914647979</v>
+        <v>1.916545337469473</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7451990257761839</v>
+        <v>0.8290132890445966</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.179026916988639</v>
+        <v>4.229315474949686</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.746856052361185</v>
+        <v>-4.518997495307451</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.812645502002304</v>
+        <v>1.903788924823797</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7581291552013921</v>
+        <v>0.8419434184698048</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.16662184038136</v>
+        <v>4.216910398342408</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.691525464459422</v>
+        <v>-4.463666907405688</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.869744673775067</v>
+        <v>1.960888096596561</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8134597431031543</v>
+        <v>0.897274006371567</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.234787129734476</v>
+        <v>4.285075687695524</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.67947133754646</v>
+        <v>-4.451612780492725</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.86825289244169</v>
+        <v>1.959396315263183</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8255138700161171</v>
+        <v>0.9093281332845298</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.235706173783691</v>
+        <v>4.285994731744739</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.720626457114681</v>
+        <v>-4.492767900060946</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.853671474798537</v>
+        <v>1.944814897620031</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7843587504478962</v>
+        <v>0.8681730137163088</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.212893732226894</v>
+        <v>4.263182290187943</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.617745867586088</v>
+        <v>-4.389887310532353</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.907674736487857</v>
+        <v>1.998818159309351</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8872393399764891</v>
+        <v>0.9710536032449018</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.287473111821932</v>
+        <v>4.337761669782981</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.849346260755588</v>
+        <v>-4.621487703701854</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.835237249393651</v>
+        <v>1.926380672215144</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8872393399764891</v>
+        <v>0.9710536032449018</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.307675781995527</v>
+        <v>4.357964339956575</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.8674187690472</v>
+        <v>-4.639560211993466</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.828008246077006</v>
+        <v>1.9191516688985</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8872393399764891</v>
+        <v>0.9710536032449018</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.307675781995527</v>
+        <v>4.357964339956575</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.042525601623645</v>
+        <v>-4.81466704456991</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.718217426639895</v>
+        <v>1.809360849461389</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8872393399764891</v>
+        <v>0.9710536032449018</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.267927695588994</v>
+        <v>4.318216253550041</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.011239581083189</v>
+        <v>-4.783381024029455</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.737754453853017</v>
+        <v>1.828897876674511</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9185253605169444</v>
+        <v>1.002339623785357</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.293721926910207</v>
+        <v>4.344010484871255</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.858214188969905</v>
+        <v>-4.630355631916171</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.898135610271235</v>
+        <v>1.989279033092729</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.071550752630229</v>
+        <v>1.155365015898641</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.484708161751082</v>
+        <v>4.534996719712129</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.886521502843175</v>
+        <v>-4.658662945789441</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.074278909630219</v>
+        <v>2.165422332451713</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.071550752630229</v>
+        <v>1.155365015898641</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.672174386659374</v>
+        <v>4.722462944620421</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.053114727956697</v>
+        <v>-4.825256170902963</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.977044570938892</v>
+        <v>2.068187993760386</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9049575275167061</v>
+        <v>0.9887717907851188</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.541621402945343</v>
+        <v>4.59190996090639</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.880050348574398</v>
+        <v>-4.652191791520663</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.04994672535353</v>
+        <v>2.141090148175024</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9049575275167061</v>
+        <v>0.9887717907851188</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.545297805607061</v>
+        <v>4.595586363568108</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.850804368118701</v>
+        <v>-4.622945811064967</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.059263172659304</v>
+        <v>2.150406595480798</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9049575275167061</v>
+        <v>0.9887717907851188</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.542915860730556</v>
+        <v>4.593204418691603</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.957729915996552</v>
+        <v>-4.729871358942818</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.013786192665799</v>
+        <v>2.104929615487293</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7980319796388547</v>
+        <v>0.8818462429072674</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.47605377116148</v>
+        <v>4.526342329122528</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.102748474503801</v>
+        <v>-4.874889917450067</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.957207571406133</v>
+        <v>2.048350994227627</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6530134211316062</v>
+        <v>0.7368276844000189</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.390471438200365</v>
+        <v>4.440759996161413</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.221090240288518</v>
+        <v>-4.993231683234784</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.009802104349999</v>
+        <v>2.100945527171493</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6636994596944963</v>
+        <v>0.747513722962909</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.496814300595852</v>
+        <v>4.5471028585569</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.272500662609226</v>
+        <v>-5.044642105555492</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.987023632547655</v>
+        <v>2.078167055369148</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6636994596944963</v>
+        <v>0.747513722962909</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.494599997721791</v>
+        <v>4.544888555682839</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.351920113816978</v>
+        <v>-5.124061556763244</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.955158980138844</v>
+        <v>2.046302402960337</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6636994596944963</v>
+        <v>0.747513722962909</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.49450312579608</v>
+        <v>4.544791683757128</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.447383111734196</v>
+        <v>-5.219524554680461</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.91696767453</v>
+        <v>2.008111097351494</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6636994596944963</v>
+        <v>0.747513722962909</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.494497019354124</v>
+        <v>4.544785577315172</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.487403109777979</v>
+        <v>-5.259544552724245</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.899056071875097</v>
+        <v>1.990199494696591</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6236794616507124</v>
+        <v>0.7074937249191251</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.468581417090464</v>
+        <v>4.518869975051512</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.542772271910173</v>
+        <v>-5.314913714856439</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.882642224769947</v>
+        <v>1.97378564759144</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6236794616507124</v>
+        <v>0.7074937249191251</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.47431523483819</v>
+        <v>4.524603792799239</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.588210051741</v>
+        <v>-5.360351494687266</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.864005476180548</v>
+        <v>1.955148899002042</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5808344709725528</v>
+        <v>0.6646487342409655</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.448146603774228</v>
+        <v>4.498435161735276</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.504984594893336</v>
+        <v>-5.277126037839602</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.917170051769933</v>
+        <v>2.008313474591427</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5808344709725528</v>
+        <v>0.6646487342409655</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.468020996624547</v>
+        <v>4.518309554585595</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.328694370288028</v>
+        <v>-5.100835813234294</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.971386842136784</v>
+        <v>2.062530264958278</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5808344709725528</v>
+        <v>0.6646487342409655</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.451721697149274</v>
+        <v>4.502010255110322</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.145482707154933</v>
+        <v>-4.917624150101199</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.047102456854068</v>
+        <v>2.138245879675561</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5808344709725528</v>
+        <v>0.6646487342409655</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.45415264661332</v>
+        <v>4.504441204574368</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.073761260141082</v>
+        <v>-4.845902703087348</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.041582221507498</v>
+        <v>2.132725644328991</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6525559179864034</v>
+        <v>0.7363701812548161</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.46297670066952</v>
+        <v>4.513265258630567</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.20314004278086</v>
+        <v>-4.975281485727126</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.936746454372758</v>
+        <v>2.027889877194252</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6104541452792001</v>
+        <v>0.6942684085476127</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.384631382966369</v>
+        <v>4.434919940927418</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.863685598826284</v>
+        <v>3.932585619135191</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.236156338691605</v>
+        <v>-5.008297781637871</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.108738140893816</v>
+        <v>2.19988156371531</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5410167686124485</v>
+        <v>0.6248310318808612</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.528167161851674</v>
+        <v>4.578455719812722</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>58.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>127.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>124.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>424.3%</t>
+          <t>423.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.4%</t>
+          <t>-686.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.2%</t>
+          <t>-165.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>587.9%</t>
+          <t>590.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-313.9%</t>
+          <t>-305.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-170.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2070"/>
+  <dimension ref="A1:G2071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.041748155587813</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.03613232637035</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5043777192648173</v>
+        <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.955814644478113</v>
+        <v>2.867122258159255</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.142945937024986</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9948571356919822</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4359689057194981</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.913973278247423</v>
+        <v>2.825280891928565</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.136434970410673</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.995061483892024</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4359689057194981</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.91157323980174</v>
+        <v>2.822880853482882</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.117396842703376</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9992014541831877</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3777852943883036</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.873187792211268</v>
+        <v>2.78449540589241</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.169912644978196</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.09748953490745</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3777852943883036</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.992482193845458</v>
+        <v>2.9037898075266</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.183779406312114</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.092776159360016</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3399273776544807</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.970600772791298</v>
+        <v>2.88190838647244</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.138975234772184</v>
+        <v>-4.39040041076919</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.116706358372914</v>
+        <v>1.016136287974112</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3399273776544807</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.976609303188224</v>
+        <v>2.887916916869366</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.991232264537182</v>
+        <v>-4.242657440534187</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.073753767744114</v>
+        <v>0.9731836973453125</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5077347348893638</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.975243938806353</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.07505348581188</v>
+        <v>-4.326478661808886</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.043018900765716</v>
+        <v>0.9424488303669141</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5077347348893638</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.978037560337834</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.068900779759096</v>
+        <v>-4.317145893814586</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.046142331578488</v>
+        <v>0.9468442859562924</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5138874409421481</v>
+        <v>0.3692468590189007</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.982391532361163</v>
+        <v>2.895607183207215</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.085710077909598</v>
+        <v>-4.333955191965088</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.038499089058398</v>
+        <v>0.9392010434362019</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4970781427916464</v>
+        <v>0.3524375608683991</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.971386430210972</v>
+        <v>2.884602081057024</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.86736263679842</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.023412079133475</v>
+        <v>-4.271657193188966</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.129753842365668</v>
+        <v>1.030455796743472</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5423724070660885</v>
+        <v>0.3977318251428411</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.064898542572458</v>
+        <v>2.97811419341851</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.821621881468317</v>
+        <v>-4.069866995523808</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.012761923145858</v>
+        <v>0.9134638775236619</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7403905992352429</v>
+        <v>0.5957500173119955</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.986001459588078</v>
+        <v>2.89921711043413</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.872508594154512</v>
+        <v>-4.120753708210002</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.062697470393555</v>
+        <v>0.9633994247713593</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6895038865490484</v>
+        <v>0.5448633046258009</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.025759664298537</v>
+        <v>2.938975315144588</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.785897851504705</v>
+        <v>-4.034142965560195</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.111969503569522</v>
+        <v>1.012671457947325</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7681296177542066</v>
+        <v>0.6234890358309592</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.087562839137675</v>
+        <v>3.000778489983727</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.846107149509989</v>
+        <v>-4.09435226356548</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.08642176519208</v>
+        <v>0.9871237195698832</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7079203197489221</v>
+        <v>0.5632797378256746</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.049973241159176</v>
+        <v>2.963188892005228</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.769685103078062</v>
+        <v>-4.017930217133554</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.115482201804779</v>
+        <v>1.016184156182583</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7079203197489221</v>
+        <v>0.5632797378256746</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.048464859199105</v>
+        <v>2.961680510045156</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.725311971439494</v>
+        <v>-3.973557085494985</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.133094321895643</v>
+        <v>1.033796276273446</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7522934513874907</v>
+        <v>0.6076528694642432</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.074951605617682</v>
+        <v>2.988167256463734</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.747792322298379</v>
+        <v>-3.99603743635387</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.118495975690679</v>
+        <v>1.019197930068483</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7522934513874907</v>
+        <v>0.6076528694642432</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.069345399756273</v>
+        <v>2.982561050602324</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.700136591737323</v>
+        <v>-3.948381705792814</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.143940024942906</v>
+        <v>1.04464197932071</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7999491819485464</v>
+        <v>0.6553086000252989</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.10432059512071</v>
+        <v>3.017536245966762</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.599618433238568</v>
+        <v>-3.847863547294059</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.189039661717133</v>
+        <v>1.089741616094936</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9004673404473009</v>
+        <v>0.7558267585240535</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.169523863594688</v>
+        <v>3.08273951444074</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.583713103806216</v>
+        <v>-3.831958217861707</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.182156465965946</v>
+        <v>1.08285842034375</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.821354679738062</v>
+        <v>0.6767140978148145</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.108810939645017</v>
+        <v>3.022026590491069</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.538874702197818</v>
+        <v>-3.787119816253309</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.204189529219934</v>
+        <v>1.104891483597737</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8258981126829315</v>
+        <v>0.681257530759684</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.115634702022567</v>
+        <v>3.028850352868619</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.558373158439826</v>
+        <v>-3.806618272495317</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.200551086354209</v>
+        <v>1.101253040732012</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7778134714030271</v>
+        <v>0.6331728894797797</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.090944856885703</v>
+        <v>3.004160507731754</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.514170321353925</v>
+        <v>-3.762415435409416</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.224111823716406</v>
+        <v>1.12481377809421</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8220163084889276</v>
+        <v>0.6773757265656801</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.12334616166508</v>
+        <v>3.036561812511132</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.521729987190972</v>
+        <v>-3.769975101246463</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.219497957850835</v>
+        <v>1.120199912228638</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8768197124987469</v>
+        <v>0.7321791305754994</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.154638204540219</v>
+        <v>3.067853855386271</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.3634385696517</v>
+        <v>-3.611683683707191</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.334062290049583</v>
+        <v>1.234764244427387</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8768197124987469</v>
+        <v>0.7321791305754994</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.205885969723259</v>
+        <v>3.11910162056931</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.155796566017224</v>
+        <v>-3.404041680072715</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.415559796097627</v>
+        <v>1.316261750475431</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.084461716133223</v>
+        <v>0.9398211342099756</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.328911876498198</v>
+        <v>3.242127527344249</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.104764473294696</v>
+        <v>-3.353009587350187</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.430920861424908</v>
+        <v>1.331622815802712</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.135493808855751</v>
+        <v>0.9908532269325034</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.354479360369985</v>
+        <v>3.267695011216036</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.03954029216749</v>
+        <v>-3.287785406222981</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.474197937968496</v>
+        <v>1.374899892346299</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.200717989982957</v>
+        <v>1.056077408059709</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.410801273139013</v>
+        <v>3.324016923985064</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.002113272096356</v>
+        <v>-3.250358386151847</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.485129718296229</v>
+        <v>1.385831672674033</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.205969528012139</v>
+        <v>1.061328946088891</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.409913168255803</v>
+        <v>3.323128819101854</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.022224928131064</v>
+        <v>-3.261238979170562</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.478341848213586</v>
+        <v>1.382736227797787</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.216996873009558</v>
+        <v>1.125630658872983</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.417786367585494</v>
+        <v>3.362966639103549</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.993811665031181</v>
+        <v>-3.232825716070678</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.65026492447475</v>
+        <v>1.554659304058951</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.158021310263129</v>
+        <v>1.066655096126554</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.542958800958848</v>
+        <v>3.488139072476903</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.919029404006168</v>
+        <v>-3.158043455045666</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.800290738102573</v>
+        <v>1.704685117686774</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.232803571288142</v>
+        <v>1.141437357151567</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.707941066791673</v>
+        <v>3.653121338309727</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.89294531974236</v>
+        <v>-3.131959370781858</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.802432347821955</v>
+        <v>1.706826727406156</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.232803571288142</v>
+        <v>1.141437357151567</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.699649042805532</v>
+        <v>3.644829314323586</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.80506740663324</v>
+        <v>-3.044081457672737</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.835776708649383</v>
+        <v>1.740171088233584</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.348729213711493</v>
+        <v>1.257362999574918</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.767397623843322</v>
+        <v>3.712577895361377</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.796174945239956</v>
+        <v>-3.035188996279454</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.856888098933487</v>
+        <v>1.761282478517688</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.348729213711493</v>
+        <v>1.257362999574918</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.784952029570113</v>
+        <v>3.730132301088168</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.964651062209834</v>
+        <v>-3.203665113249332</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.78135269955012</v>
+        <v>1.685747079134321</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.320781377994912</v>
+        <v>1.229415163858337</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.760038375544748</v>
+        <v>3.705218647062804</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.518394869580394</v>
+        <v>-2.757408920619892</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.941124873789758</v>
+        <v>1.845519253373959</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.226062708325279</v>
+        <v>1.134696494188705</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.684476870930831</v>
+        <v>3.629657142448886</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.495673765897242</v>
+        <v>-2.73468781693674</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.940877337759924</v>
+        <v>1.845271717344124</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.226062708325279</v>
+        <v>1.134696494188705</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.675140893427735</v>
+        <v>3.62032116494579</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.624875579191284</v>
+        <v>-2.863889630230782</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.048102738293475</v>
+        <v>1.952497117877677</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.096860895031237</v>
+        <v>1.005494680894662</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.756525931302479</v>
+        <v>3.701706202820534</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.65074997766531</v>
+        <v>-2.889764028704808</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.074830801397512</v>
+        <v>1.979225180981713</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.141772503742978</v>
+        <v>1.050406289606403</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.82055071902317</v>
+        <v>3.765730990541226</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.643695287450136</v>
+        <v>-2.882709338489634</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.074328033473126</v>
+        <v>1.978722413057327</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.148827193958152</v>
+        <v>1.057460979821577</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.82145888914182</v>
+        <v>3.766639160659875</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.616744063123648</v>
+        <v>-2.855758114163146</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.095114676848463</v>
+        <v>1.999509056432664</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.163707539985871</v>
+        <v>1.072341325849296</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.840393250403193</v>
+        <v>3.785573521921248</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.752697071179965</v>
+        <v>-2.991711122219463</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.224836605770896</v>
+        <v>2.129230985355097</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.163707539985871</v>
+        <v>1.072341325849296</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.024496382548152</v>
+        <v>3.969676654066207</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.775105188984837</v>
+        <v>-3.014119240024335</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.207990053551941</v>
+        <v>2.112384433136142</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.163707539985871</v>
+        <v>1.072341325849296</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.016613077451145</v>
+        <v>3.9617933489692</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.803329424562437</v>
+        <v>-3.042343475601935</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.198754358870538</v>
+        <v>2.103148738454739</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.18168429243718</v>
+        <v>1.090318078300605</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.029453128471568</v>
+        <v>3.974633399989624</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.812770350450967</v>
+        <v>-3.051784401490465</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.251231706236974</v>
+        <v>2.155626085821174</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.304111409980571</v>
+        <v>1.212745195843997</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.15916311671945</v>
+        <v>4.104343388237505</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.865043957786608</v>
+        <v>-3.104058008826106</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.233213357848018</v>
+        <v>2.137607737432218</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.25183780264493</v>
+        <v>1.160471588508355</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.130690046863366</v>
+        <v>4.075870318381422</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.941373935387514</v>
+        <v>-3.180387986427012</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.200793179701431</v>
+        <v>2.105187559285631</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.25183780264493</v>
+        <v>1.160471588508355</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.128801859757141</v>
+        <v>4.073982131275197</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.143627655711867</v>
+        <v>-3.382641706751365</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.114711921174552</v>
+        <v>2.019106300758752</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.049584082320576</v>
+        <v>0.9582178681840017</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.002269857165391</v>
+        <v>3.947450128683447</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.305196081239123</v>
+        <v>-3.544210132278621</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.048518561173802</v>
+        <v>1.952912940758003</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9228011585226968</v>
+        <v>0.8314349443861223</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.924634113096817</v>
+        <v>3.869814384614871</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.413496743109242</v>
+        <v>-3.65251079414874</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.018271703291672</v>
+        <v>1.922666082875873</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9228011585226968</v>
+        <v>0.8314349443861223</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.937707519962735</v>
+        <v>3.88288779148079</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.506644214412609</v>
+        <v>-3.745658265452107</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.973017911553266</v>
+        <v>1.877412291137467</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7999719472401641</v>
+        <v>0.7086057331035895</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.856015189976155</v>
+        <v>3.801195461494211</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.534545001522082</v>
+        <v>-3.77355905256158</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.960381637836479</v>
+        <v>1.864776017420679</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7653750230972293</v>
+        <v>0.6740088089606547</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.833781076617396</v>
+        <v>3.778961348135452</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.657071104224975</v>
+        <v>-3.896085155264474</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.90813564073252</v>
+        <v>1.812530020316721</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6428489203943354</v>
+        <v>0.5514827062577609</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.757029858972859</v>
+        <v>3.702210130490914</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.887585600410564</v>
+        <v>-4.126599651450062</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.882635801848788</v>
+        <v>1.787030181432989</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4123344242087467</v>
+        <v>0.3209682100721721</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.685427120852009</v>
+        <v>3.630607392370064</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.236330685635008</v>
+        <v>-4.475344736674506</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.883449486760858</v>
+        <v>1.787843866345058</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3035864702898489</v>
+        <v>0.2122202561532743</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.760490067502518</v>
+        <v>3.705670339020573</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.390317103411149</v>
+        <v>-4.629331154450647</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.890835188796041</v>
+        <v>1.795229568380242</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3035864702898489</v>
+        <v>0.2122202561532743</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.829470336648158</v>
+        <v>3.774650608166213</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.339795199583483</v>
+        <v>-4.578809250622981</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.897095152447228</v>
+        <v>1.801489532031429</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3035864702898489</v>
+        <v>0.2122202561532743</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.815521538768278</v>
+        <v>3.760701810286334</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.592270353591207</v>
+        <v>-4.831284404630705</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.807975579899553</v>
+        <v>1.712369959483753</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3035864702898489</v>
+        <v>0.2122202561532743</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.827392027823692</v>
+        <v>3.772572299341748</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.885166110070619</v>
+        <v>-5.124180161110117</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.692027811826732</v>
+        <v>1.596422191410932</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3035864702898489</v>
+        <v>0.2122202561532743</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.828602562342636</v>
+        <v>3.773782833860691</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.071830238205427</v>
+        <v>-5.310844289244925</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.62148390280013</v>
+        <v>1.525878282384331</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.276847499465289</v>
+        <v>0.1854812853287144</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.816680922075221</v>
+        <v>3.761861193593277</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.217850925119389</v>
+        <v>-5.456864976158887</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.558153480770734</v>
+        <v>1.462547860354935</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.267764407671432</v>
+        <v>0.1763981935348575</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.806308919735097</v>
+        <v>3.751489191253152</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.309564934228975</v>
+        <v>-5.548578985268472</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.683671933825944</v>
+        <v>1.588066313410145</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.267764407671432</v>
+        <v>0.1763981935348575</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.968512976434141</v>
+        <v>3.913693247952196</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.341216593288944</v>
+        <v>-5.580230644328442</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.665857908165771</v>
+        <v>1.570252287749972</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2625959504269918</v>
+        <v>0.1712297362904173</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.960258540051291</v>
+        <v>3.905438811569346</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.423151411557828</v>
+        <v>-5.662165462597325</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.643313398426709</v>
+        <v>1.547707778010909</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2526612048399116</v>
+        <v>0.1612949907033371</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.964527110267534</v>
+        <v>3.909707381785589</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.525127533806235</v>
+        <v>-5.764141584845732</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.611448587983248</v>
+        <v>1.515842967567449</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.150685082591504</v>
+        <v>0.05931886845492951</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.912267075374392</v>
+        <v>3.857447346892447</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.415121250329014</v>
+        <v>-5.654135301368511</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.647603988618312</v>
+        <v>1.551998368202513</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1738896545087792</v>
+        <v>0.08252344037220471</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.918342705768932</v>
+        <v>3.863522977286987</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.272061674588087</v>
+        <v>-5.511075725627585</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.709077829636656</v>
+        <v>1.613472209220858</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1819030810987585</v>
+        <v>0.09053686696218399</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.927400772444894</v>
+        <v>3.87258104396295</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.97061494911625</v>
+        <v>-5.209629000155747</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.836917402707928</v>
+        <v>1.741311782292129</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4833498065705958</v>
+        <v>0.3919835924340213</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.115529690610533</v>
+        <v>4.060709962128588</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.995205193351434</v>
+        <v>-5.234219244390931</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.828052482766565</v>
+        <v>1.732446862350766</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4833498065705958</v>
+        <v>0.3919835924340213</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.116500868363243</v>
+        <v>4.061681139881299</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.944166817344914</v>
+        <v>-5.183180868384411</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.849310737548928</v>
+        <v>1.753705117133129</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4833498065705958</v>
+        <v>0.3919835924340213</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.117343772742998</v>
+        <v>4.062524044261054</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.903027522478283</v>
+        <v>-5.14204157351778</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.884804554369726</v>
+        <v>1.789198933953927</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5244891014372266</v>
+        <v>0.4331228873006521</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.161065448537123</v>
+        <v>4.106245720055178</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.806392610459643</v>
+        <v>-5.04540666149914</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.739642515301117</v>
+        <v>1.644036894885318</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6211240134558665</v>
+        <v>0.529757799319292</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.035230391872241</v>
+        <v>3.980410663390296</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.936973344990485</v>
+        <v>-5.175987396029982</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.690912265562744</v>
+        <v>1.595306645146945</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.490543278925024</v>
+        <v>0.3991770647884495</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.9603839952277</v>
+        <v>3.905564266745755</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.772477010799523</v>
+        <v>-5.01149106183902</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.741137618315211</v>
+        <v>1.645531997899412</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6550396131159859</v>
+        <v>0.5636733989794114</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.043508614818359</v>
+        <v>3.988688886336415</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.799846943483955</v>
+        <v>-5.038860994523453</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.729377355677868</v>
+        <v>1.633771735262069</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6550396131159859</v>
+        <v>0.5636733989794114</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.04269632525479</v>
+        <v>3.987876596772844</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.810232138373845</v>
+        <v>-5.049246189413342</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.735092056846985</v>
+        <v>1.639486436431186</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6446544182260966</v>
+        <v>0.5532882040895221</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.046333987445928</v>
+        <v>3.991514258963983</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.82882029709607</v>
+        <v>-5.067834348135567</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.79849379913452</v>
+        <v>1.702888178718721</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6260662595038713</v>
+        <v>0.5347000453672968</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.106018097989018</v>
+        <v>4.051198369507073</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496549</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.829118843792106</v>
+        <v>-5.068132894831603</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.795243391274404</v>
+        <v>1.699637770858605</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6257677128078354</v>
+        <v>0.5344014986712609</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.102707980789695</v>
+        <v>4.04788825230775</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.728295710101678</v>
+        <v>-4.967309761141175</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.840103539689966</v>
+        <v>1.744497919274167</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6382319282921892</v>
+        <v>0.5468657141556147</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.114717405019698</v>
+        <v>4.059897676537754</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.537514349349271</v>
+        <v>-4.776528400388768</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.916545337469473</v>
+        <v>1.820939717053674</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8290132890445966</v>
+        <v>0.7376470749080221</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.229315474949686</v>
+        <v>4.174495746467741</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.518997495307451</v>
+        <v>-4.758011546346948</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.903788924823797</v>
+        <v>1.808183304407998</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8419434184698048</v>
+        <v>0.7505772043332303</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.216910398342408</v>
+        <v>4.162090669860463</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.78576168591298</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.463666907405688</v>
+        <v>-4.702680958445185</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.960888096596561</v>
+        <v>1.865282476180762</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.897274006371567</v>
+        <v>0.8059077922349924</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.285075687695524</v>
+        <v>4.230255959213578</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539889</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.451612780492725</v>
+        <v>-4.690626831532223</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.959396315263183</v>
+        <v>1.863790694847385</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9093281332845298</v>
+        <v>0.8179619191479552</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.285994731744739</v>
+        <v>4.231175003262794</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.492767900060946</v>
+        <v>-4.731781951100444</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.944814897620031</v>
+        <v>1.849209277204232</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8681730137163088</v>
+        <v>0.7768067995797343</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.263182290187943</v>
+        <v>4.208362561705997</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382914</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.389887310532353</v>
+        <v>-4.628901361571851</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.998818159309351</v>
+        <v>1.903212538893552</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9710536032449018</v>
+        <v>0.8796873891083272</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.337761669782981</v>
+        <v>4.282941941301035</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.64685760776031</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.621487703701854</v>
+        <v>-4.860501754741351</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.926380672215144</v>
+        <v>1.830775051799346</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9710536032449018</v>
+        <v>0.8796873891083272</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.357964339956575</v>
+        <v>4.30314461147463</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.639560211993466</v>
+        <v>-4.878574263032963</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.9191516688985</v>
+        <v>1.823546048482701</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9710536032449018</v>
+        <v>0.8796873891083272</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.357964339956575</v>
+        <v>4.30314461147463</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.81466704456991</v>
+        <v>-5.053681095609408</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.809360849461389</v>
+        <v>1.71375522904559</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9710536032449018</v>
+        <v>0.8796873891083272</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.318216253550041</v>
+        <v>4.263396525068097</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943584</v>
+        <v>3.745593333943582</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.783381024029455</v>
+        <v>-5.022395075068952</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.828897876674511</v>
+        <v>1.733292256258712</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.002339623785357</v>
+        <v>0.9109734096487826</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.344010484871255</v>
+        <v>4.28919075638931</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677819</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.630355631916171</v>
+        <v>-4.869369682955668</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.989279033092729</v>
+        <v>1.89367341267693</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.155365015898641</v>
+        <v>1.063998801762067</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.534996719712129</v>
+        <v>4.480176991230184</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.658662945789441</v>
+        <v>-4.897676996828938</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.165422332451713</v>
+        <v>2.069816712035914</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.155365015898641</v>
+        <v>1.063998801762067</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.722462944620421</v>
+        <v>4.667643216138477</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.825256170902963</v>
+        <v>-5.06427022194246</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.068187993760386</v>
+        <v>1.972582373344587</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9887717907851188</v>
+        <v>0.8974055766485443</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.59190996090639</v>
+        <v>4.537090232424446</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568378</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.652191791520663</v>
+        <v>-4.891205842560161</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.141090148175024</v>
+        <v>2.045484527759225</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9887717907851188</v>
+        <v>0.8974055766485443</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.595586363568108</v>
+        <v>4.540766635086164</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.622945811064967</v>
+        <v>-4.861959862104464</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.150406595480798</v>
+        <v>2.054800975064999</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9887717907851188</v>
+        <v>0.8974055766485443</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.593204418691603</v>
+        <v>4.538384690209659</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.729871358942818</v>
+        <v>-4.968885409982315</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.104929615487293</v>
+        <v>2.009323995071494</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8818462429072674</v>
+        <v>0.7904800287706929</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.526342329122528</v>
+        <v>4.471522600640583</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.874889917450067</v>
+        <v>-5.113903968489564</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.048350994227627</v>
+        <v>1.952745373811828</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7368276844000189</v>
+        <v>0.6454614702634444</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.440759996161413</v>
+        <v>4.385940267679468</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.993231683234784</v>
+        <v>-5.232245734274281</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.100945527171493</v>
+        <v>2.005339906755694</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.747513722962909</v>
+        <v>0.6561475088263344</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.5471028585569</v>
+        <v>4.492283130074955</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073533</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.044642105555492</v>
+        <v>-5.283656156594989</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.078167055369148</v>
+        <v>1.98256143495335</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.747513722962909</v>
+        <v>0.6561475088263344</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.544888555682839</v>
+        <v>4.490068827200894</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.70477813472006</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.124061556763244</v>
+        <v>-5.363075607802741</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.046302402960337</v>
+        <v>1.950696782544539</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.747513722962909</v>
+        <v>0.6561475088263344</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.544791683757128</v>
+        <v>4.489971955275183</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.219524554680461</v>
+        <v>-5.458538605719959</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.008111097351494</v>
+        <v>1.912505476935695</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.747513722962909</v>
+        <v>0.6561475088263344</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.544785577315172</v>
+        <v>4.489965848833227</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.259544552724245</v>
+        <v>-5.498558603763742</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.990199494696591</v>
+        <v>1.894593874280792</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7074937249191251</v>
+        <v>0.6161275107825506</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.518869975051512</v>
+        <v>4.464050246569567</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636265</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.314913714856439</v>
+        <v>-5.553927765895936</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.97378564759144</v>
+        <v>1.878180027175641</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7074937249191251</v>
+        <v>0.6161275107825506</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.524603792799239</v>
+        <v>4.469784064317293</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396008</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.360351494687266</v>
+        <v>-5.599365545726763</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.955148899002042</v>
+        <v>1.859543278586243</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6646487342409655</v>
+        <v>0.573282520104391</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.498435161735276</v>
+        <v>4.44361543325333</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396417</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.277126037839602</v>
+        <v>-5.516140088879099</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.008313474591427</v>
+        <v>1.912707854175628</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6646487342409655</v>
+        <v>0.573282520104391</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.518309554585595</v>
+        <v>4.46348982610365</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.79450702929917</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.100835813234294</v>
+        <v>-5.339849864273791</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.062530264958278</v>
+        <v>1.966924644542479</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6646487342409655</v>
+        <v>0.573282520104391</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.502010255110322</v>
+        <v>4.447190526628377</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590402</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.917624150101199</v>
+        <v>-5.156638201140696</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.138245879675561</v>
+        <v>2.042640259259763</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6646487342409655</v>
+        <v>0.573282520104391</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.504441204574368</v>
+        <v>4.449621476092423</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146281</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.845902703087348</v>
+        <v>-5.084916754126845</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.132725644328991</v>
+        <v>2.037120023913193</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7363701812548161</v>
+        <v>0.6450039671182416</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.513265258630567</v>
+        <v>4.458445530148623</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676844</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.975281485727126</v>
+        <v>-5.214295536766623</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.027889877194252</v>
+        <v>1.932284256778453</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6942684085476127</v>
+        <v>0.6029021944110382</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.434919940927418</v>
+        <v>4.380100212445472</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,45 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.932585619135191</v>
+        <v>3.715627631739457</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.008297781637871</v>
+        <v>-5.247311832677368</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.19988156371531</v>
+        <v>2.10427594329951</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6248310318808612</v>
+        <v>0.5334648177442867</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.578455719812722</v>
+        <v>4.523635991330777</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="2" t="n">
+        <v>45533</v>
+      </c>
+      <c r="B2071" t="n">
+        <v>3.864907041611877</v>
+      </c>
+      <c r="C2071" t="n">
+        <v>4.390211449873751</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>-5.247311832677368</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>2.10427594329951</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>0.5334648177442867</v>
+      </c>
+      <c r="G2071" t="n">
+        <v>4.383275246860119</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>102.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>421.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.3%</t>
+          <t>-672.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.8%</t>
+          <t>-160.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.7%</t>
+          <t>587.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-305.8%</t>
+          <t>-310.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-170.6%</t>
+          <t>-168.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-32.4%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.57568762888042</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.042087625168595</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.3757158684972343</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>3.098148622132851</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.442819939817142</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.11112888359573</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.3757158684972343</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>3.114042804934675</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.322646856452644</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.160343961381831</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.4958889518617332</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.187292499393676</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-4.187393495122667</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.224533408475262</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.6311423131917103</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.278532618753102</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.247268322480359</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.186620968933611</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.5712674858340182</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.228645213739913</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-4.127448091569522</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.249838230532154</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.5712674858340182</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.243934382974121</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-4.129917798031328</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.156494547269873</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.5687977793722121</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>3.150096758419479</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.198287984355338</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.04840833422557</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.578073478408427</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>3.074924039326509</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.310160263981489</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>0.9940961310070013</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.578073478408427</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>3.065360747958401</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.365680339874078</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.108918937342168</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.578073478408427</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.202391584650603</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.190206080081609</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.183675873250944</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.578073478408427</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.206958816642391</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-4.182281705496695</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.162587651846116</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.578073478408427</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.182700845403598</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-4.176003502926846</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.093637246275506</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.5843516809782761</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>3.115006080346957</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-4.116150883723122</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.127750680389127</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.5843516809782761</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>3.12517846677909</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-4.029907420696745</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.157194336173539</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.5843516809782761</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>3.12012473735295</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-4.075214240095725</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.130847383858472</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5435415179690453</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>3.087414414991937</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-4.104247344798026</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.119786015010654</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5435415179690453</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>3.087966288025038</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-4.011436863347166</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.086182899482363</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.6363519994199046</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>3.07292526878692</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-4.055826332676594</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.070300587675193</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.5919625300904769</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>3.048165063113864</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-4.172367937781936</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.018759654144779</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.4754209249851342</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>2.973315808562381</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.212292032364508</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.008281312142417</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.4754209249851342</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>2.978807104393049</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.240072430265861</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.008666354750415</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.4476405270837811</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>2.973636067420776</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.358453102995999</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.799669805659013</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.3804226749328049</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.771661076130843</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.46706718143933</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.8763738350008863</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.3804226749328049</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.891810736850049</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.431658143191187</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9050504764024665</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.3804226749328049</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>2.906323762952372</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.393274480633036</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.9178233827680955</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4188063374909561</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>2.926773401829631</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.21615815059787</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>0.9853989436274639</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4188063374909561</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>2.923502430674933</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.261250395431416</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>0.9680454374559586</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.3569102943215663</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.887048196535213</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-4.081874974192648</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.03358258125788</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.513687052492285</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>2.974901226744058</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-4.126889187713255</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>0.9963843511812271</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.4833381571776804</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>2.937499344886885</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.142468521988684</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9958441798100013</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.4367957629994946</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.915265470718919</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.243666303425857</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.9545689891316336</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.3683869494541754</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.873424104488229</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.237155336811544</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.9547733373316754</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.3683869494541754</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.871024066042546</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.218117209104247</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.9589133076228391</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.3102033381229808</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.832638618452074</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.270633011379068</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>1.057201388347101</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.3102033381229808</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.951933020086265</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.284499772712985</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>1.052488012799668</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.2723454213891579</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.930051599032104</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.39040041076919</v>
+        <v>-4.239695601173056</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.016136287974112</v>
+        <v>1.076418211812566</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.2723454213891579</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.93606012942903</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.242657440534187</v>
+        <v>-4.091952630938053</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9731836973453125</v>
+        <v>1.033465621183766</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.4401527786240411</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.934694765047159</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.326478661808886</v>
+        <v>-4.175773852212751</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9424488303669141</v>
+        <v>1.002730754205368</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.4401527786240411</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.93748838657864</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.317145893814586</v>
+        <v>-4.169621146159967</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9468442859562924</v>
+        <v>1.00585418501814</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3692468590189007</v>
+        <v>0.4463054846768253</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.895607183207215</v>
+        <v>2.941842358601969</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.333955191965088</v>
+        <v>-4.186430444310469</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9392010434362019</v>
+        <v>0.9982109424980494</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3524375608683991</v>
+        <v>0.4294961865263237</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.884602081057024</v>
+        <v>2.930837256451779</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679842</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.271657193188966</v>
+        <v>-4.124132445534347</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.030455796743472</v>
+        <v>1.089465695805319</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3977318251428411</v>
+        <v>0.4747904508007658</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.97811419341851</v>
+        <v>3.024349368813265</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.069866995523808</v>
+        <v>-3.922342247869189</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9134638775236619</v>
+        <v>0.9724737765855094</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5957500173119955</v>
+        <v>0.6728086429699202</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89921711043413</v>
+        <v>2.945452285828885</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.120753708210002</v>
+        <v>-3.973228960555383</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9633994247713593</v>
+        <v>1.022409323833207</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5448633046258009</v>
+        <v>0.6219219302837256</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.938975315144588</v>
+        <v>2.985210490539343</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.034142965560195</v>
+        <v>-3.886618217905576</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.012671457947325</v>
+        <v>1.071681357009173</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6234890358309592</v>
+        <v>0.7005476614888838</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.000778489983727</v>
+        <v>3.047013665378481</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.09435226356548</v>
+        <v>-3.946827515910861</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9871237195698832</v>
+        <v>1.046133618631731</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5632797378256746</v>
+        <v>0.6403383634835993</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.963188892005228</v>
+        <v>3.009424067399983</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.017930217133554</v>
+        <v>-3.870405469478934</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.016184156182583</v>
+        <v>1.075194055244431</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5632797378256746</v>
+        <v>0.6403383634835993</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.961680510045156</v>
+        <v>3.007915685439911</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.973557085494985</v>
+        <v>-3.826032337840365</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.033796276273446</v>
+        <v>1.092806175335294</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6076528694642432</v>
+        <v>0.6847114951221679</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.988167256463734</v>
+        <v>3.034402431858489</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.99603743635387</v>
+        <v>-3.84851268869925</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.019197930068483</v>
+        <v>1.078207829130331</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6076528694642432</v>
+        <v>0.6847114951221679</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.982561050602324</v>
+        <v>3.028796225997079</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.948381705792814</v>
+        <v>-3.800856958138194</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.04464197932071</v>
+        <v>1.103651878382558</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6553086000252989</v>
+        <v>0.7323672256832235</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.017536245966762</v>
+        <v>3.063771421361517</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.847863547294059</v>
+        <v>-3.700338799639439</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.089741616094936</v>
+        <v>1.148751515156784</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7558267585240535</v>
+        <v>0.8328853841819781</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.08273951444074</v>
+        <v>3.128974689835494</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.831958217861707</v>
+        <v>-3.684433470207087</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.08285842034375</v>
+        <v>1.141868319405598</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6767140978148145</v>
+        <v>0.7537727234727392</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.022026590491069</v>
+        <v>3.068261765885823</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.787119816253309</v>
+        <v>-3.639595068598689</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.104891483597737</v>
+        <v>1.163901382659585</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.681257530759684</v>
+        <v>0.7583161564176086</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.028850352868619</v>
+        <v>3.075085528263374</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.806618272495317</v>
+        <v>-3.659093524840697</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.101253040732012</v>
+        <v>1.16026293979386</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6331728894797797</v>
+        <v>0.7102315151377043</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.004160507731754</v>
+        <v>3.050395683126509</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.762415435409416</v>
+        <v>-3.614890687754797</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.12481377809421</v>
+        <v>1.183823677156058</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6773757265656801</v>
+        <v>0.7544343522236048</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.036561812511132</v>
+        <v>3.082796987905887</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265638</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.769975101246463</v>
+        <v>-3.622450353591844</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.120199912228638</v>
+        <v>1.179209811290486</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7321791305754994</v>
+        <v>0.8092377562334241</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.067853855386271</v>
+        <v>3.114089030781026</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.611683683707191</v>
+        <v>-3.464158936052571</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.234764244427387</v>
+        <v>1.293774143489235</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7321791305754994</v>
+        <v>0.8092377562334241</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.11910162056931</v>
+        <v>3.165336795964065</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.404041680072715</v>
+        <v>-3.256516932418095</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.316261750475431</v>
+        <v>1.375271649537278</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9398211342099756</v>
+        <v>1.0168797598679</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.242127527344249</v>
+        <v>3.288362702739004</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.353009587350187</v>
+        <v>-3.205484839695567</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.331622815802712</v>
+        <v>1.39063271486456</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9908532269325034</v>
+        <v>1.067911852590428</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.267695011216036</v>
+        <v>3.313930186610791</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.287785406222981</v>
+        <v>-3.140260658568361</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.374899892346299</v>
+        <v>1.433909791408147</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.056077408059709</v>
+        <v>1.133136033717634</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.324016923985064</v>
+        <v>3.370252099379819</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.250358386151847</v>
+        <v>-3.102833638497227</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.385831672674033</v>
+        <v>1.444841571735881</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.061328946088891</v>
+        <v>1.138387571746815</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.323128819101854</v>
+        <v>3.369363994496609</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.261238979170562</v>
+        <v>-3.122945294531936</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.382736227797787</v>
+        <v>1.438053701653238</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.125630658872983</v>
+        <v>1.149414916744235</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.362966639103549</v>
+        <v>3.3772371938263</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.232825716070678</v>
+        <v>-3.094532031432052</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.554659304058951</v>
+        <v>1.609976777914402</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.066655096126554</v>
+        <v>1.090439353997806</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.488139072476903</v>
+        <v>3.502409627199654</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.158043455045666</v>
+        <v>-3.01974977040704</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.704685117686774</v>
+        <v>1.760002591542224</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.141437357151567</v>
+        <v>1.165221615022819</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.653121338309727</v>
+        <v>3.667391893032478</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.131959370781858</v>
+        <v>-2.993665686143232</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.706826727406156</v>
+        <v>1.762144201261606</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.141437357151567</v>
+        <v>1.165221615022819</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.644829314323586</v>
+        <v>3.659099869046337</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.044081457672737</v>
+        <v>-2.905787773034111</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.740171088233584</v>
+        <v>1.795488562089034</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.257362999574918</v>
+        <v>1.28114725744617</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.712577895361377</v>
+        <v>3.726848450084128</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959852</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.035188996279454</v>
+        <v>-2.896895311640828</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.761282478517688</v>
+        <v>1.816599952373139</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.257362999574918</v>
+        <v>1.28114725744617</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.730132301088168</v>
+        <v>3.744402855810919</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.203665113249332</v>
+        <v>-3.065371428610705</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.685747079134321</v>
+        <v>1.741064552989772</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.229415163858337</v>
+        <v>1.253199421729589</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.705218647062804</v>
+        <v>3.719489201785555</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.757408920619892</v>
+        <v>-2.619115235981265</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.845519253373959</v>
+        <v>1.90083672722941</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.134696494188705</v>
+        <v>1.158480752059956</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.629657142448886</v>
+        <v>3.643927697171637</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.73468781693674</v>
+        <v>-2.596394132298113</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.845271717344124</v>
+        <v>1.900589191199575</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.134696494188705</v>
+        <v>1.158480752059956</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.62032116494579</v>
+        <v>3.634591719668541</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.863889630230782</v>
+        <v>-2.725595945592155</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.952497117877677</v>
+        <v>2.007814591733127</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.005494680894662</v>
+        <v>1.029278938765914</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.701706202820534</v>
+        <v>3.715976757543285</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.889764028704808</v>
+        <v>-2.751470344066181</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.979225180981713</v>
+        <v>2.034542654837163</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.050406289606403</v>
+        <v>1.074190547477655</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.765730990541226</v>
+        <v>3.780001545263976</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.882709338489634</v>
+        <v>-2.744415653851008</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.978722413057327</v>
+        <v>2.034039886912778</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.057460979821577</v>
+        <v>1.081245237692829</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.766639160659875</v>
+        <v>3.780909715382626</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.855758114163146</v>
+        <v>-2.71746442952452</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.999509056432664</v>
+        <v>2.054826530288115</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.072341325849296</v>
+        <v>1.096125583720548</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.785573521921248</v>
+        <v>3.799844076643999</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.991711122219463</v>
+        <v>-2.853417437580836</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.129230985355097</v>
+        <v>2.184548459210548</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.072341325849296</v>
+        <v>1.096125583720548</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.969676654066207</v>
+        <v>3.983947208788958</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.014119240024335</v>
+        <v>-2.875825555385708</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.112384433136142</v>
+        <v>2.167701906991592</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.072341325849296</v>
+        <v>1.096125583720548</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.9617933489692</v>
+        <v>3.976063903691951</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.042343475601935</v>
+        <v>-2.904049790963308</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.103148738454739</v>
+        <v>2.15846621231019</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.090318078300605</v>
+        <v>1.114102336171856</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.974633399989624</v>
+        <v>3.988903954712375</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.051784401490465</v>
+        <v>-2.913490716851838</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.155626085821174</v>
+        <v>2.210943559676624</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.212745195843997</v>
+        <v>1.236529453715248</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.104343388237505</v>
+        <v>4.118613942960256</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.104058008826106</v>
+        <v>-2.96576432418748</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.137607737432218</v>
+        <v>2.192925211287669</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.160471588508355</v>
+        <v>1.184255846379607</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.075870318381422</v>
+        <v>4.090140873104172</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.180387986427012</v>
+        <v>-3.042094301788385</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.105187559285631</v>
+        <v>2.160505033141082</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.160471588508355</v>
+        <v>1.184255846379607</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.073982131275197</v>
+        <v>4.088252685997947</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.382641706751365</v>
+        <v>-3.244348022112739</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.019106300758752</v>
+        <v>2.074423774614203</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9582178681840017</v>
+        <v>0.9820021260552532</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.947450128683447</v>
+        <v>3.961720683406198</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.544210132278621</v>
+        <v>-3.405916447639994</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.952912940758003</v>
+        <v>2.008230414613453</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8314349443861223</v>
+        <v>0.8552192022573738</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.869814384614871</v>
+        <v>3.884084939337622</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.65251079414874</v>
+        <v>-3.514217109510113</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.922666082875873</v>
+        <v>1.977983556731324</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8314349443861223</v>
+        <v>0.8552192022573738</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.88288779148079</v>
+        <v>3.897158346203541</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.745658265452107</v>
+        <v>-3.60736458081348</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.877412291137467</v>
+        <v>1.932729764992917</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7086057331035895</v>
+        <v>0.732389990974841</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.801195461494211</v>
+        <v>3.815466016216961</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.77355905256158</v>
+        <v>-3.635265367922953</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.864776017420679</v>
+        <v>1.92009349127613</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6740088089606547</v>
+        <v>0.6977930668319062</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.778961348135452</v>
+        <v>3.793231902858202</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.896085155264474</v>
+        <v>-3.757791470625847</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.812530020316721</v>
+        <v>1.867847494172171</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5514827062577609</v>
+        <v>0.5752669641290123</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.702210130490914</v>
+        <v>3.716480685213665</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.126599651450062</v>
+        <v>-3.988305966811436</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.787030181432989</v>
+        <v>1.842347655288439</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3209682100721721</v>
+        <v>0.3447524679434236</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.630607392370064</v>
+        <v>3.644877947092815</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814661</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.475344736674506</v>
+        <v>-4.337051052035879</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.787843866345058</v>
+        <v>1.843161340200509</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2122202561532743</v>
+        <v>0.2360045140245258</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.705670339020573</v>
+        <v>3.719940893743324</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.629331154450647</v>
+        <v>-4.49103746981202</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.795229568380242</v>
+        <v>1.850547042235693</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2122202561532743</v>
+        <v>0.2360045140245258</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.774650608166213</v>
+        <v>3.788921162888963</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.578809250622981</v>
+        <v>-4.440515565984354</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.801489532031429</v>
+        <v>1.85680700588688</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2122202561532743</v>
+        <v>0.2360045140245258</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.760701810286334</v>
+        <v>3.774972365009084</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.831284404630705</v>
+        <v>-4.692990719992078</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.712369959483753</v>
+        <v>1.767687433339204</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2122202561532743</v>
+        <v>0.2360045140245258</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.772572299341748</v>
+        <v>3.786842854064498</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.124180161110117</v>
+        <v>-4.985886476471491</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.596422191410932</v>
+        <v>1.651739665266383</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2122202561532743</v>
+        <v>0.2360045140245258</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.773782833860691</v>
+        <v>3.788053388583442</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.310844289244925</v>
+        <v>-5.172550604606299</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.525878282384331</v>
+        <v>1.581195756239781</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1854812853287144</v>
+        <v>0.2092655431999659</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.761861193593277</v>
+        <v>3.776131748316028</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.456864976158887</v>
+        <v>-5.318571291520261</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.462547860354935</v>
+        <v>1.517865334210386</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1763981935348575</v>
+        <v>0.200182451406109</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.751489191253152</v>
+        <v>3.765759745975903</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.548578985268472</v>
+        <v>-5.410285300629846</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.588066313410145</v>
+        <v>1.643383787265595</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1763981935348575</v>
+        <v>0.200182451406109</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.913693247952196</v>
+        <v>3.927963802674947</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.580230644328442</v>
+        <v>-5.441936959689816</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.570252287749972</v>
+        <v>1.625569761605422</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1712297362904173</v>
+        <v>0.1950139941616688</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.905438811569346</v>
+        <v>3.919709366292097</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.662165462597325</v>
+        <v>-5.523871777958699</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.547707778010909</v>
+        <v>1.60302525186636</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1612949907033371</v>
+        <v>0.1850792485745886</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.909707381785589</v>
+        <v>3.92397793650834</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.764141584845732</v>
+        <v>-5.625847900207106</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.515842967567449</v>
+        <v>1.571160441422899</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.05931886845492951</v>
+        <v>0.083103126326181</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.857447346892447</v>
+        <v>3.871717901615198</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.654135301368511</v>
+        <v>-5.515841616729885</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.551998368202513</v>
+        <v>1.607315842057963</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.08252344037220471</v>
+        <v>0.1063076982434562</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.863522977286987</v>
+        <v>3.877793532009739</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.511075725627585</v>
+        <v>-5.372782040988959</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.613472209220858</v>
+        <v>1.668789683076308</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.09053686696218399</v>
+        <v>0.1143211248334355</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.87258104396295</v>
+        <v>3.8868515986857</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.209629000155747</v>
+        <v>-5.071335315517121</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.741311782292129</v>
+        <v>1.796629256147579</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3919835924340213</v>
+        <v>0.4157678503052727</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.060709962128588</v>
+        <v>4.074980516851339</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.234219244390931</v>
+        <v>-5.095925559752305</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.732446862350766</v>
+        <v>1.787764336206216</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3919835924340213</v>
+        <v>0.4157678503052727</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.061681139881299</v>
+        <v>4.07595169460405</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.183180868384411</v>
+        <v>-5.044887183745785</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.753705117133129</v>
+        <v>1.80902259098858</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3919835924340213</v>
+        <v>0.4157678503052727</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.062524044261054</v>
+        <v>4.076794598983805</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.14204157351778</v>
+        <v>-5.003747888879154</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.789198933953927</v>
+        <v>1.844516407809377</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4331228873006521</v>
+        <v>0.4569071451719036</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.106245720055178</v>
+        <v>4.120516274777929</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.04540666149914</v>
+        <v>-4.907112976860514</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.644036894885318</v>
+        <v>1.699354368740768</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.529757799319292</v>
+        <v>0.5535420571905435</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.980410663390296</v>
+        <v>3.994681218113048</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.175987396029982</v>
+        <v>-5.037693711391356</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.595306645146945</v>
+        <v>1.650624119002395</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3991770647884495</v>
+        <v>0.422961322659701</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.905564266745755</v>
+        <v>3.919834821468505</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.01149106183902</v>
+        <v>-4.873197377200395</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.645531997899412</v>
+        <v>1.700849471754863</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5636733989794114</v>
+        <v>0.5874576568506629</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.988688886336415</v>
+        <v>4.002959441059166</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.038860994523453</v>
+        <v>-4.900567309884827</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.633771735262069</v>
+        <v>1.689089209117519</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5636733989794114</v>
+        <v>0.5874576568506629</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.987876596772844</v>
+        <v>4.002147151495596</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.049246189413342</v>
+        <v>-4.910952504774716</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.639486436431186</v>
+        <v>1.694803910286636</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5532882040895221</v>
+        <v>0.5770724619607736</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.991514258963983</v>
+        <v>4.005784813686734</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.067834348135567</v>
+        <v>-4.929540663496941</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.702888178718721</v>
+        <v>1.758205652574171</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5347000453672968</v>
+        <v>0.5584843032385483</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.051198369507073</v>
+        <v>4.065468924229824</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496549</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.068132894831603</v>
+        <v>-4.929839210192977</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.699637770858605</v>
+        <v>1.754955244714055</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5344014986712609</v>
+        <v>0.5581857565425123</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.04788825230775</v>
+        <v>4.062158807030501</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.967309761141175</v>
+        <v>-4.829016076502549</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.744497919274167</v>
+        <v>1.799815393129618</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5468657141556147</v>
+        <v>0.5706499720268662</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.059897676537754</v>
+        <v>4.074168231260505</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.776528400388768</v>
+        <v>-4.638234715750142</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.820939717053674</v>
+        <v>1.876257190909124</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7376470749080221</v>
+        <v>0.7614313327792736</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.174495746467741</v>
+        <v>4.188766301190492</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.758011546346948</v>
+        <v>-4.619717861708322</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.808183304407998</v>
+        <v>1.863500778263449</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7505772043332303</v>
+        <v>0.7743614622044818</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.162090669860463</v>
+        <v>4.176361224583214</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591298</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.702680958445185</v>
+        <v>-4.56438727380656</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.865282476180762</v>
+        <v>1.920599950036212</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8059077922349924</v>
+        <v>0.8296920501062439</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.230255959213578</v>
+        <v>4.24452651393633</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539889</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.690626831532223</v>
+        <v>-4.552333146893597</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.863790694847385</v>
+        <v>1.919108168702835</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8179619191479552</v>
+        <v>0.8417461770192067</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.231175003262794</v>
+        <v>4.245445557985545</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.731781951100444</v>
+        <v>-4.593488266461818</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.849209277204232</v>
+        <v>1.904526751059682</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7768067995797343</v>
+        <v>0.8005910574509858</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.208362561705997</v>
+        <v>4.222633116428749</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382914</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.628901361571851</v>
+        <v>-4.490607676933225</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.903212538893552</v>
+        <v>1.958530012749002</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8796873891083272</v>
+        <v>0.9034716469795787</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.282941941301035</v>
+        <v>4.297212496023787</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64685760776031</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.860501754741351</v>
+        <v>-4.722208070102726</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.830775051799346</v>
+        <v>1.886092525654796</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8796873891083272</v>
+        <v>0.9034716469795787</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.30314461147463</v>
+        <v>4.317415166197381</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.878574263032963</v>
+        <v>-4.740280578394337</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.823546048482701</v>
+        <v>1.878863522338151</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8796873891083272</v>
+        <v>0.9034716469795787</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.30314461147463</v>
+        <v>4.317415166197381</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.053681095609408</v>
+        <v>-4.915387410970782</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.71375522904559</v>
+        <v>1.76907270290104</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8796873891083272</v>
+        <v>0.9034716469795787</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.263396525068097</v>
+        <v>4.277667079790848</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943582</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.022395075068952</v>
+        <v>-4.884101390430327</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.733292256258712</v>
+        <v>1.788609730114162</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9109734096487826</v>
+        <v>0.9347576675200341</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.28919075638931</v>
+        <v>4.303461311112061</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677819</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.869369682955668</v>
+        <v>-4.731075998317042</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.89367341267693</v>
+        <v>1.94899088653238</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.063998801762067</v>
+        <v>1.087783059633318</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.480176991230184</v>
+        <v>4.494447545952935</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.897676996828938</v>
+        <v>-4.759383312190312</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.069816712035914</v>
+        <v>2.125134185891365</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.063998801762067</v>
+        <v>1.087783059633318</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.667643216138477</v>
+        <v>4.681913770861228</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.06427022194246</v>
+        <v>-4.925976537303835</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.972582373344587</v>
+        <v>2.027899847200038</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8974055766485443</v>
+        <v>0.9211898345197957</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.537090232424446</v>
+        <v>4.551360787147196</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.891205842560161</v>
+        <v>-4.752912157921535</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.045484527759225</v>
+        <v>2.100802001614675</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8974055766485443</v>
+        <v>0.9211898345197957</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.540766635086164</v>
+        <v>4.555037189808914</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.861959862104464</v>
+        <v>-4.723666177465838</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.054800975064999</v>
+        <v>2.110118448920449</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8974055766485443</v>
+        <v>0.9211898345197957</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.538384690209659</v>
+        <v>4.552655244932409</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.968885409982315</v>
+        <v>-4.830591725343689</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.009323995071494</v>
+        <v>2.064641468926944</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7904800287706929</v>
+        <v>0.8142642866419444</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.471522600640583</v>
+        <v>4.485793155363334</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.113903968489564</v>
+        <v>-4.975610283850938</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.952745373811828</v>
+        <v>2.008062847667278</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6454614702634444</v>
+        <v>0.6692457281346958</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.385940267679468</v>
+        <v>4.400210822402219</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.232245734274281</v>
+        <v>-5.093952049635655</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.005339906755694</v>
+        <v>2.060657380611145</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6561475088263344</v>
+        <v>0.6799317666975859</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.492283130074955</v>
+        <v>4.506553684797706</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073533</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.283656156594989</v>
+        <v>-5.145362471956363</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.98256143495335</v>
+        <v>2.0378789088088</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6561475088263344</v>
+        <v>0.6799317666975859</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.490068827200894</v>
+        <v>4.504339381923645</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70477813472006</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.363075607802741</v>
+        <v>-5.224781923164115</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.950696782544539</v>
+        <v>2.006014256399989</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6561475088263344</v>
+        <v>0.6799317666975859</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.489971955275183</v>
+        <v>4.504242509997934</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.458538605719959</v>
+        <v>-5.320244921081333</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.912505476935695</v>
+        <v>1.967822950791145</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6561475088263344</v>
+        <v>0.6799317666975859</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.489965848833227</v>
+        <v>4.504236403555978</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500729</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.498558603763742</v>
+        <v>-5.360264919125116</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.894593874280792</v>
+        <v>1.949911348136243</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6161275107825506</v>
+        <v>0.6399117686538021</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.464050246569567</v>
+        <v>4.478320801292318</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636265</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.553927765895936</v>
+        <v>-5.41563408125731</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.878180027175641</v>
+        <v>1.933497501031092</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6161275107825506</v>
+        <v>0.6399117686538021</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.469784064317293</v>
+        <v>4.484054619040045</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396008</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.599365545726763</v>
+        <v>-5.461071861088137</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.859543278586243</v>
+        <v>1.914860752441694</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.573282520104391</v>
+        <v>0.5970667779756424</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.44361543325333</v>
+        <v>4.457885987976081</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396417</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.516140088879099</v>
+        <v>-5.377846404240473</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.912707854175628</v>
+        <v>1.968025328031079</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.573282520104391</v>
+        <v>0.5970667779756424</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.46348982610365</v>
+        <v>4.477760380826401</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79450702929917</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.339849864273791</v>
+        <v>-5.201556179635165</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.966924644542479</v>
+        <v>2.02224211839793</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.573282520104391</v>
+        <v>0.5970667779756424</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.447190526628377</v>
+        <v>4.461461081351128</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590402</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.156638201140696</v>
+        <v>-5.01834451650207</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.042640259259763</v>
+        <v>2.097957733115213</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.573282520104391</v>
+        <v>0.5970667779756424</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.449621476092423</v>
+        <v>4.463892030815174</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146281</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.084916754126845</v>
+        <v>-4.946623069488219</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.037120023913193</v>
+        <v>2.092437497768643</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6450039671182416</v>
+        <v>0.6687882249894931</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.458445530148623</v>
+        <v>4.472716084871374</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676844</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.214295536766623</v>
+        <v>-5.076001852127997</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.932284256778453</v>
+        <v>1.987601730633903</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6029021944110382</v>
+        <v>0.6266864522822897</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.380100212445472</v>
+        <v>4.394370767168224</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739457</v>
+        <v>3.715627631739459</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.247311832677368</v>
+        <v>-5.109018148038742</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.10427594329951</v>
+        <v>2.159593417154961</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5334648177442867</v>
+        <v>0.5572490756155382</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.523635991330777</v>
+        <v>4.537906546053528</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.864907041611877</v>
+        <v>3.559664546163284</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.390211449873751</v>
+        <v>4.143657675023303</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.247311832677368</v>
+        <v>-5.109018148038742</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.10427594329951</v>
+        <v>2.159593417154961</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5334648177442867</v>
+        <v>0.5572490756155382</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.383275246860119</v>
+        <v>4.136721472009671</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>129.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.1%</t>
+          <t>423.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-672.5%</t>
+          <t>-686.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.3%</t>
+          <t>-165.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>587.5%</t>
+          <t>593.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-310.4%</t>
+          <t>-264.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-178.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.57568762888042</v>
+        <v>-4.572673044669742</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.042087625168595</v>
+        <v>1.043293458852867</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3757158684972343</v>
+        <v>0.3769032721991853</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.098148622132851</v>
+        <v>3.098861064354022</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.442819939817142</v>
+        <v>-4.439805355606464</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.11112888359573</v>
+        <v>1.112334717280001</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3757158684972343</v>
+        <v>0.3769032721991853</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.114042804934675</v>
+        <v>3.114755247155845</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.322646856452644</v>
+        <v>-4.319632272241965</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.160343961381831</v>
+        <v>1.161549795066102</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4958889518617332</v>
+        <v>0.4970763555636842</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.187292499393676</v>
+        <v>3.188004941614846</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.187393495122667</v>
+        <v>-4.184378910911988</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.224533408475262</v>
+        <v>1.225739242159533</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6311423131917103</v>
+        <v>0.6323297168936614</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.278532618753102</v>
+        <v>3.279245060974273</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.247268322480359</v>
+        <v>-4.244253738269681</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.186620968933611</v>
+        <v>1.187826802617882</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5712674858340182</v>
+        <v>0.5724548895359692</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.228645213739913</v>
+        <v>3.229357655961083</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.127448091569522</v>
+        <v>-4.124433507358844</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.249838230532154</v>
+        <v>1.251044064216425</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5712674858340182</v>
+        <v>0.5724548895359692</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.243934382974121</v>
+        <v>3.244646825195292</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.129917798031328</v>
+        <v>-4.12690321382065</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.156494547269873</v>
+        <v>1.157700380954144</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5687977793722121</v>
+        <v>0.5699851830741631</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.150096758419479</v>
+        <v>3.15080920064065</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.198287984355338</v>
+        <v>-4.19527340014466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.04840833422557</v>
+        <v>1.049614167909842</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.578073478408427</v>
+        <v>0.5792608821103781</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.074924039326509</v>
+        <v>3.07563648154768</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.310160263981489</v>
+        <v>-4.307145679770811</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9940961310070013</v>
+        <v>0.9953019646912726</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.578073478408427</v>
+        <v>0.5792608821103781</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.065360747958401</v>
+        <v>3.066073190179571</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.365680339874078</v>
+        <v>-4.3626657556634</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.108918937342168</v>
+        <v>1.110124771026439</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.578073478408427</v>
+        <v>0.5792608821103781</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.202391584650603</v>
+        <v>3.203104026871774</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.190206080081609</v>
+        <v>-4.18719149587093</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.183675873250944</v>
+        <v>1.184881706935215</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.578073478408427</v>
+        <v>0.5792608821103781</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.206958816642391</v>
+        <v>3.207671258863562</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.182281705496695</v>
+        <v>-4.179267121286016</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.162587651846116</v>
+        <v>1.163793485530388</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.578073478408427</v>
+        <v>0.5792608821103781</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.182700845403598</v>
+        <v>3.183413287624769</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.176003502926846</v>
+        <v>-4.172988918716167</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.093637246275506</v>
+        <v>1.094843079959777</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5843516809782761</v>
+        <v>0.5855390846802271</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.115006080346957</v>
+        <v>3.115718522568128</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.116150883723122</v>
+        <v>-4.113136299512444</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.127750680389127</v>
+        <v>1.128956514073399</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5843516809782761</v>
+        <v>0.5855390846802271</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.12517846677909</v>
+        <v>3.12589090900026</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.029907420696745</v>
+        <v>-4.026892836486066</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.157194336173539</v>
+        <v>1.15840016985781</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5843516809782761</v>
+        <v>0.5855390846802271</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.12012473735295</v>
+        <v>3.12083717957412</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.075214240095725</v>
+        <v>-4.072199655885046</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.130847383858472</v>
+        <v>1.132053217542744</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5435415179690453</v>
+        <v>0.5447289216709963</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.087414414991937</v>
+        <v>3.088126857213108</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.104247344798026</v>
+        <v>-4.101232760587347</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.119786015010654</v>
+        <v>1.120991848694925</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5435415179690453</v>
+        <v>0.5447289216709963</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.087966288025038</v>
+        <v>3.088678730246209</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.011436863347166</v>
+        <v>-4.008422279136488</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.086182899482363</v>
+        <v>1.087388733166634</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6363519994199046</v>
+        <v>0.6375394031218556</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.07292526878692</v>
+        <v>3.07363771100809</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.055826332676594</v>
+        <v>-4.052811748465915</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.070300587675193</v>
+        <v>1.071506421359464</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5919625300904769</v>
+        <v>0.593149933792428</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.048165063113864</v>
+        <v>3.048877505335034</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.172367937781936</v>
+        <v>-4.169353353571258</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.018759654144779</v>
+        <v>1.01996548782905</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4754209249851342</v>
+        <v>0.4766083286870852</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.973315808562381</v>
+        <v>2.974028250783552</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.212292032364508</v>
+        <v>-4.20927744815383</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.008281312142417</v>
+        <v>1.009487145826688</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4754209249851342</v>
+        <v>0.4766083286870852</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.978807104393049</v>
+        <v>2.979519546614219</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.240072430265861</v>
+        <v>-4.237057846055182</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.008666354750415</v>
+        <v>1.009872188434686</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4476405270837811</v>
+        <v>0.4488279307857321</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.973636067420776</v>
+        <v>2.974348509641946</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.358453102995999</v>
+        <v>-4.355438518785321</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.799669805659013</v>
+        <v>0.8008756393432841</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3804226749328049</v>
+        <v>0.3816100786347559</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.771661076130843</v>
+        <v>2.772373518352014</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.46706718143933</v>
+        <v>-4.464052597228652</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8763738350008863</v>
+        <v>0.8775796686851574</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3804226749328049</v>
+        <v>0.3816100786347559</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.891810736850049</v>
+        <v>2.892523179071219</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.431658143191187</v>
+        <v>-4.428643558980509</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9050504764024665</v>
+        <v>0.9062563100867373</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3804226749328049</v>
+        <v>0.3816100786347559</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.906323762952372</v>
+        <v>2.907036205173542</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.393274480633036</v>
+        <v>-4.390259896422358</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9178233827680955</v>
+        <v>0.9190292164523666</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4188063374909561</v>
+        <v>0.4199937411929071</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.926773401829631</v>
+        <v>2.927485844050802</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.21615815059787</v>
+        <v>-4.213143566387192</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9853989436274639</v>
+        <v>0.9866047773117348</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4188063374909561</v>
+        <v>0.4199937411929071</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.923502430674933</v>
+        <v>2.924214872896104</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.261250395431416</v>
+        <v>-4.258235811220738</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9680454374559586</v>
+        <v>0.9692512711402297</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3569102943215663</v>
+        <v>0.3580976980235173</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.887048196535213</v>
+        <v>2.887760638756383</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.081874974192648</v>
+        <v>-4.07886038998197</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.03358258125788</v>
+        <v>1.034788414942151</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.513687052492285</v>
+        <v>0.514874456194236</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.974901226744058</v>
+        <v>2.975613668965229</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.126889187713255</v>
+        <v>-4.123874603502576</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9963843511812271</v>
+        <v>0.9975901848654987</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4833381571776804</v>
+        <v>0.4845255608796314</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.937499344886885</v>
+        <v>2.938211787108056</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.142468521988684</v>
+        <v>-4.390879113775011</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9958441798100013</v>
+        <v>0.8964799430954704</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4367957629994946</v>
+        <v>0.2901625228366828</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.915265470718919</v>
+        <v>2.827285526621232</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.243666303425857</v>
+        <v>-4.492076895212183</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9545689891316336</v>
+        <v>0.8552047524171027</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3683869494541754</v>
+        <v>0.2217537092913636</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.873424104488229</v>
+        <v>2.785444160390542</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.237155336811544</v>
+        <v>-4.485565928597871</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9547733373316754</v>
+        <v>0.8554091006171445</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3683869494541754</v>
+        <v>0.2217537092913636</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.871024066042546</v>
+        <v>2.783044121944859</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.218117209104247</v>
+        <v>-4.466527800890574</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9589133076228391</v>
+        <v>0.8595490709083082</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3102033381229808</v>
+        <v>0.1635700979601691</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.832638618452074</v>
+        <v>2.744658674354387</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.270633011379068</v>
+        <v>-4.519043603165394</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.057201388347101</v>
+        <v>0.9578371516325705</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3102033381229808</v>
+        <v>0.1635700979601691</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.951933020086265</v>
+        <v>2.863953075988578</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.284499772712985</v>
+        <v>-4.532910364499312</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.052488012799668</v>
+        <v>0.9531237760851368</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2723454213891579</v>
+        <v>0.1257121812263461</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.930051599032104</v>
+        <v>2.842071654934417</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.239695601173056</v>
+        <v>-4.488106192959382</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.076418211812566</v>
+        <v>0.9770539750980347</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2723454213891579</v>
+        <v>0.1257121812263461</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.93606012942903</v>
+        <v>2.848080185331343</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.091952630938053</v>
+        <v>-4.340363222724379</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.033465621183766</v>
+        <v>0.9341013844692352</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4401527786240411</v>
+        <v>0.2935195384612293</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.934694765047159</v>
+        <v>2.846714820949472</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.175773852212751</v>
+        <v>-4.424184443999078</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.002730754205368</v>
+        <v>0.903366517490837</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4401527786240411</v>
+        <v>0.2935195384612293</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.93748838657864</v>
+        <v>2.849508442480953</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.169621146159967</v>
+        <v>-4.418031737946293</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.00585418501814</v>
+        <v>0.9064899483036091</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4463054846768253</v>
+        <v>0.2996722445140136</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.941842358601969</v>
+        <v>2.853862414504282</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.186430444310469</v>
+        <v>-4.434841036096795</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9982109424980494</v>
+        <v>0.8988467057835186</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4294961865263237</v>
+        <v>0.2828629463635119</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.930837256451779</v>
+        <v>2.842857312354091</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.86736263679842</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.124132445534347</v>
+        <v>-4.372543037320673</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.089465695805319</v>
+        <v>0.9901014590907882</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4747904508007658</v>
+        <v>0.328157210637954</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.024349368813265</v>
+        <v>2.936369424715578</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.922342247869189</v>
+        <v>-4.170752839655515</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9724737765855094</v>
+        <v>0.8731095398709785</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6728086429699202</v>
+        <v>0.5261754028071084</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.945452285828885</v>
+        <v>2.857472341731198</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.973228960555383</v>
+        <v>-4.22163955234171</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.022409323833207</v>
+        <v>0.9230450871186759</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6219219302837256</v>
+        <v>0.4752886901209138</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.985210490539343</v>
+        <v>2.897230546441656</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.886618217905576</v>
+        <v>-4.135028809691903</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.071681357009173</v>
+        <v>0.9723171202946421</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7005476614888838</v>
+        <v>0.553914421326072</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.047013665378481</v>
+        <v>2.959033721280794</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.946827515910861</v>
+        <v>-4.195238107697188</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.046133618631731</v>
+        <v>0.9467693819171998</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6403383634835993</v>
+        <v>0.4937051233207875</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.009424067399983</v>
+        <v>2.921444123302296</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.870405469478934</v>
+        <v>-4.118816061265261</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.075194055244431</v>
+        <v>0.9758298185298993</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6403383634835993</v>
+        <v>0.4937051233207875</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.007915685439911</v>
+        <v>2.919935741342224</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.826032337840365</v>
+        <v>-4.074442929626692</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.092806175335294</v>
+        <v>0.9934419386207629</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6847114951221679</v>
+        <v>0.5380782549593561</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.034402431858489</v>
+        <v>2.946422487760802</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.84851268869925</v>
+        <v>-4.096923280485577</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.078207829130331</v>
+        <v>0.9788435924157994</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6847114951221679</v>
+        <v>0.5380782549593561</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.028796225997079</v>
+        <v>2.940816281899392</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.800856958138194</v>
+        <v>-4.049267549924521</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.103651878382558</v>
+        <v>1.004287641668026</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7323672256832235</v>
+        <v>0.5857339855204118</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.063771421361517</v>
+        <v>2.97579147726383</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.700338799639439</v>
+        <v>-3.948749391425767</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.148751515156784</v>
+        <v>1.049387278442253</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8328853841819781</v>
+        <v>0.6862521440191663</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.128974689835494</v>
+        <v>3.040994745737807</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.684433470207087</v>
+        <v>-3.932844061993414</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.141868319405598</v>
+        <v>1.042504082691066</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7537727234727392</v>
+        <v>0.6071394833099275</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.068261765885823</v>
+        <v>2.980281821788136</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.639595068598689</v>
+        <v>-3.888005660385016</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.163901382659585</v>
+        <v>1.064537145945054</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7583161564176086</v>
+        <v>0.611682916254797</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.075085528263374</v>
+        <v>2.987105584165687</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.659093524840697</v>
+        <v>-3.907504116627024</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.16026293979386</v>
+        <v>1.060898703079329</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7102315151377043</v>
+        <v>0.5635982749748927</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.050395683126509</v>
+        <v>2.962415739028822</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405955</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.614890687754797</v>
+        <v>-3.863301279541124</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.183823677156058</v>
+        <v>1.084459440441526</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7544343522236048</v>
+        <v>0.6078011120607931</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.082796987905887</v>
+        <v>2.9948170438082</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.622450353591844</v>
+        <v>-3.870860945378171</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.179209811290486</v>
+        <v>1.079845574575955</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8092377562334241</v>
+        <v>0.6626045160706124</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.114089030781026</v>
+        <v>3.026109086683339</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.464158936052571</v>
+        <v>-3.712569527838899</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.293774143489235</v>
+        <v>1.194409906774704</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8092377562334241</v>
+        <v>0.6626045160706124</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.165336795964065</v>
+        <v>3.077356851866378</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.256516932418095</v>
+        <v>-3.504927524204422</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.375271649537278</v>
+        <v>1.275907412822747</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.0168797598679</v>
+        <v>0.8702465197050886</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.288362702739004</v>
+        <v>3.200382758641317</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.205484839695567</v>
+        <v>-3.453895431481894</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.39063271486456</v>
+        <v>1.291268478150028</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.067911852590428</v>
+        <v>0.9212786124276166</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.313930186610791</v>
+        <v>3.225950242513104</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.140260658568361</v>
+        <v>-3.388671250354689</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.433909791408147</v>
+        <v>1.334545554693616</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.133136033717634</v>
+        <v>0.9865027935548222</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.370252099379819</v>
+        <v>3.282272155282132</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.102833638497227</v>
+        <v>-3.351244230283555</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.444841571735881</v>
+        <v>1.34547733502135</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.138387571746815</v>
+        <v>0.9917543315840038</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.369363994496609</v>
+        <v>3.281384050398922</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.122945294531936</v>
+        <v>-3.371355886318263</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.438053701653238</v>
+        <v>1.338689464938706</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.149414916744235</v>
+        <v>1.002781676581423</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.3772371938263</v>
+        <v>3.289257249728613</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.094532031432052</v>
+        <v>-3.342942623218379</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.609976777914402</v>
+        <v>1.510612541199871</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.090439353997806</v>
+        <v>0.9438061138349942</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.502409627199654</v>
+        <v>3.414429683101967</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.01974977040704</v>
+        <v>-3.268160362193367</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.760002591542224</v>
+        <v>1.660638354827693</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.165221615022819</v>
+        <v>1.018588374860007</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.667391893032478</v>
+        <v>3.579411948934792</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.993665686143232</v>
+        <v>-3.242076277929559</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.762144201261606</v>
+        <v>1.662779964547075</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.165221615022819</v>
+        <v>1.018588374860007</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.659099869046337</v>
+        <v>3.57111992494865</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.905787773034111</v>
+        <v>-3.154198364820438</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.795488562089034</v>
+        <v>1.696124325374503</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.28114725744617</v>
+        <v>1.134514017283358</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.726848450084128</v>
+        <v>3.638868505986441</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.896895311640828</v>
+        <v>-3.145305903427155</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.816599952373139</v>
+        <v>1.717235715658608</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.28114725744617</v>
+        <v>1.134514017283358</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.744402855810919</v>
+        <v>3.656422911713232</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.065371428610705</v>
+        <v>-3.313782020397033</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.741064552989772</v>
+        <v>1.64170031627524</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.253199421729589</v>
+        <v>1.106566181566777</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.719489201785555</v>
+        <v>3.631509257687868</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.619115235981265</v>
+        <v>-2.867525827767593</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.90083672722941</v>
+        <v>1.801472490514878</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.158480752059956</v>
+        <v>1.011847511897145</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.643927697171637</v>
+        <v>3.55594775307395</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.596394132298113</v>
+        <v>-2.84480472408444</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.900589191199575</v>
+        <v>1.801224954485044</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.158480752059956</v>
+        <v>1.011847511897145</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.634591719668541</v>
+        <v>3.546611775570855</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.725595945592155</v>
+        <v>-2.974006537378483</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.007814591733127</v>
+        <v>1.908450355018596</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.029278938765914</v>
+        <v>0.8826456986031024</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.715976757543285</v>
+        <v>3.627996813445598</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.751470344066181</v>
+        <v>-2.999880935852508</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.034542654837163</v>
+        <v>1.935178418122632</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.074190547477655</v>
+        <v>0.9275573073148435</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.780001545263976</v>
+        <v>3.69202160116629</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.744415653851008</v>
+        <v>-2.992826245637335</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.034039886912778</v>
+        <v>1.934675650198247</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.081245237692829</v>
+        <v>0.9346119975300173</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.780909715382626</v>
+        <v>3.692929771284939</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.71746442952452</v>
+        <v>-2.965875021310847</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.054826530288115</v>
+        <v>1.955462293573583</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.096125583720548</v>
+        <v>0.9494923435577365</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.799844076643999</v>
+        <v>3.711864132546312</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.853417437580836</v>
+        <v>-3.101828029367163</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.184548459210548</v>
+        <v>2.085184222496017</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.096125583720548</v>
+        <v>0.9494923435577365</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.983947208788958</v>
+        <v>3.895967264691272</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.875825555385708</v>
+        <v>-3.124236147172035</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.167701906991592</v>
+        <v>2.068337670277061</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.096125583720548</v>
+        <v>0.9494923435577365</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.976063903691951</v>
+        <v>3.888083959594265</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.904049790963308</v>
+        <v>-3.152460382749636</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.15846621231019</v>
+        <v>2.059101975595658</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.114102336171856</v>
+        <v>0.9674690960090451</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.988903954712375</v>
+        <v>3.900924010614687</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.913490716851838</v>
+        <v>-3.161901308638166</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.210943559676624</v>
+        <v>2.111579322962093</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.236529453715248</v>
+        <v>1.089896213552437</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.118613942960256</v>
+        <v>4.030633998862569</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.96576432418748</v>
+        <v>-3.214174915973807</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.192925211287669</v>
+        <v>2.093560974573138</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.184255846379607</v>
+        <v>1.037622606216795</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.090140873104172</v>
+        <v>4.002160929006486</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.042094301788385</v>
+        <v>-3.290504893574713</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.160505033141082</v>
+        <v>2.06114079642655</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.184255846379607</v>
+        <v>1.037622606216795</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.088252685997947</v>
+        <v>4.000272741900261</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.244348022112739</v>
+        <v>-3.492758613899066</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.074423774614203</v>
+        <v>1.975059537899671</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9820021260552532</v>
+        <v>0.8353688858924417</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.961720683406198</v>
+        <v>3.873740739308511</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.405916447639994</v>
+        <v>-3.654327039426321</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.008230414613453</v>
+        <v>1.908866177898922</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8552192022573738</v>
+        <v>0.7085859620945624</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.884084939337622</v>
+        <v>3.796104995239935</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.514217109510113</v>
+        <v>-3.762627701296441</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.977983556731324</v>
+        <v>1.878619320016793</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8552192022573738</v>
+        <v>0.7085859620945624</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.897158346203541</v>
+        <v>3.809178402105854</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.60736458081348</v>
+        <v>-3.855775172599807</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.932729764992917</v>
+        <v>1.833365528278386</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.732389990974841</v>
+        <v>0.5857567508120296</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.815466016216961</v>
+        <v>3.727486072119274</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.635265367922953</v>
+        <v>-3.88367595970928</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.92009349127613</v>
+        <v>1.820729254561599</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6977930668319062</v>
+        <v>0.5511598266690948</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.793231902858202</v>
+        <v>3.705251958760515</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.757791470625847</v>
+        <v>-4.006202062412174</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.867847494172171</v>
+        <v>1.76848325745764</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5752669641290123</v>
+        <v>0.4286337239662009</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.716480685213665</v>
+        <v>3.628500741115978</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.988305966811436</v>
+        <v>-4.236716558597763</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.842347655288439</v>
+        <v>1.742983418573908</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3447524679434236</v>
+        <v>0.1981192277806122</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.644877947092815</v>
+        <v>3.556898002995128</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.337051052035879</v>
+        <v>-4.585461643822207</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.843161340200509</v>
+        <v>1.743797103485978</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2360045140245258</v>
+        <v>0.0893712738617144</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.719940893743324</v>
+        <v>3.631960949645637</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.49103746981202</v>
+        <v>-4.739448061598347</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.850547042235693</v>
+        <v>1.751182805521161</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2360045140245258</v>
+        <v>0.0893712738617144</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.788921162888963</v>
+        <v>3.700941218791277</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.440515565984354</v>
+        <v>-4.688926157770681</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.85680700588688</v>
+        <v>1.757442769172349</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2360045140245258</v>
+        <v>0.0893712738617144</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.774972365009084</v>
+        <v>3.686992420911398</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.692990719992078</v>
+        <v>-4.941401311778406</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.767687433339204</v>
+        <v>1.668323196624673</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2360045140245258</v>
+        <v>0.0893712738617144</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.786842854064498</v>
+        <v>3.698862909966812</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.985886476471491</v>
+        <v>-5.234297068257818</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.651739665266383</v>
+        <v>1.552375428551852</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2360045140245258</v>
+        <v>0.0893712738617144</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.788053388583442</v>
+        <v>3.700073444485755</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.172550604606299</v>
+        <v>-5.420961196392626</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.581195756239781</v>
+        <v>1.48183151952525</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2092655431999659</v>
+        <v>0.0626323030371545</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.776131748316028</v>
+        <v>3.688151804218341</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.318571291520261</v>
+        <v>-5.566981883306588</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.517865334210386</v>
+        <v>1.418501097495855</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.200182451406109</v>
+        <v>0.05354921124329753</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.765759745975903</v>
+        <v>3.677779801878216</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.410285300629846</v>
+        <v>-5.658695892416174</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.643383787265595</v>
+        <v>1.544019550551064</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.200182451406109</v>
+        <v>0.05354921124329753</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.927963802674947</v>
+        <v>3.83998385857726</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.441936959689816</v>
+        <v>-5.690347551476143</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.625569761605422</v>
+        <v>1.526205524890891</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1950139941616688</v>
+        <v>0.04838075399885733</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.919709366292097</v>
+        <v>3.83172942219441</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.523871777958699</v>
+        <v>-5.772282369745026</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.60302525186636</v>
+        <v>1.503661015151828</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1850792485745886</v>
+        <v>0.03844600841177714</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.92397793650834</v>
+        <v>3.835997992410653</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.625847900207106</v>
+        <v>-5.874258491993434</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.571160441422899</v>
+        <v>1.471796204708368</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.083103126326181</v>
+        <v>-0.06353011383663043</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.871717901615198</v>
+        <v>3.783737957517511</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.515841616729885</v>
+        <v>-5.764252208516212</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.607315842057963</v>
+        <v>1.507951605343432</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1063076982434562</v>
+        <v>-0.04032554191935522</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.877793532009739</v>
+        <v>3.789813587912052</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.372782040988959</v>
+        <v>-5.621192632775286</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.668789683076308</v>
+        <v>1.569425446361777</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1143211248334355</v>
+        <v>-0.03231211532937595</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.8868515986857</v>
+        <v>3.798871654588014</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.071335315517121</v>
+        <v>-5.319745907303449</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.796629256147579</v>
+        <v>1.697265019433048</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4157678503052727</v>
+        <v>0.2691346101424613</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.074980516851339</v>
+        <v>3.987000572753652</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.095925559752305</v>
+        <v>-5.344336151538633</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.787764336206216</v>
+        <v>1.688400099491685</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4157678503052727</v>
+        <v>0.2691346101424613</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.07595169460405</v>
+        <v>3.987971750506363</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.044887183745785</v>
+        <v>-5.293297775532112</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.80902259098858</v>
+        <v>1.709658354274048</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4157678503052727</v>
+        <v>0.2691346101424613</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.076794598983805</v>
+        <v>3.988814654886118</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.003747888879154</v>
+        <v>-5.252158480665481</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.844516407809377</v>
+        <v>1.745152171094846</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4569071451719036</v>
+        <v>0.3102739050090921</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.120516274777929</v>
+        <v>4.032536330680242</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.907112976860514</v>
+        <v>-5.155523568646841</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.699354368740768</v>
+        <v>1.599990132026237</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5535420571905435</v>
+        <v>0.4069088170277321</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.994681218113048</v>
+        <v>3.906701274015361</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.037693711391356</v>
+        <v>-5.286104303177684</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.650624119002395</v>
+        <v>1.551259882287864</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.422961322659701</v>
+        <v>0.2763280824968896</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.919834821468505</v>
+        <v>3.831854877370819</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.873197377200395</v>
+        <v>-5.121607968986722</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.700849471754863</v>
+        <v>1.601485235040331</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5874576568506629</v>
+        <v>0.4408244166878514</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.002959441059166</v>
+        <v>3.914979496961479</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.900567309884827</v>
+        <v>-5.148977901671154</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.689089209117519</v>
+        <v>1.589724972402988</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5874576568506629</v>
+        <v>0.4408244166878514</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.002147151495596</v>
+        <v>3.914167207397909</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.910952504774716</v>
+        <v>-5.159363096561044</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.694803910286636</v>
+        <v>1.595439673572105</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5770724619607736</v>
+        <v>0.4304392217979621</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.005784813686734</v>
+        <v>3.917804869589047</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.929540663496941</v>
+        <v>-5.177951255283268</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.758205652574171</v>
+        <v>1.65884141585964</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5584843032385483</v>
+        <v>0.4118510630757368</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.065468924229824</v>
+        <v>3.977488980132137</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496549</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.929839210192977</v>
+        <v>-5.178249801979304</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.754955244714055</v>
+        <v>1.655591007999524</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5581857565425123</v>
+        <v>0.4115525163797009</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.062158807030501</v>
+        <v>3.974178862932814</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.829016076502549</v>
+        <v>-5.077426668288877</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.799815393129618</v>
+        <v>1.700451156415086</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5706499720268662</v>
+        <v>0.4240167318640547</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.074168231260505</v>
+        <v>3.986188287162818</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.638234715750142</v>
+        <v>-4.88664530753647</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.876257190909124</v>
+        <v>1.776892954194593</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7614313327792736</v>
+        <v>0.614798092616462</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.188766301190492</v>
+        <v>4.100786357092805</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.619717861708322</v>
+        <v>-4.868128453494649</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.863500778263449</v>
+        <v>1.764136541548917</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7743614622044818</v>
+        <v>0.6277282220416702</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.176361224583214</v>
+        <v>4.088381280485527</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.78576168591298</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.56438727380656</v>
+        <v>-4.812797865592887</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.920599950036212</v>
+        <v>1.821235713321681</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8296920501062439</v>
+        <v>0.6830588099434324</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.24452651393633</v>
+        <v>4.156546569838643</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539889</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.552333146893597</v>
+        <v>-4.800743738679924</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.919108168702835</v>
+        <v>1.819743931988304</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8417461770192067</v>
+        <v>0.6951129368563952</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.245445557985545</v>
+        <v>4.157465613887858</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.593488266461818</v>
+        <v>-4.841898858248145</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.904526751059682</v>
+        <v>1.805162514345151</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8005910574509858</v>
+        <v>0.6539578172881743</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.222633116428749</v>
+        <v>4.134653172331062</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382914</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.490607676933225</v>
+        <v>-4.739018268719552</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.958530012749002</v>
+        <v>1.859165776034471</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9034716469795787</v>
+        <v>0.7568384068167672</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.297212496023787</v>
+        <v>4.2092325519261</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.64685760776031</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.722208070102726</v>
+        <v>-4.970618661889053</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.886092525654796</v>
+        <v>1.786728288940265</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9034716469795787</v>
+        <v>0.7568384068167672</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.317415166197381</v>
+        <v>4.229435222099694</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.740280578394337</v>
+        <v>-4.988691170180664</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.878863522338151</v>
+        <v>1.77949928562362</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9034716469795787</v>
+        <v>0.7568384068167672</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.317415166197381</v>
+        <v>4.229435222099694</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.915387410970782</v>
+        <v>-5.163798002757109</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.76907270290104</v>
+        <v>1.669708466186509</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9034716469795787</v>
+        <v>0.7568384068167672</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.277667079790848</v>
+        <v>4.189687135693161</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943582</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.884101390430327</v>
+        <v>-5.132511982216654</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.788609730114162</v>
+        <v>1.689245493399631</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9347576675200341</v>
+        <v>0.7881244273572225</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.303461311112061</v>
+        <v>4.215481367014374</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677819</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.731075998317042</v>
+        <v>-4.979486590103369</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.94899088653238</v>
+        <v>1.849626649817849</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.087783059633318</v>
+        <v>0.9411498194705067</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.494447545952935</v>
+        <v>4.406467601855248</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.759383312190312</v>
+        <v>-5.00779390397664</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.125134185891365</v>
+        <v>2.025769949176833</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.087783059633318</v>
+        <v>0.9411498194705067</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.681913770861228</v>
+        <v>4.593933826763541</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903165</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.925976537303835</v>
+        <v>-5.174387129090162</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.027899847200038</v>
+        <v>1.928535610485506</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9211898345197957</v>
+        <v>0.7745565943569843</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.551360787147196</v>
+        <v>4.46338084304951</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568378</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.752912157921535</v>
+        <v>-5.001322749707862</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.100802001614675</v>
+        <v>2.001437764900144</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9211898345197957</v>
+        <v>0.7745565943569843</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.555037189808914</v>
+        <v>4.467057245711228</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.723666177465838</v>
+        <v>-4.972076769252165</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.110118448920449</v>
+        <v>2.010754212205918</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9211898345197957</v>
+        <v>0.7745565943569843</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.552655244932409</v>
+        <v>4.464675300834722</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.830591725343689</v>
+        <v>-5.079002317130016</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.064641468926944</v>
+        <v>1.965277232212413</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8142642866419444</v>
+        <v>0.667631046479133</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.485793155363334</v>
+        <v>4.397813211265647</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.975610283850938</v>
+        <v>-5.224020875637265</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.008062847667278</v>
+        <v>1.908698610952747</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6692457281346958</v>
+        <v>0.5226124879718844</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.400210822402219</v>
+        <v>4.312230878304532</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.093952049635655</v>
+        <v>-5.233587744070452</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.060657380611145</v>
+        <v>2.004803102837225</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6799317666975859</v>
+        <v>0.5746011018025645</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.506553684797706</v>
+        <v>4.443355285860693</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073533</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.145362471956363</v>
+        <v>-5.28499816639116</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.0378789088088</v>
+        <v>1.982024631034881</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6799317666975859</v>
+        <v>0.5746011018025645</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.504339381923645</v>
+        <v>4.441140982986632</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.70477813472006</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.224781923164115</v>
+        <v>-5.364417617598912</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.006014256399989</v>
+        <v>1.95015997862607</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6799317666975859</v>
+        <v>0.5746011018025645</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.504242509997934</v>
+        <v>4.441044111060921</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.320244921081333</v>
+        <v>-5.45988061551613</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.967822950791145</v>
+        <v>1.911968673017226</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6799317666975859</v>
+        <v>0.5746011018025645</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.504236403555978</v>
+        <v>4.441038004618965</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.360264919125116</v>
+        <v>-5.499900613559913</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.949911348136243</v>
+        <v>1.894057070362324</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6399117686538021</v>
+        <v>0.5345811037587807</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.478320801292318</v>
+        <v>4.415122402355305</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636265</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.41563408125731</v>
+        <v>-5.555269775692107</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.933497501031092</v>
+        <v>1.877643223257173</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6399117686538021</v>
+        <v>0.5345811037587807</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.484054619040045</v>
+        <v>4.420856220103031</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396008</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.461071861088137</v>
+        <v>-5.600707555522934</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.914860752441694</v>
+        <v>1.859006474667775</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5970667779756424</v>
+        <v>0.491736113080621</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.457885987976081</v>
+        <v>4.394687589039068</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396417</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.377846404240473</v>
+        <v>-5.51748209867527</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.968025328031079</v>
+        <v>1.91217105025716</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5970667779756424</v>
+        <v>0.491736113080621</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.477760380826401</v>
+        <v>4.414561981889388</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.79450702929917</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.201556179635165</v>
+        <v>-5.341191874069962</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.02224211839793</v>
+        <v>1.96638784062401</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5970667779756424</v>
+        <v>0.491736113080621</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.461461081351128</v>
+        <v>4.398262682414115</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590402</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.01834451650207</v>
+        <v>-5.157980210936867</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.097957733115213</v>
+        <v>2.042103455341294</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5970667779756424</v>
+        <v>0.491736113080621</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.463892030815174</v>
+        <v>4.400693631878161</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146281</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.946623069488219</v>
+        <v>-5.086258763923016</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.092437497768643</v>
+        <v>2.036583219994724</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6687882249894931</v>
+        <v>0.5634575600944717</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.472716084871374</v>
+        <v>4.409517685934361</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676844</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.076001852127997</v>
+        <v>-5.215637546562794</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.987601730633903</v>
+        <v>1.931747452859984</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6266864522822897</v>
+        <v>0.5213557873872683</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.394370767168224</v>
+        <v>4.33117236823121</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739459</v>
+        <v>3.715627631739457</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.109018148038742</v>
+        <v>-5.248653842473539</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.159593417154961</v>
+        <v>2.103739139381042</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5572490756155382</v>
+        <v>0.4519184107205167</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.537906546053528</v>
+        <v>4.474708147116515</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.559664546163284</v>
+        <v>3.884797435958554</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.143657675023303</v>
+        <v>4.410563420766932</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.109018148038742</v>
+        <v>-5.248653842473539</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.159593417154961</v>
+        <v>2.103739139381042</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5572490756155382</v>
+        <v>0.4519184107205167</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.136721472009671</v>
+        <v>4.4036272177533</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>129.4%</t>
+          <t>168.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.5%</t>
+          <t>423.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.4%</t>
+          <t>-641.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.8%</t>
+          <t>-147.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>593.3%</t>
+          <t>590.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-264.2%</t>
+          <t>-308.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-178.8%</t>
+          <t>-133.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.572673044669742</v>
+        <v>-4.474967262479548</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.043293458852867</v>
+        <v>1.082375771728944</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3769032721991853</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.098861064354022</v>
+        <v>3.138697795892045</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.439805355606464</v>
+        <v>-4.34209957341627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.112334717280001</v>
+        <v>1.151417030156078</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3769032721991853</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.114755247155845</v>
+        <v>3.154591978693869</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.319632272241965</v>
+        <v>-4.221926490051771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.161549795066102</v>
+        <v>1.20063210794218</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4970763555636842</v>
+        <v>0.5634709081270561</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.188004941614846</v>
+        <v>3.22784167315287</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.184378910911988</v>
+        <v>-4.086673128721794</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.225739242159533</v>
+        <v>1.264821555035611</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6323297168936614</v>
+        <v>0.6987242694570333</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.279245060974273</v>
+        <v>3.319081792512296</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.244253738269681</v>
+        <v>-4.146547956079487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.187826802617882</v>
+        <v>1.22690911549396</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5724548895359692</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.229357655961083</v>
+        <v>3.269194387499106</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.124433507358844</v>
+        <v>-4.02672772516865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.251044064216425</v>
+        <v>1.290126377092503</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5724548895359692</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.244646825195292</v>
+        <v>3.284483556733315</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.12690321382065</v>
+        <v>-4.029197431630456</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.157700380954144</v>
+        <v>1.196782693830222</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5699851830741631</v>
+        <v>0.6363797356375349</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.15080920064065</v>
+        <v>3.190645932178673</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003597</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.19527340014466</v>
+        <v>-4.097567617954466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.049614167909842</v>
+        <v>1.088696480785919</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5792608821103781</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.07563648154768</v>
+        <v>3.115473213085703</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.307145679770811</v>
+        <v>-4.209439897580617</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9953019646912726</v>
+        <v>1.03438427756735</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5792608821103781</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.066073190179571</v>
+        <v>3.105909921717594</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.3626657556634</v>
+        <v>-4.264959973473206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.110124771026439</v>
+        <v>1.149207083902517</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5792608821103781</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.203104026871774</v>
+        <v>3.242940758409797</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.18719149587093</v>
+        <v>-4.089485713680737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.184881706935215</v>
+        <v>1.223964019811292</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5792608821103781</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.207671258863562</v>
+        <v>3.247507990401584</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.179267121286016</v>
+        <v>-4.081561339095823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.163793485530388</v>
+        <v>1.202875798406465</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5792608821103781</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.183413287624769</v>
+        <v>3.223250019162792</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.172988918716167</v>
+        <v>-4.075283136525974</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.094843079959777</v>
+        <v>1.133925392835854</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5855390846802271</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.115718522568128</v>
+        <v>3.155555254106151</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.113136299512444</v>
+        <v>-4.015430517322251</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.128956514073399</v>
+        <v>1.168038826949476</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5855390846802271</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.12589090900026</v>
+        <v>3.165727640538283</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.026892836486066</v>
+        <v>-3.929187054295873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.15840016985781</v>
+        <v>1.197482482733887</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5855390846802271</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.12083717957412</v>
+        <v>3.160673911112144</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.072199655885046</v>
+        <v>-3.974493873694853</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.132053217542744</v>
+        <v>1.171135530418821</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5447289216709963</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.088126857213108</v>
+        <v>3.127963588751131</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.101232760587347</v>
+        <v>-4.003526978397154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.120991848694925</v>
+        <v>1.160074161571002</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5447289216709963</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.088678730246209</v>
+        <v>3.128515461784232</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.008422279136488</v>
+        <v>-3.910716496946295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.087388733166634</v>
+        <v>1.126471046042711</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6375394031218556</v>
+        <v>0.7039339556852274</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.07363771100809</v>
+        <v>3.113474442546113</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.052811748465915</v>
+        <v>-3.955105966275723</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.071506421359464</v>
+        <v>1.110588734235541</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.593149933792428</v>
+        <v>0.6595444863557998</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.048877505335034</v>
+        <v>3.088714236873058</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.169353353571258</v>
+        <v>-4.071647571381066</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.01996548782905</v>
+        <v>1.059047800705127</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4766083286870852</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.974028250783552</v>
+        <v>3.013864982321575</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.20927744815383</v>
+        <v>-4.111571665963638</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.009487145826688</v>
+        <v>1.048569458702765</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4766083286870852</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.979519546614219</v>
+        <v>3.019356278152242</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.237057846055182</v>
+        <v>-4.13935206386499</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.009872188434686</v>
+        <v>1.048954501310763</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4488279307857321</v>
+        <v>0.5152224833491039</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.974348509641946</v>
+        <v>3.014185241179969</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.355438518785321</v>
+        <v>-4.257732736595129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8008756393432841</v>
+        <v>0.8399579522193612</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3816100786347559</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.772373518352014</v>
+        <v>2.812210249890037</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.464052597228652</v>
+        <v>-4.36634681503846</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8775796686851574</v>
+        <v>0.9166619815612345</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3816100786347559</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.892523179071219</v>
+        <v>2.932359910609243</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.428643558980509</v>
+        <v>-4.330937776790317</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9062563100867373</v>
+        <v>0.9453386229628147</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3816100786347559</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.907036205173542</v>
+        <v>2.946872936711566</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.390259896422358</v>
+        <v>-4.292554114232166</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9190292164523666</v>
+        <v>0.9581115293284437</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4199937411929071</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.927485844050802</v>
+        <v>2.967322575588825</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.213143566387192</v>
+        <v>-4.115437784197</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9866047773117348</v>
+        <v>1.025687090187812</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4199937411929071</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.924214872896104</v>
+        <v>2.964051604434127</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.258235811220738</v>
+        <v>-4.160530029030546</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9692512711402297</v>
+        <v>1.008333584016307</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3580976980235173</v>
+        <v>0.4244922505868891</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.887760638756383</v>
+        <v>2.927597370294406</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.07886038998197</v>
+        <v>-3.981154607791778</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.034788414942151</v>
+        <v>1.073870727818228</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.514874456194236</v>
+        <v>0.5812690087576078</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.975613668965229</v>
+        <v>3.015450400503252</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.123874603502576</v>
+        <v>-4.026168821312384</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9975901848654987</v>
+        <v>1.036672497741576</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4845255608796314</v>
+        <v>0.5509201134430032</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.938211787108056</v>
+        <v>2.978048518646079</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.390879113775011</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8964799430954704</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2901625228366828</v>
+        <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.827285526621232</v>
+        <v>2.867122258159255</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.492076895212183</v>
+        <v>-4.35271504825208</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8552047524171027</v>
+        <v>0.9109494912011447</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2217537092913636</v>
+        <v>0.3697944234406838</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.785444160390542</v>
+        <v>2.874268588880134</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.485565928597871</v>
+        <v>-4.346204081637767</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8554091006171445</v>
+        <v>0.9111538394011864</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2217537092913636</v>
+        <v>0.3697944234406838</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.783044121944859</v>
+        <v>2.871868550434451</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.466527800890574</v>
+        <v>-4.32716595393047</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8595490709083082</v>
+        <v>0.9152938096923502</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1635700979601691</v>
+        <v>0.3116108121094892</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.744658674354387</v>
+        <v>2.833483102843979</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.519043603165394</v>
+        <v>-4.37968175620529</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9578371516325705</v>
+        <v>1.013581890416612</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1635700979601691</v>
+        <v>0.3116108121094892</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.863953075988578</v>
+        <v>2.95277750447817</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.532910364499312</v>
+        <v>-4.393548517539208</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9531237760851368</v>
+        <v>1.008868514869179</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1257121812263461</v>
+        <v>0.2737528953756663</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.842071654934417</v>
+        <v>2.930896083424009</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.488106192959382</v>
+        <v>-4.348744345999278</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9770539750980347</v>
+        <v>1.032798713882077</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1257121812263461</v>
+        <v>0.2737528953756663</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.848080185331343</v>
+        <v>2.936904613820935</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.340363222724379</v>
+        <v>-4.201001375764275</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9341013844692352</v>
+        <v>0.9898461232532771</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2935195384612293</v>
+        <v>0.4415602526105494</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.846714820949472</v>
+        <v>2.935539249439064</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.424184443999078</v>
+        <v>-4.284822597038974</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.903366517490837</v>
+        <v>0.9591112562748787</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2935195384612293</v>
+        <v>0.4415602526105494</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.849508442480953</v>
+        <v>2.938332870970545</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.418031737946293</v>
+        <v>-4.27866989098619</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9064899483036091</v>
+        <v>0.9622346870876508</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2996722445140136</v>
+        <v>0.4477129586633337</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.853862414504282</v>
+        <v>2.942686842993874</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.434841036096795</v>
+        <v>-4.295479189136691</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8988467057835186</v>
+        <v>0.9545914445675603</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2828629463635119</v>
+        <v>0.4309036605128321</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.842857312354091</v>
+        <v>2.931681740843683</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679842</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.372543037320673</v>
+        <v>-4.233181190360569</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9901014590907882</v>
+        <v>1.04584619787483</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.328157210637954</v>
+        <v>0.4761979247872741</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.936369424715578</v>
+        <v>3.02519385320517</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.170752839655515</v>
+        <v>-4.031390992695411</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8731095398709785</v>
+        <v>0.9288542786550205</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5261754028071084</v>
+        <v>0.6742161169564285</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.857472341731198</v>
+        <v>2.94629677022079</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.22163955234171</v>
+        <v>-4.082277705381606</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9230450871186759</v>
+        <v>0.9787898259027177</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4752886901209138</v>
+        <v>0.623329404270234</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.897230546441656</v>
+        <v>2.986054974931248</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.135028809691903</v>
+        <v>-3.995666962731799</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9723171202946421</v>
+        <v>1.028061859078684</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.553914421326072</v>
+        <v>0.7019551354753922</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.959033721280794</v>
+        <v>3.047858149770386</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.195238107697188</v>
+        <v>-3.964861068408348</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9467693819171998</v>
+        <v>1.038920197632736</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4937051233207875</v>
+        <v>0.7327610297988432</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.921444123302296</v>
+        <v>3.064877667189129</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.118816061265261</v>
+        <v>-3.888439021976421</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9758298185298993</v>
+        <v>1.067980634245436</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4937051233207875</v>
+        <v>0.7327610297988432</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.919935741342224</v>
+        <v>3.063369285229057</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.074442929626692</v>
+        <v>-3.844065890337852</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9934419386207629</v>
+        <v>1.085592754336299</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5380782549593561</v>
+        <v>0.7771341614374118</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.946422487760802</v>
+        <v>3.089856031647635</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.096923280485577</v>
+        <v>-3.866546241196737</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9788435924157994</v>
+        <v>1.070994408131336</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5380782549593561</v>
+        <v>0.7771341614374118</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.940816281899392</v>
+        <v>3.084249825786225</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.049267549924521</v>
+        <v>-3.818890510635682</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.004287641668026</v>
+        <v>1.096438457383563</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5857339855204118</v>
+        <v>0.8247898919984674</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.97579147726383</v>
+        <v>3.119225021150664</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.948749391425767</v>
+        <v>-3.718372352136927</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.049387278442253</v>
+        <v>1.141538094157789</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6862521440191663</v>
+        <v>0.925308050497222</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.040994745737807</v>
+        <v>3.184428289624641</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.932844061993414</v>
+        <v>-3.702467022704575</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.042504082691066</v>
+        <v>1.134654898406602</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6071394833099275</v>
+        <v>0.846195389787983</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.980281821788136</v>
+        <v>3.12371536567497</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.888005660385016</v>
+        <v>-3.657628621096177</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.064537145945054</v>
+        <v>1.15668796166059</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.611682916254797</v>
+        <v>0.8507388227328525</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.987105584165687</v>
+        <v>3.13053912805252</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.907504116627024</v>
+        <v>-3.677127077338185</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.060898703079329</v>
+        <v>1.153049518794865</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5635982749748927</v>
+        <v>0.8026541814529482</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.962415739028822</v>
+        <v>3.105849282915655</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405955</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.863301279541124</v>
+        <v>-3.632924240252284</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.084459440441526</v>
+        <v>1.176610256157062</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6078011120607931</v>
+        <v>0.8468570185388486</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.9948170438082</v>
+        <v>3.138250587695033</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265638</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.870860945378171</v>
+        <v>-3.640483906089331</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.079845574575955</v>
+        <v>1.171996390291491</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6626045160706124</v>
+        <v>0.901660422548668</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.026109086683339</v>
+        <v>3.169542630570172</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.712569527838899</v>
+        <v>-3.482192488550059</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.194409906774704</v>
+        <v>1.28656072249024</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6626045160706124</v>
+        <v>0.901660422548668</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.077356851866378</v>
+        <v>3.220790395753212</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.504927524204422</v>
+        <v>-3.274550484915583</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.275907412822747</v>
+        <v>1.368058228538283</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8702465197050886</v>
+        <v>1.109302426183144</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.200382758641317</v>
+        <v>3.34381630252815</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.453895431481894</v>
+        <v>-3.223518392193055</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.291268478150028</v>
+        <v>1.383419293865565</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9212786124276166</v>
+        <v>1.160334518905672</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.225950242513104</v>
+        <v>3.369383786399937</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.388671250354689</v>
+        <v>-3.158294211065849</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.334545554693616</v>
+        <v>1.426696370409152</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9865027935548222</v>
+        <v>1.225558700032878</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.282272155282132</v>
+        <v>3.425705699168966</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.351244230283555</v>
+        <v>-3.120867190994715</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.34547733502135</v>
+        <v>1.437628150736886</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9917543315840038</v>
+        <v>1.230810238062059</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.281384050398922</v>
+        <v>3.424817594285755</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.371355886318263</v>
+        <v>-3.140978847029424</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.338689464938706</v>
+        <v>1.430840280654243</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.002781676581423</v>
+        <v>1.241837583059479</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.289257249728613</v>
+        <v>3.432690793615447</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.342942623218379</v>
+        <v>-3.11256558392954</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.510612541199871</v>
+        <v>1.602763356915407</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9438061138349942</v>
+        <v>1.18286202031305</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.414429683101967</v>
+        <v>3.5578632269888</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.268160362193367</v>
+        <v>-3.037783322904527</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.660638354827693</v>
+        <v>1.752789170543229</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.018588374860007</v>
+        <v>1.257644281338062</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.579411948934792</v>
+        <v>3.722845492821625</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.242076277929559</v>
+        <v>-3.011699238640719</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.662779964547075</v>
+        <v>1.754930780262611</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.018588374860007</v>
+        <v>1.257644281338062</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.57111992494865</v>
+        <v>3.714553468835484</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.154198364820438</v>
+        <v>-2.923821325531599</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.696124325374503</v>
+        <v>1.788275141090039</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.134514017283358</v>
+        <v>1.373569923761413</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.638868505986441</v>
+        <v>3.782302049873274</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959852</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.145305903427155</v>
+        <v>-2.914928864138315</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.717235715658608</v>
+        <v>1.809386531374144</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.134514017283358</v>
+        <v>1.373569923761413</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.656422911713232</v>
+        <v>3.799856455600065</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.313782020397033</v>
+        <v>-3.083404981108193</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.64170031627524</v>
+        <v>1.733851131990777</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.106566181566777</v>
+        <v>1.345622088044833</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.631509257687868</v>
+        <v>3.774942801574701</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.867525827767593</v>
+        <v>-2.637148788478753</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.801472490514878</v>
+        <v>1.893623306230414</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.011847511897145</v>
+        <v>1.2509034183752</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.55594775307395</v>
+        <v>3.699381296960783</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.84480472408444</v>
+        <v>-2.614427684795601</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.801224954485044</v>
+        <v>1.89337577020058</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.011847511897145</v>
+        <v>1.2509034183752</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.546611775570855</v>
+        <v>3.690045319457687</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.974006537378483</v>
+        <v>-2.743629498089643</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.908450355018596</v>
+        <v>2.000601170734132</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8826456986031024</v>
+        <v>1.121701605081158</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.627996813445598</v>
+        <v>3.771430357332431</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.999880935852508</v>
+        <v>-2.769503896563669</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.935178418122632</v>
+        <v>2.027329233838168</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9275573073148435</v>
+        <v>1.166613213792899</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.69202160116629</v>
+        <v>3.835455145053122</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.992826245637335</v>
+        <v>-2.762449206348495</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.934675650198247</v>
+        <v>2.026826465913783</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9346119975300173</v>
+        <v>1.173667904008073</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.692929771284939</v>
+        <v>3.836363315171772</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.965875021310847</v>
+        <v>-2.735497982022007</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.955462293573583</v>
+        <v>2.04761310928912</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9494923435577365</v>
+        <v>1.188548250035792</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.711864132546312</v>
+        <v>3.855297676433145</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.101828029367163</v>
+        <v>-2.871450990078324</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.085184222496017</v>
+        <v>2.177335038211553</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9494923435577365</v>
+        <v>1.188548250035792</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.895967264691272</v>
+        <v>4.039400808578105</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.124236147172035</v>
+        <v>-2.893859107883196</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.068337670277061</v>
+        <v>2.160488485992597</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9494923435577365</v>
+        <v>1.188548250035792</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.888083959594265</v>
+        <v>4.031517503481098</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.152460382749636</v>
+        <v>-2.922083343460796</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.059101975595658</v>
+        <v>2.151252791311195</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9674690960090451</v>
+        <v>1.2065250024871</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.900924010614687</v>
+        <v>4.044357554501521</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.161901308638166</v>
+        <v>-2.931524269349326</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.111579322962093</v>
+        <v>2.20373013867763</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.089896213552437</v>
+        <v>1.328952120030492</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.030633998862569</v>
+        <v>4.174067542749403</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.214174915973807</v>
+        <v>-2.983797876684967</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.093560974573138</v>
+        <v>2.185711790288674</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.037622606216795</v>
+        <v>1.276678512694851</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.002160929006486</v>
+        <v>4.145594472893318</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.290504893574713</v>
+        <v>-3.060127854285873</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.06114079642655</v>
+        <v>2.153291612142087</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.037622606216795</v>
+        <v>1.276678512694851</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.000272741900261</v>
+        <v>4.143706285787093</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.492758613899066</v>
+        <v>-3.262381574610226</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.975059537899671</v>
+        <v>2.067210353615208</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8353688858924417</v>
+        <v>1.074424792370497</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.873740739308511</v>
+        <v>4.017174283195344</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.654327039426321</v>
+        <v>-3.423950000137482</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.908866177898922</v>
+        <v>2.001016993614458</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7085859620945624</v>
+        <v>0.9476418685726177</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.796104995239935</v>
+        <v>3.939538539126769</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.762627701296441</v>
+        <v>-3.532250662007601</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.878619320016793</v>
+        <v>1.970770135732329</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7085859620945624</v>
+        <v>0.9476418685726177</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.809178402105854</v>
+        <v>3.952611945992688</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.855775172599807</v>
+        <v>-3.625398133310968</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.833365528278386</v>
+        <v>1.925516343993922</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5857567508120296</v>
+        <v>0.8248126572900849</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.727486072119274</v>
+        <v>3.870919616006108</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.88367595970928</v>
+        <v>-3.653298920420441</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.820729254561599</v>
+        <v>1.912880070277135</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5511598266690948</v>
+        <v>0.7902157331471501</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.705251958760515</v>
+        <v>3.848685502647349</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.006202062412174</v>
+        <v>-3.775825023123335</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.76848325745764</v>
+        <v>1.860634073173176</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4286337239662009</v>
+        <v>0.6676896304442562</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.628500741115978</v>
+        <v>3.771934285002811</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.236716558597763</v>
+        <v>-4.006339519308924</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.742983418573908</v>
+        <v>1.835134234289444</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1981192277806122</v>
+        <v>0.4371751342586675</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.556898002995128</v>
+        <v>3.700331546881962</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814661</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.585461643822207</v>
+        <v>-4.355084604533367</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.743797103485978</v>
+        <v>1.835947919201514</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.0893712738617144</v>
+        <v>0.3284271803397697</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.631960949645637</v>
+        <v>3.77539449353247</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.739448061598347</v>
+        <v>-4.509071022309508</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.751182805521161</v>
+        <v>1.843333621236698</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.0893712738617144</v>
+        <v>0.3284271803397697</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.700941218791277</v>
+        <v>3.84437476267811</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.688926157770681</v>
+        <v>-4.458549118481842</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.757442769172349</v>
+        <v>1.849593584887885</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.0893712738617144</v>
+        <v>0.3284271803397697</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.686992420911398</v>
+        <v>3.830425964798231</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.941401311778406</v>
+        <v>-4.711024272489566</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.668323196624673</v>
+        <v>1.760474012340209</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.0893712738617144</v>
+        <v>0.3284271803397697</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.698862909966812</v>
+        <v>3.842296453853645</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.234297068257818</v>
+        <v>-5.003920028968978</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.552375428551852</v>
+        <v>1.644526244267388</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.0893712738617144</v>
+        <v>0.3284271803397697</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.700073444485755</v>
+        <v>3.843506988372588</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.420961196392626</v>
+        <v>-5.190584157103786</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.48183151952525</v>
+        <v>1.573982335240786</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.0626323030371545</v>
+        <v>0.3016882095152098</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.688151804218341</v>
+        <v>3.831585348105174</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.566981883306588</v>
+        <v>-5.336604844017748</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.418501097495855</v>
+        <v>1.510651913211391</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.05354921124329753</v>
+        <v>0.2926051177213528</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.677779801878216</v>
+        <v>3.821213345765049</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.658695892416174</v>
+        <v>-5.428318853127333</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.544019550551064</v>
+        <v>1.636170366266601</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.05354921124329753</v>
+        <v>0.2926051177213528</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.83998385857726</v>
+        <v>3.983417402464093</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.690347551476143</v>
+        <v>-5.459970512187303</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.526205524890891</v>
+        <v>1.618356340606427</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.04838075399885733</v>
+        <v>0.2874366604769126</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.83172942219441</v>
+        <v>3.975162966081244</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.772282369745026</v>
+        <v>-5.541905330456186</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.503661015151828</v>
+        <v>1.595811830867365</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.03844600841177714</v>
+        <v>0.2775019148898324</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.835997992410653</v>
+        <v>3.979431536297486</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.874258491993434</v>
+        <v>-5.643881452704593</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.471796204708368</v>
+        <v>1.563947020423905</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.06353011383663043</v>
+        <v>0.1755257926414249</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.783737957517511</v>
+        <v>3.927171501404344</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.764252208516212</v>
+        <v>-5.533875169227372</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.507951605343432</v>
+        <v>1.600102421058969</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.04032554191935522</v>
+        <v>0.1987303645587001</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.789813587912052</v>
+        <v>3.933247131798884</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.621192632775286</v>
+        <v>-5.390815593486446</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.569425446361777</v>
+        <v>1.661576262077313</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.03231211532937595</v>
+        <v>0.2067437911486794</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.798871654588014</v>
+        <v>3.942305198474847</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.319745907303449</v>
+        <v>-5.089368868014608</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.697265019433048</v>
+        <v>1.789415835148584</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2691346101424613</v>
+        <v>0.5081905166205166</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.987000572753652</v>
+        <v>4.130434116640485</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.344336151538633</v>
+        <v>-5.113959112249792</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.688400099491685</v>
+        <v>1.780550915207221</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2691346101424613</v>
+        <v>0.5081905166205166</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.987971750506363</v>
+        <v>4.131405294393196</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.293297775532112</v>
+        <v>-5.062920736243272</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.709658354274048</v>
+        <v>1.801809169989585</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2691346101424613</v>
+        <v>0.5081905166205166</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.988814654886118</v>
+        <v>4.132248198772952</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.252158480665481</v>
+        <v>-5.021781441376641</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.745152171094846</v>
+        <v>1.837302986810383</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3102739050090921</v>
+        <v>0.5493298114871474</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.032536330680242</v>
+        <v>4.175969874567075</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.155523568646841</v>
+        <v>-4.925146529358001</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.599990132026237</v>
+        <v>1.692140947741773</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4069088170277321</v>
+        <v>0.6459647235057874</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.906701274015361</v>
+        <v>4.050134817902194</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.286104303177684</v>
+        <v>-4.8465534941379</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.551259882287864</v>
+        <v>1.727080205903778</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2763280824968896</v>
+        <v>0.7245577587258875</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.831854877370819</v>
+        <v>4.100792683108218</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.121607968986722</v>
+        <v>-4.682057159946939</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.601485235040331</v>
+        <v>1.777305558656245</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4408244166878514</v>
+        <v>0.8890540929168493</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.914979496961479</v>
+        <v>4.183917302698878</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.148977901671154</v>
+        <v>-4.709427092631371</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.589724972402988</v>
+        <v>1.765545296018902</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4408244166878514</v>
+        <v>0.8890540929168493</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.914167207397909</v>
+        <v>4.183105013135307</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.159363096561044</v>
+        <v>-4.71981228752126</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.595439673572105</v>
+        <v>1.771259997188019</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4304392217979621</v>
+        <v>0.87866889802696</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.917804869589047</v>
+        <v>4.186742675326446</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.177951255283268</v>
+        <v>-4.738400446243485</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.65884141585964</v>
+        <v>1.834661739475554</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4118510630757368</v>
+        <v>0.8600807393047347</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.977488980132137</v>
+        <v>4.246426785869536</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496549</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.178249801979304</v>
+        <v>-4.738698992939521</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.655591007999524</v>
+        <v>1.831411331615438</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4115525163797009</v>
+        <v>0.8597821926086988</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.974178862932814</v>
+        <v>4.243116668670213</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.077426668288877</v>
+        <v>-4.637875859249093</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.700451156415086</v>
+        <v>1.876271480031</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4240167318640547</v>
+        <v>0.8722464080930526</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.986188287162818</v>
+        <v>4.255126092900217</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.88664530753647</v>
+        <v>-4.447094498496686</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.776892954194593</v>
+        <v>1.952713277810507</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.614798092616462</v>
+        <v>1.06302776884546</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.100786357092805</v>
+        <v>4.369724162830204</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.868128453494649</v>
+        <v>-4.428577644454865</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.764136541548917</v>
+        <v>1.939956865164831</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6277282220416702</v>
+        <v>1.075957898270668</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.088381280485527</v>
+        <v>4.357319086222926</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591298</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.812797865592887</v>
+        <v>-4.373247056553103</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.821235713321681</v>
+        <v>1.997056036937595</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6830588099434324</v>
+        <v>1.13128848617243</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.156546569838643</v>
+        <v>4.425484375576041</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539889</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.800743738679924</v>
+        <v>-4.36119292964014</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.819743931988304</v>
+        <v>1.995564255604218</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6951129368563952</v>
+        <v>1.143342613085393</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.157465613887858</v>
+        <v>4.426403419625257</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.841898858248145</v>
+        <v>-4.402348049208361</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.805162514345151</v>
+        <v>1.980982837961065</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6539578172881743</v>
+        <v>1.102187493517172</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.134653172331062</v>
+        <v>4.40359097806846</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382914</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.739018268719552</v>
+        <v>-4.299467459679768</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.859165776034471</v>
+        <v>2.034986099650385</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7568384068167672</v>
+        <v>1.205068083045765</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.2092325519261</v>
+        <v>4.478170357663498</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64685760776031</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.970618661889053</v>
+        <v>-4.531067852849269</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.786728288940265</v>
+        <v>1.962548612556179</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7568384068167672</v>
+        <v>1.205068083045765</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.229435222099694</v>
+        <v>4.498373027837093</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781704</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.988691170180664</v>
+        <v>-4.54914036114088</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.77949928562362</v>
+        <v>1.955319609239534</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7568384068167672</v>
+        <v>1.205068083045765</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.229435222099694</v>
+        <v>4.498373027837093</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082833</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.163798002757109</v>
+        <v>-4.724247193717325</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.669708466186509</v>
+        <v>1.845528789802423</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7568384068167672</v>
+        <v>1.205068083045765</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.189687135693161</v>
+        <v>4.45862494143056</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943582</v>
+        <v>3.745593333943584</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.132511982216654</v>
+        <v>-4.69296117317687</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.689245493399631</v>
+        <v>1.865065817015545</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7881244273572225</v>
+        <v>1.23635410358622</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.215481367014374</v>
+        <v>4.484419172751773</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677819</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.979486590103369</v>
+        <v>-4.539935781063585</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.849626649817849</v>
+        <v>2.025446973433763</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9411498194705067</v>
+        <v>1.389379495699504</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.406467601855248</v>
+        <v>4.675405407592647</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.00779390397664</v>
+        <v>-4.568243094936856</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.025769949176833</v>
+        <v>2.201590272792747</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9411498194705067</v>
+        <v>1.389379495699504</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.593933826763541</v>
+        <v>4.86287163250094</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.174387129090162</v>
+        <v>-4.734836320050378</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.928535610485506</v>
+        <v>2.10435593410142</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7745565943569843</v>
+        <v>1.222786270585982</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.46338084304951</v>
+        <v>4.732318648786908</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.001322749707862</v>
+        <v>-4.561771940668078</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.001437764900144</v>
+        <v>2.177258088516058</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7745565943569843</v>
+        <v>1.222786270585982</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.467057245711228</v>
+        <v>4.735995051448626</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.972076769252165</v>
+        <v>-4.532525960212381</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.010754212205918</v>
+        <v>2.186574535821832</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7745565943569843</v>
+        <v>1.222786270585982</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.464675300834722</v>
+        <v>4.733613106572121</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.079002317130016</v>
+        <v>-4.639451508090232</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.965277232212413</v>
+        <v>2.141097555828327</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.667631046479133</v>
+        <v>1.115860722708131</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.397813211265647</v>
+        <v>4.666751017003046</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.224020875637265</v>
+        <v>-4.784470066597481</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.908698610952747</v>
+        <v>2.084518934568662</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5226124879718844</v>
+        <v>0.9708421642008822</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.312230878304532</v>
+        <v>4.581168684041931</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.233587744070452</v>
+        <v>-4.781672807074926</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.004803102837225</v>
+        <v>2.185569077635436</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5746011018025645</v>
+        <v>1.025901233267297</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.443355285860693</v>
+        <v>4.714135364739533</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073533</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.28499816639116</v>
+        <v>-4.833083229395634</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.982024631034881</v>
+        <v>2.162790605833091</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5746011018025645</v>
+        <v>1.025901233267297</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.441140982986632</v>
+        <v>4.711921061865471</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70477813472006</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.364417617598912</v>
+        <v>-4.912502680603386</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.95015997862607</v>
+        <v>2.13092595342428</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5746011018025645</v>
+        <v>1.025901233267297</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.441044111060921</v>
+        <v>4.711824189939761</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.45988061551613</v>
+        <v>-5.007965678520604</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.911968673017226</v>
+        <v>2.092734647815437</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5746011018025645</v>
+        <v>1.025901233267297</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.441038004618965</v>
+        <v>4.711818083497804</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500729</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.499900613559913</v>
+        <v>-5.047985676564387</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.894057070362324</v>
+        <v>2.074823045160534</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5345811037587807</v>
+        <v>0.9858812352235133</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.415122402355305</v>
+        <v>4.685902481234145</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636265</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.555269775692107</v>
+        <v>-5.103354838696581</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.877643223257173</v>
+        <v>2.058409198055383</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5345811037587807</v>
+        <v>0.9858812352235133</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.420856220103031</v>
+        <v>4.691636298981871</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396008</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.600707555522934</v>
+        <v>-5.148792618527408</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.859006474667775</v>
+        <v>2.039772449465985</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.491736113080621</v>
+        <v>0.9430362445453537</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.394687589039068</v>
+        <v>4.665467667917908</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396417</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.51748209867527</v>
+        <v>-5.065567161679744</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.91217105025716</v>
+        <v>2.09293702505537</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.491736113080621</v>
+        <v>0.9430362445453537</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.414561981889388</v>
+        <v>4.685342060768227</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79450702929917</v>
+        <v>3.794507029299175</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.341191874069962</v>
+        <v>-4.889276937074436</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.96638784062401</v>
+        <v>2.147153815422221</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.491736113080621</v>
+        <v>0.9430362445453537</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.398262682414115</v>
+        <v>4.669042761292955</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590402</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.157980210936867</v>
+        <v>-4.706065273941341</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.042103455341294</v>
+        <v>2.222869430139505</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.491736113080621</v>
+        <v>0.9430362445453537</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.400693631878161</v>
+        <v>4.671473710757001</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146281</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.086258763923016</v>
+        <v>-4.63434382692749</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.036583219994724</v>
+        <v>2.217349194792934</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5634575600944717</v>
+        <v>1.014757691559204</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.409517685934361</v>
+        <v>4.680297764813201</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676844</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.215637546562794</v>
+        <v>-4.763722609567268</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.931747452859984</v>
+        <v>2.112513427658195</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5213557873872683</v>
+        <v>0.9726559188520012</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.33117236823121</v>
+        <v>4.60195244711005</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739457</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.248653842473539</v>
+        <v>-4.796738905478013</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.103739139381042</v>
+        <v>2.284505114179253</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4519184107205167</v>
+        <v>0.9032185421852497</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.474708147116515</v>
+        <v>4.745488225995355</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.884797435958554</v>
+        <v>3.95118780299766</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.410563420766932</v>
+        <v>4.805156069341006</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.248653842473539</v>
+        <v>-4.796738905478013</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.103739139381042</v>
+        <v>2.284505114179253</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.4519184107205167</v>
+        <v>0.9032185421852497</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.4036272177533</v>
+        <v>4.798219866327374</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>101.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>168.9%</t>
+          <t>136.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-37.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.8%</t>
+          <t>423.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-641.2%</t>
+          <t>-668.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.8%</t>
+          <t>-130.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.8%</t>
+          <t>592.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.0%</t>
+          <t>-295.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-133.7%</t>
+          <t>-150.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.35271504825208</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9109494912011447</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3697944234406838</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.874268588880134</v>
+        <v>2.825280891928565</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.346204081637767</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9111538394011864</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3697944234406838</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.871868550434451</v>
+        <v>2.822880853482882</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.32716595393047</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9152938096923502</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3116108121094892</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.833483102843979</v>
+        <v>2.78449540589241</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.37968175620529</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.013581890416612</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3116108121094892</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.95277750447817</v>
+        <v>2.9037898075266</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.393548517539208</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.008868514869179</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2737528953756663</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.930896083424009</v>
+        <v>2.88190838647244</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.348744345999278</v>
+        <v>-4.39040041076919</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.032798713882077</v>
+        <v>1.016136287974112</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2737528953756663</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.936904613820935</v>
+        <v>2.887916916869366</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.201001375764275</v>
+        <v>-4.242657440534187</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9898461232532771</v>
+        <v>0.9731836973453125</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4415602526105494</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.935539249439064</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.284822597038974</v>
+        <v>-4.326478661808886</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9591112562748787</v>
+        <v>0.9424488303669141</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4415602526105494</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.938332870970545</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.27866989098619</v>
+        <v>-4.320325955756101</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9622346870876508</v>
+        <v>0.9455722611796862</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4477129586633337</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.942686842993874</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.615198253765279</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.295479189136691</v>
+        <v>-4.337135253906603</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9545914445675603</v>
+        <v>0.8799877278888903</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4309036605128321</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.931681740843683</v>
+        <v>2.824752753121409</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.6815338075621</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.233181190360569</v>
+        <v>-4.274837255130481</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.04584619787483</v>
+        <v>0.9712424811961602</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4761979247872741</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.02519385320517</v>
+        <v>2.918264865482896</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.483825809276227</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.031390992695411</v>
+        <v>-4.073047057465323</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9288542786550205</v>
+        <v>0.8542505619763503</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6742161169564285</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.94629677022079</v>
+        <v>2.839367782498515</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.554116041598402</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.082277705381606</v>
+        <v>-4.123933770151518</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9787898259027177</v>
+        <v>0.9041861092240477</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.623329404270234</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.986054974931248</v>
+        <v>2.879125987208974</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.568743777714446</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.995666962731799</v>
+        <v>-4.037323027501711</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.028061859078684</v>
+        <v>0.9534581424000141</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7019551354753922</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.047858149770386</v>
+        <v>2.940929162048112</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.567279758539117</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.964861068408348</v>
+        <v>-4.097532325506996</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.038920197632736</v>
+        <v>0.9279104040225719</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7327610297988432</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.064877667189129</v>
+        <v>2.903339564069613</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.565771376579046</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.888439021976421</v>
+        <v>-4.021110279075069</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.067980634245436</v>
+        <v>0.956970840635271</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7327610297988432</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.063369285229057</v>
+        <v>2.901831182109542</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.565634244014482</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.844065890337852</v>
+        <v>-3.9767371474365</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.085592754336299</v>
+        <v>0.9745829607261347</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7771341614374118</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.089856031647635</v>
+        <v>2.928317928528119</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.560028038153073</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.866546241196737</v>
+        <v>-3.999217498295385</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.070994408131336</v>
+        <v>0.9599846145211712</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7771341614374118</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.084249825786225</v>
+        <v>2.92271172266671</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.566409795180877</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.818890510635682</v>
+        <v>-3.951561767734329</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.096438457383563</v>
+        <v>0.9854286637733978</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8247898919984674</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.119225021150664</v>
+        <v>2.957686918031147</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.571302168555602</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.718372352136927</v>
+        <v>-3.851043609235575</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.141538094157789</v>
+        <v>1.030528300547624</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.925308050497222</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.184428289624641</v>
+        <v>3.022890186505125</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.558056841031474</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.702467022704575</v>
+        <v>-3.835138279803222</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.134654898406602</v>
+        <v>1.023645104796438</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.846195389787983</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.12371536567497</v>
+        <v>2.962177262555454</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.562154543642102</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.657628621096177</v>
+        <v>-3.790299878194824</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.15668796166059</v>
+        <v>1.045678168050426</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8507388227328525</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.13053912805252</v>
+        <v>2.969001024933004</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.56631548327318</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.677127077338185</v>
+        <v>-3.809798334436832</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.153049518794865</v>
+        <v>1.0420397251847</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8026541814529482</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.105849282915655</v>
+        <v>2.94431117979614</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.572195085801018</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.632924240252284</v>
+        <v>-3.765595497350932</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.176610256157062</v>
+        <v>1.065600462546898</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8468570185388486</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.138250587695033</v>
+        <v>2.976712484575517</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.570605086270265</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.640483906089331</v>
+        <v>-3.773155163187979</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.171996390291491</v>
+        <v>1.060986596681326</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.901660422548668</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.169542630570172</v>
+        <v>3.008004527450656</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.621852851453305</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.482192488550059</v>
+        <v>-3.614863745648706</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.28656072249024</v>
+        <v>1.175550928880075</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.901660422548668</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.220790395753212</v>
+        <v>3.059252292633696</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.620293556047558</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.274550484915583</v>
+        <v>-3.40722174201423</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.368058228538283</v>
+        <v>1.257048434928119</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.109302426183144</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.34381630252815</v>
+        <v>3.182278199408635</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.615241784285828</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.223518392193055</v>
+        <v>-3.356189649291702</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.383419293865565</v>
+        <v>1.2724095002554</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.160334518905672</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.369383786399937</v>
+        <v>3.207845683280421</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.632429188378533</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.158294211065849</v>
+        <v>-3.290965468164496</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.426696370409152</v>
+        <v>1.315686576798987</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.225558700032878</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.425705699168966</v>
+        <v>3.264167596049449</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.628390160677813</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.120867190994715</v>
+        <v>-3.253538448093363</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.437628150736886</v>
+        <v>1.326618357126721</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.230810238062059</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.424817594285755</v>
+        <v>3.263279491166239</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.629646953009054</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.140978847029424</v>
+        <v>-3.273650104128071</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.430840280654243</v>
+        <v>1.319830487044078</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.241837583059479</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.432690793615447</v>
+        <v>3.27115269049593</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.790204724030264</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.11256558392954</v>
+        <v>-3.245236841028187</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.602763356915407</v>
+        <v>1.491753563305242</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.18286202031305</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.5578632269888</v>
+        <v>3.396325123869284</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>2.910317633248082</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.037783322904527</v>
+        <v>-3.170454580003175</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.752789170543229</v>
+        <v>1.641779376933064</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.257644281338062</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.722845492821625</v>
+        <v>3.561307389702109</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>2.902025609261941</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.011699238640719</v>
+        <v>-3.144370495739367</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.754930780262611</v>
+        <v>1.643920986652446</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.257644281338062</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.714553468835484</v>
+        <v>3.553015365715968</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>2.90021880484572</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.923821325531599</v>
+        <v>-3.056492582630246</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.788275141090039</v>
+        <v>1.677265347479874</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.373569923761413</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.782302049873274</v>
+        <v>3.620763946753758</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>2.917773210572511</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.914928864138315</v>
+        <v>-3.047600121236963</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.809386531374144</v>
+        <v>1.698376737763979</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.373569923761413</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.799856455600065</v>
+        <v>3.638318352480549</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>2.909628257977095</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.083404981108193</v>
+        <v>-3.216076238206841</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.733851131990777</v>
+        <v>1.622841338380612</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.345622088044833</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.774942801574701</v>
+        <v>3.613404698455185</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>2.890897955164957</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.637148788478753</v>
+        <v>-2.769820045577401</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.893623306230414</v>
+        <v>1.78261351262025</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.2509034183752</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.699381296960783</v>
+        <v>3.537843193841267</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>2.881561977661862</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.614427684795601</v>
+        <v>-2.747098941894248</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.89337577020058</v>
+        <v>1.782365976590415</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.2509034183752</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.690045319457687</v>
+        <v>3.528507216338172</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>3.040468103513031</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.743629498089643</v>
+        <v>-2.876300755188291</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.000601170734132</v>
+        <v>1.889591377123967</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.121701605081158</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.771430357332431</v>
+        <v>3.609892254212915</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>3.077545926006677</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.769503896563669</v>
+        <v>-2.902175153662316</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.027329233838168</v>
+        <v>1.916319440228003</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.166613213792899</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.835455145053122</v>
+        <v>3.673917041933606</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>3.074221281996222</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.762449206348495</v>
+        <v>-2.895120463447143</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.026826465913783</v>
+        <v>1.915816672303618</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.173667904008073</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.836363315171772</v>
+        <v>3.674825212052256</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>3.084227435640964</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.735497982022007</v>
+        <v>-2.868169239120655</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.04761310928912</v>
+        <v>1.936603315678955</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.188548250035792</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.855297676433145</v>
+        <v>3.693759573313629</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.268330567785924</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.871450990078324</v>
+        <v>-3.004122247176971</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.177335038211553</v>
+        <v>2.066325244601388</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.188548250035792</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.039400808578105</v>
+        <v>3.877862705458589</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.260447262688917</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.893859107883196</v>
+        <v>-3.026530364981843</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.160488485992597</v>
+        <v>2.049478692382432</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.188548250035792</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.031517503481098</v>
+        <v>3.869979400361582</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.262501262238554</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.922083343460796</v>
+        <v>-3.054754600559443</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.151252791311195</v>
+        <v>2.040242997701029</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.2065250024871</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.044357554501521</v>
+        <v>3.882819451382004</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.318754979960401</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.931524269349326</v>
+        <v>-3.064195526447973</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.20373013867763</v>
+        <v>2.092720345067465</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.328952120030492</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.174067542749403</v>
+        <v>4.012529439629887</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.321646074505702</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.983797876684967</v>
+        <v>-3.116469133783615</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.185711790288674</v>
+        <v>2.074701996678509</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.276678512694851</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.145594472893318</v>
+        <v>3.984056369773803</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.319757887399478</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.060127854285873</v>
+        <v>-3.192799111384521</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.153291612142087</v>
+        <v>2.042281818531922</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.276678512694851</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.143706285787093</v>
+        <v>3.982168182667578</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.31457811700234</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.262381574610226</v>
+        <v>-3.395052831708874</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.067210353615208</v>
+        <v>1.956200560005043</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.074424792370497</v>
+        <v>0.9017634384558131</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.017174283195344</v>
+        <v>3.855636180075828</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.313012127212492</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.423950000137482</v>
+        <v>-3.556621257236129</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.001016993614458</v>
+        <v>1.890007200004293</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9476418685726177</v>
+        <v>0.7749805146579337</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.939538539126769</v>
+        <v>3.778000436007253</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.326085534078411</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.532250662007601</v>
+        <v>-3.664921919106249</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.970770135732329</v>
+        <v>1.859760342122164</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9476418685726177</v>
+        <v>0.7749805146579337</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.952611945992688</v>
+        <v>3.791073842873171</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.318090730861351</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.625398133310968</v>
+        <v>-3.758069390409615</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.925516343993922</v>
+        <v>1.814506550383757</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8248126572900849</v>
+        <v>0.6521513033754009</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.870919616006108</v>
+        <v>3.709381512886591</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.316614771988353</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.653298920420441</v>
+        <v>-3.785970177519088</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.912880070277135</v>
+        <v>1.80187027666697</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7902157331471501</v>
+        <v>0.6175543792324661</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.848685502647349</v>
+        <v>3.687147399527833</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.313379215965552</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.775825023123335</v>
+        <v>-3.908496280221982</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.860634073173176</v>
+        <v>1.749624279563011</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6676896304442562</v>
+        <v>0.4950282765295723</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.771934285002811</v>
+        <v>3.610396181883295</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.380085175556055</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.006339519308924</v>
+        <v>-4.139010776407571</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.835134234289444</v>
+        <v>1.72412444067928</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4371751342586675</v>
+        <v>0.2645137803439835</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.700331546881962</v>
+        <v>3.538793443762446</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.520396894557902</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.355084604533367</v>
+        <v>-4.487755861632015</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.835947919201514</v>
+        <v>1.724938125591349</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3284271803397697</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.77539449353247</v>
+        <v>3.613856390412954</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.589377163703542</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.509071022309508</v>
+        <v>-4.641742279408155</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.843333621236698</v>
+        <v>1.732323827626533</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3284271803397697</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.84437476267811</v>
+        <v>3.682836659558594</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.575428365823663</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.458549118481842</v>
+        <v>-4.591220375580489</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.849593584887885</v>
+        <v>1.73858379127772</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3284271803397697</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.830425964798231</v>
+        <v>3.668887861678715</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.587298854879077</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.711024272489566</v>
+        <v>-4.843695529588214</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.760474012340209</v>
+        <v>1.649464218730044</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3284271803397697</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.842296453853645</v>
+        <v>3.680758350734129</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.588509389398021</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.003920028968978</v>
+        <v>-5.136591286067626</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.644526244267388</v>
+        <v>1.533516450657223</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3284271803397697</v>
+        <v>0.1557658264250857</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.843506988372588</v>
+        <v>3.681968885253073</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.592631131625342</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.190584157103786</v>
+        <v>-5.323255414202434</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.573982335240786</v>
+        <v>1.462972541630621</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3016882095152098</v>
+        <v>0.1290268556005258</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.831585348105174</v>
+        <v>3.670047244985658</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.587708984361532</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.336604844017748</v>
+        <v>-5.469276101116396</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.510651913211391</v>
+        <v>1.399642119601226</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2926051177213528</v>
+        <v>0.1199437638066689</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.821213345765049</v>
+        <v>3.659675242645533</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.749913041060576</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.428318853127333</v>
+        <v>-5.560990110225982</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.636170366266601</v>
+        <v>1.525160572656436</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2926051177213528</v>
+        <v>0.1199437638066689</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.983417402464093</v>
+        <v>3.821879299344577</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.74475967902439</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.459970512187303</v>
+        <v>-5.592641769285951</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.618356340606427</v>
+        <v>1.507346546996262</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2874366604769126</v>
+        <v>0.1147753065622287</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.975162966081244</v>
+        <v>3.813624862961727</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.754989096592881</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.541905330456186</v>
+        <v>-5.674576587554834</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.595811830867365</v>
+        <v>1.4848020372572</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2775019148898324</v>
+        <v>0.1048405609751485</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.979431536297486</v>
+        <v>3.81789343317797</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.763914735048783</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.643881452704593</v>
+        <v>-5.776552709803242</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.563947020423905</v>
+        <v>1.452937226813739</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1755257926414249</v>
+        <v>0.002864438726740914</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.927171501404344</v>
+        <v>3.765633398284828</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.756067622292959</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.533875169227372</v>
+        <v>-5.66654642632602</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.600102421058969</v>
+        <v>1.489092627448803</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1987303645587001</v>
+        <v>0.02606901064401612</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.933247131798884</v>
+        <v>3.771709028679369</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.760317633014933</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.390815593486446</v>
+        <v>-5.523486850585094</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.661576262077313</v>
+        <v>1.550566468467148</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2067437911486794</v>
+        <v>0.0340824372339954</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.942305198474847</v>
+        <v>3.780767095355331</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.767578515897469</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.089368868014608</v>
+        <v>-5.222040125113256</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.789415835148584</v>
+        <v>1.678406041538419</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5081905166205166</v>
+        <v>0.3355291627058327</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.130434116640485</v>
+        <v>3.968896013520969</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.76854969365018</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.113959112249792</v>
+        <v>-5.24663036934844</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.780550915207221</v>
+        <v>1.669541121597056</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5081905166205166</v>
+        <v>0.3355291627058327</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.131405294393196</v>
+        <v>3.969867191273679</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.769392598029935</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.062920736243272</v>
+        <v>-5.19559199334192</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.801809169989585</v>
+        <v>1.69079937637942</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5081905166205166</v>
+        <v>0.3355291627058327</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.132248198772952</v>
+        <v>3.970710095653435</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.788430696904081</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.021781441376641</v>
+        <v>-5.154452698475289</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.837302986810383</v>
+        <v>1.726293193200218</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5493298114871474</v>
+        <v>0.3766684575724635</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.175969874567075</v>
+        <v>4.014431771447559</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.604614693028015</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.925146529358001</v>
+        <v>-5.057817786456649</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.692140947741773</v>
+        <v>1.581131154131608</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6459647235057874</v>
+        <v>0.4733033695911034</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.050134817902194</v>
+        <v>3.888596714782678</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.608116737101979</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.8465534941379</v>
+        <v>-4.98054850538735</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.727080205903778</v>
+        <v>1.615540910633292</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7245577587258875</v>
+        <v>0.550572650660402</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.100792683108218</v>
+        <v>3.938460327498221</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.592543556178062</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.682057159946939</v>
+        <v>-4.816052171196389</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.777305558656245</v>
+        <v>1.665766263385759</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8890540929168493</v>
+        <v>0.7150689848513638</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.183917302698878</v>
+        <v>4.02158494708888</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.591731266614492</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.709427092631371</v>
+        <v>-4.843422103880821</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.765545296018902</v>
+        <v>1.654006000748416</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8890540929168493</v>
+        <v>0.7150689848513638</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.183105013135307</v>
+        <v>4.02077265752531</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.601600045739564</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.71981228752126</v>
+        <v>-4.85380729877071</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.771259997188019</v>
+        <v>1.659720701917533</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.87866889802696</v>
+        <v>0.7046837899614745</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.186742675326446</v>
+        <v>4.024410319716449</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.672437051515989</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.738400446243485</v>
+        <v>-4.872395457492935</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.834661739475554</v>
+        <v>1.723122444205068</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8600807393047347</v>
+        <v>0.6860956312392492</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.246426785869536</v>
+        <v>4.084094430259539</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496549</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.669306062334288</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.738698992939521</v>
+        <v>-4.872694004188971</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.831411331615438</v>
+        <v>1.719872036344952</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8597821926086988</v>
+        <v>0.6857970845432133</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.243116668670213</v>
+        <v>4.080784313060215</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.673836957273679</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.637875859249093</v>
+        <v>-4.771870870498543</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.876271480031</v>
+        <v>1.764732184760514</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8722464080930526</v>
+        <v>0.6982613000275671</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.255126092900217</v>
+        <v>4.092793737290219</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.673966210752222</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.447094498496686</v>
+        <v>-4.581089509746135</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.952713277810507</v>
+        <v>1.841173982540021</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.06302776884546</v>
+        <v>0.8890426607799745</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.369724162830204</v>
+        <v>4.207391807220207</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.653803056489819</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.428577644454865</v>
+        <v>-4.562572655704315</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.939956865164831</v>
+        <v>1.828417569894346</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.075957898270668</v>
+        <v>0.9019727902051827</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.357319086222926</v>
+        <v>4.194986730612928</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.78576168591298</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.688769993101877</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.373247056553103</v>
+        <v>-4.507242067802553</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.997056036937595</v>
+        <v>1.885516741667109</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.13128848617243</v>
+        <v>0.9573033781069449</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.425484375576041</v>
+        <v>4.263152019966045</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539889</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.682456561003315</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.36119292964014</v>
+        <v>-4.49518794088959</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.995564255604218</v>
+        <v>1.884024960333732</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.143342613085393</v>
+        <v>0.9693575050199077</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.426403419625257</v>
+        <v>4.26407106401526</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.684337191187451</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.402348049208361</v>
+        <v>-4.536343060457811</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.980982837961065</v>
+        <v>1.869443542690579</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.102187493517172</v>
+        <v>0.9282023854516868</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.40359097806846</v>
+        <v>4.241258622458464</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382914</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.697188217065333</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.299467459679768</v>
+        <v>-4.433462470929218</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.034986099650385</v>
+        <v>1.923446804379899</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.205068083045765</v>
+        <v>1.03108297498028</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.478170357663498</v>
+        <v>4.315838002053502</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.64685760776031</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.717390887238928</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.531067852849269</v>
+        <v>-4.665062864098719</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.962548612556179</v>
+        <v>1.851009317285693</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.205068083045765</v>
+        <v>1.03108297498028</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.498373027837093</v>
+        <v>4.336040672227096</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781704</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.775332178009633</v>
+        <v>3.717390887238928</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.54914036114088</v>
+        <v>-4.68313537239033</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.955319609239534</v>
+        <v>1.843780313969048</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.205068083045765</v>
+        <v>1.03108297498028</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.498373027837093</v>
+        <v>4.336040672227096</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082833</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.7355840916031</v>
+        <v>3.677642800832394</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.724247193717325</v>
+        <v>-4.858242204966775</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.845528789802423</v>
+        <v>1.733989494531937</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.205068083045765</v>
+        <v>1.03108297498028</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.45862494143056</v>
+        <v>4.296292585820562</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943584</v>
+        <v>3.745593333943582</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.74260671060004</v>
+        <v>3.684665419829334</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.69296117317687</v>
+        <v>-4.82695618442632</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.865065817015545</v>
+        <v>1.753526521745059</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.23635410358622</v>
+        <v>1.062368995520735</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.484419172751773</v>
+        <v>4.322086817141775</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677819</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.841777710172944</v>
+        <v>3.783836419402239</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.539935781063585</v>
+        <v>-4.673930792313035</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.025446973433763</v>
+        <v>1.913907678163278</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.389379495699504</v>
+        <v>1.215394387634019</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.675405407592647</v>
+        <v>4.513073051982651</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.029243935081237</v>
+        <v>3.971302644310531</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.568243094936856</v>
+        <v>-4.702238106186305</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.201590272792747</v>
+        <v>2.090050977522261</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.389379495699504</v>
+        <v>1.215394387634019</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.86287163250094</v>
+        <v>4.700539276890942</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.998646886435319</v>
+        <v>3.940705595664613</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.734836320050378</v>
+        <v>-4.868831331299828</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.10435593410142</v>
+        <v>1.992816638830935</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.222786270585982</v>
+        <v>1.048801162520496</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.732318648786908</v>
+        <v>4.569986293176911</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568378</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.002323289097037</v>
+        <v>3.944381998326331</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.561771940668078</v>
+        <v>-4.695766951917528</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.177258088516058</v>
+        <v>2.065718793245573</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.222786270585982</v>
+        <v>1.048801162520496</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.735995051448626</v>
+        <v>4.573662695838629</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.999941344220532</v>
+        <v>3.942000053449826</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.532525960212381</v>
+        <v>-4.666520971461831</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.186574535821832</v>
+        <v>2.075035240551347</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.222786270585982</v>
+        <v>1.048801162520496</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.733613106572121</v>
+        <v>4.571280750962124</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.997234583378167</v>
+        <v>3.939293292607461</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.639451508090232</v>
+        <v>-4.773446519339682</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.141097555828327</v>
+        <v>2.029558260557841</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.115860722708131</v>
+        <v>0.9418756146426451</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.666751017003046</v>
+        <v>4.504418661393048</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.998663385521401</v>
+        <v>3.940722094750695</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.784470066597481</v>
+        <v>-4.918465077846931</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.084518934568662</v>
+        <v>1.972979639298176</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9708421642008822</v>
+        <v>0.7968570561353966</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.581168684041931</v>
+        <v>4.418836328431934</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.098594624779154</v>
+        <v>4.040653334008448</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.781672807074926</v>
+        <v>-5.036806843631648</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.185569077635436</v>
+        <v>2.025574172242042</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.025901233267297</v>
+        <v>0.8075430946982867</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.714135364739533</v>
+        <v>4.52517919082742</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073534</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.096380321905093</v>
+        <v>4.038439031134387</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.833083229395634</v>
+        <v>-5.088217265952356</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.162790605833091</v>
+        <v>2.002795700439697</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.025901233267297</v>
+        <v>0.8075430946982867</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.711921061865471</v>
+        <v>4.522964887953359</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.096283449979382</v>
+        <v>4.038342159208677</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.912502680603386</v>
+        <v>-5.167636717160108</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.13092595342428</v>
+        <v>1.970931048030886</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.025901233267297</v>
+        <v>0.8075430946982867</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.711824189939761</v>
+        <v>4.522868016027648</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.096277343537426</v>
+        <v>4.03833605276672</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.007965678520604</v>
+        <v>-5.263099715077326</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.092734647815437</v>
+        <v>1.932739742422042</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.025901233267297</v>
+        <v>0.8075430946982867</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.711818083497804</v>
+        <v>4.522861909585692</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.094373740100036</v>
+        <v>4.036432449329331</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.047985676564387</v>
+        <v>-5.303119713121109</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.074823045160534</v>
+        <v>1.91482813976714</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9858812352235133</v>
+        <v>0.7675230966545028</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.685902481234145</v>
+        <v>4.496946307322032</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.100107557847763</v>
+        <v>4.042166267077057</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.103354838696581</v>
+        <v>-5.358488875253303</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.058409198055383</v>
+        <v>1.898414292661989</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9858812352235133</v>
+        <v>0.7675230966545028</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.691636298981871</v>
+        <v>4.502680125069759</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.099645921190696</v>
+        <v>4.041704630419989</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.148792618527408</v>
+        <v>-5.40392665508413</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.039772449465985</v>
+        <v>1.87977754407259</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9430362445453537</v>
+        <v>0.7246781059763432</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.665467667917908</v>
+        <v>4.476511494005796</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.119520314041015</v>
+        <v>4.061579023270308</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.065567161679744</v>
+        <v>-5.320701198236466</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.09293702505537</v>
+        <v>1.932942119661975</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9430362445453537</v>
+        <v>0.7246781059763432</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.685342060768227</v>
+        <v>4.496385886856115</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.794507029299172</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.103221014565743</v>
+        <v>4.045279723795036</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.889276937074436</v>
+        <v>-5.144410973631159</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.147153815422221</v>
+        <v>1.987158910028826</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9430362445453537</v>
+        <v>0.7246781059763432</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.669042761292955</v>
+        <v>4.480086587380843</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.105651964029788</v>
+        <v>4.047710673259082</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.706065273941341</v>
+        <v>-4.961199310498063</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.222869430139505</v>
+        <v>2.062874524746109</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9430362445453537</v>
+        <v>0.7246781059763432</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.671473710757001</v>
+        <v>4.482517536844888</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.071443149877678</v>
+        <v>4.013501859106971</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.63434382692749</v>
+        <v>-4.889477863484212</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.217349194792934</v>
+        <v>2.057354289399539</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.014757691559204</v>
+        <v>0.7963995529901938</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.680297764813201</v>
+        <v>4.491341590901087</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.018358895798849</v>
+        <v>3.960417605028143</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.763722609567268</v>
+        <v>-5.01885664612399</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.112513427658195</v>
+        <v>1.952518522264799</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9726559188520012</v>
+        <v>0.7542977802829904</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.60195244711005</v>
+        <v>4.412996273197937</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.71562763173946</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.203557100684205</v>
+        <v>4.145615809913498</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.796738905478013</v>
+        <v>-5.051872942034735</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.284505114179253</v>
+        <v>2.124510208785857</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9032185421852497</v>
+        <v>0.6848604036162389</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.745488225995355</v>
+        <v>4.556532052083242</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.95118780299766</v>
+        <v>3.834375656590533</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.805156069341006</v>
+        <v>4.47995353794344</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.796738905478013</v>
+        <v>-5.064411020296672</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.284505114179253</v>
+        <v>2.453832705511024</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.9032185421852497</v>
+        <v>0.7313099497988336</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.798219866327374</v>
+        <v>4.918739507822741</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240829.xlsx
+++ b/tame_output/ON/bt/strategyON_20240829.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.5%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,32 +834,32 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>136.4%</t>
+          <t>95.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.0%</t>
+          <t>-688.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-130.8%</t>
+          <t>-179.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>592.8%</t>
+          <t>590.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-295.0%</t>
+          <t>-299.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.9%</t>
+          <t>-170.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>101.7%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>-6.5%</t>
         </is>
       </c>
     </row>
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.615198253765279</v>
+        <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.337135253906603</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8799877278888903</v>
+        <v>0.9379290186595957</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.824752753121409</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.6815338075621</v>
+        <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.274837255130481</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9712424811961602</v>
+        <v>1.029183771966866</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.918264865482896</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.483825809276227</v>
+        <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.073047057465323</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8542505619763503</v>
+        <v>0.9121918527470556</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.839367782498515</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.554116041598402</v>
+        <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.123933770151518</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9041861092240477</v>
+        <v>0.9621273999947531</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.879125987208974</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.568743777714446</v>
+        <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.037323027501711</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9534581424000141</v>
+        <v>1.011399433170719</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.940929162048112</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.567279758539117</v>
+        <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.097532325506996</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9279104040225719</v>
+        <v>0.9858516947932772</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.903339564069613</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.565771376579046</v>
+        <v>2.501302379577145</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.021110279075069</v>
+        <v>-4.063741713780721</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.956970840635271</v>
+        <v>0.8754492697511091</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.901831182109542</v>
+        <v>2.83736218510764</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.565634244014482</v>
+        <v>2.501165247012581</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.9767371474365</v>
+        <v>-4.019368582142152</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9745829607261347</v>
+        <v>0.8930613898419728</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.928317928528119</v>
+        <v>2.863848931526218</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.560028038153073</v>
+        <v>2.495559041151171</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.999217498295385</v>
+        <v>-4.041848933001037</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9599846145211712</v>
+        <v>0.8784630436370093</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.92271172266671</v>
+        <v>2.858242725664808</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.566409795180877</v>
+        <v>2.501940798178976</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.951561767734329</v>
+        <v>-3.994193202439981</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9854286637733978</v>
+        <v>0.9039070928892359</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.957686918031147</v>
+        <v>2.893217921029246</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.571302168555602</v>
+        <v>2.5068331715537</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.851043609235575</v>
+        <v>-3.893675043941227</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.030528300547624</v>
+        <v>0.9490067296634626</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.022890186505125</v>
+        <v>2.958421189503224</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.558056841031474</v>
+        <v>2.493587844029573</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.835138279803222</v>
+        <v>-3.877769714508874</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.023645104796438</v>
+        <v>0.9421235339122758</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.962177262555454</v>
+        <v>2.897708265553553</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.562154543642102</v>
+        <v>2.497685546640201</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.790299878194824</v>
+        <v>-3.832931312900476</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.045678168050426</v>
+        <v>0.9641565971662636</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.969001024933004</v>
+        <v>2.904532027931103</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.56631548327318</v>
+        <v>2.501846486271279</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.809798334436832</v>
+        <v>-3.852429769142484</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.0420397251847</v>
+        <v>0.9605181543005383</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.94431117979614</v>
+        <v>2.879842182794238</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.572195085801018</v>
+        <v>2.507726088799116</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.765595497350932</v>
+        <v>-3.808226932056584</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.065600462546898</v>
+        <v>0.9840788916627357</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.976712484575517</v>
+        <v>2.912243487573615</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.570605086270265</v>
+        <v>2.506136089268364</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.773155163187979</v>
+        <v>-3.815786597893631</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.060986596681326</v>
+        <v>0.9794650257971644</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.008004527450656</v>
+        <v>2.943535530448755</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.621852851453305</v>
+        <v>2.557383854451404</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.614863745648706</v>
+        <v>-3.657495180354358</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.175550928880075</v>
+        <v>1.094029357995913</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.059252292633696</v>
+        <v>2.994783295631795</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.620293556047558</v>
+        <v>2.555824559045657</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.40722174201423</v>
+        <v>-3.449853176719882</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.257048434928119</v>
+        <v>1.175526864043956</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.182278199408635</v>
+        <v>3.117809202406733</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.615241784285828</v>
+        <v>2.550772787283927</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.356189649291702</v>
+        <v>-3.398821083997354</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.2724095002554</v>
+        <v>1.190887929371238</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.207845683280421</v>
+        <v>3.14337668627852</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.632429188378533</v>
+        <v>2.567960191376632</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.290965468164496</v>
+        <v>-3.333596902870148</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.315686576798987</v>
+        <v>1.234165005914825</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.264167596049449</v>
+        <v>3.199698599047548</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.628390160677813</v>
+        <v>2.563921163675912</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.253538448093363</v>
+        <v>-3.296169882799015</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.326618357126721</v>
+        <v>1.245096786242559</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.263279491166239</v>
+        <v>3.198810494164337</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.629646953009054</v>
+        <v>2.565177956007152</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.273650104128071</v>
+        <v>-3.316281538833723</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.319830487044078</v>
+        <v>1.238308916159916</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.27115269049593</v>
+        <v>3.206683693494029</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.790204724030264</v>
+        <v>2.725735727028363</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.245236841028187</v>
+        <v>-3.287868275733839</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.491753563305242</v>
+        <v>1.41023199242108</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.396325123869284</v>
+        <v>3.331856126867383</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.910317633248082</v>
+        <v>2.84584863624618</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.170454580003175</v>
+        <v>-3.213086014708827</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.641779376933064</v>
+        <v>1.560257806048902</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.561307389702109</v>
+        <v>3.496838392700208</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.902025609261941</v>
+        <v>2.837556612260039</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.144370495739367</v>
+        <v>-3.187001930445019</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.643920986652446</v>
+        <v>1.562399415768285</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.553015365715968</v>
+        <v>3.488546368714067</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.90021880484572</v>
+        <v>2.835749807843819</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.056492582630246</v>
+        <v>-3.099124017335898</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.677265347479874</v>
+        <v>1.595743776595712</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.620763946753758</v>
+        <v>3.556294949751857</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.917773210572511</v>
+        <v>2.85330421357061</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.047600121236963</v>
+        <v>-3.090231555942615</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.698376737763979</v>
+        <v>1.616855166879817</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.638318352480549</v>
+        <v>3.573849355478648</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.909628257977095</v>
+        <v>2.845159260975194</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.216076238206841</v>
+        <v>-3.258707672912493</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.622841338380612</v>
+        <v>1.54131976749645</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.613404698455185</v>
+        <v>3.548935701453284</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.890897955164957</v>
+        <v>2.826428958163056</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.769820045577401</v>
+        <v>-2.812451480283053</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.78261351262025</v>
+        <v>1.701091941736088</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.537843193841267</v>
+        <v>3.473374196839366</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.881561977661862</v>
+        <v>2.81709298065996</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.747098941894248</v>
+        <v>-2.7897303765999</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.782365976590415</v>
+        <v>1.700844405706253</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.528507216338172</v>
+        <v>3.46403821933627</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.040468103513031</v>
+        <v>2.97599910651113</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.876300755188291</v>
+        <v>-2.918932189893943</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.889591377123967</v>
+        <v>1.808069806239805</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.609892254212915</v>
+        <v>3.545423257211014</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.077545926006677</v>
+        <v>3.013076929004776</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.902175153662316</v>
+        <v>-2.944806588367968</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.916319440228003</v>
+        <v>1.834797869343842</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.673917041933606</v>
+        <v>3.609448044931705</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.074221281996222</v>
+        <v>3.009752284994321</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.895120463447143</v>
+        <v>-2.937751898152795</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.915816672303618</v>
+        <v>1.834295101419456</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.674825212052256</v>
+        <v>3.610356215050355</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.084227435640964</v>
+        <v>3.019758438639063</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.868169239120655</v>
+        <v>-2.910800673826307</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.936603315678955</v>
+        <v>1.855081744794793</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.693759573313629</v>
+        <v>3.629290576311728</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.268330567785924</v>
+        <v>3.203861570784023</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.004122247176971</v>
+        <v>-3.046753681882623</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.066325244601388</v>
+        <v>1.984803673717226</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.877862705458589</v>
+        <v>3.813393708456688</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.260447262688917</v>
+        <v>3.195978265687016</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.026530364981843</v>
+        <v>-3.069161799687495</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.049478692382432</v>
+        <v>1.96795712149827</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.869979400361582</v>
+        <v>3.805510403359681</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.262501262238554</v>
+        <v>3.198032265236653</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.054754600559443</v>
+        <v>-3.097386035265095</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.040242997701029</v>
+        <v>1.958721426816868</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.882819451382004</v>
+        <v>3.818350454380103</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.318754979960401</v>
+        <v>3.2542859829585</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.064195526447973</v>
+        <v>-3.106826961153625</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.092720345067465</v>
+        <v>2.011198774183303</v>
       </c>
       <c r="F2006" t="n">
         <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.012529439629887</v>
+        <v>3.948060442627986</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.321646074505702</v>
+        <v>3.257177077503801</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.116469133783615</v>
+        <v>-3.159100568489267</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.074701996678509</v>
+        <v>1.993180425794347</v>
       </c>
       <c r="F2007" t="n">
         <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.984056369773803</v>
+        <v>3.919587372771901</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.319757887399478</v>
+        <v>3.255288890397576</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.192799111384521</v>
+        <v>-3.235430546090173</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.042281818531922</v>
+        <v>1.96076024764776</v>
       </c>
       <c r="F2008" t="n">
         <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.982168182667578</v>
+        <v>3.917699185665676</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.31457811700234</v>
+        <v>3.250109120000439</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.395052831708874</v>
+        <v>-3.437684266414526</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.956200560005043</v>
+        <v>1.874678989120881</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9017634384558131</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.855636180075828</v>
+        <v>3.791167183073927</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.313012127212492</v>
+        <v>3.248543130210591</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.556621257236129</v>
+        <v>-3.599252691941781</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.890007200004293</v>
+        <v>1.808485629120131</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7749805146579337</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.778000436007253</v>
+        <v>3.713531439005351</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.326085534078411</v>
+        <v>3.26161653707651</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.664921919106249</v>
+        <v>-3.707553353811901</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.859760342122164</v>
+        <v>1.778238771238002</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7749805146579337</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.791073842873171</v>
+        <v>3.72660484587127</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.318090730861351</v>
+        <v>3.25362173385945</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.758069390409615</v>
+        <v>-3.800700825115267</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.814506550383757</v>
+        <v>1.732984979499595</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6521513033754009</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.709381512886591</v>
+        <v>3.64491251588469</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.316614771988353</v>
+        <v>3.252145774986452</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.785970177519088</v>
+        <v>-3.82860161222474</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.80187027666697</v>
+        <v>1.720348705782808</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6175543792324661</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.687147399527833</v>
+        <v>3.622678402525931</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.313379215965552</v>
+        <v>3.24891021896365</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.908496280221982</v>
+        <v>-3.951127714927634</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.749624279563011</v>
+        <v>1.668102708678849</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4950282765295723</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.610396181883295</v>
+        <v>3.545927184881394</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.380085175556055</v>
+        <v>3.315616178554154</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.139010776407571</v>
+        <v>-4.181642211113223</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.72412444067928</v>
+        <v>1.642602869795118</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2645137803439835</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.538793443762446</v>
+        <v>3.474324446760544</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814661</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.520396894557902</v>
+        <v>3.455927897556001</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.487755861632015</v>
+        <v>-4.530387296337667</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.724938125591349</v>
+        <v>1.643416554707187</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.613856390412954</v>
+        <v>3.549387393411053</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.589377163703542</v>
+        <v>3.524908166701641</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.641742279408155</v>
+        <v>-4.684373714113807</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.732323827626533</v>
+        <v>1.650802256742371</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.682836659558594</v>
+        <v>3.618367662556693</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.575428365823663</v>
+        <v>3.510959368821762</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.591220375580489</v>
+        <v>-4.633851810286141</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.73858379127772</v>
+        <v>1.657062220393558</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.668887861678715</v>
+        <v>3.604418864676814</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.587298854879077</v>
+        <v>3.522829857877176</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.843695529588214</v>
+        <v>-4.886326964293866</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.649464218730044</v>
+        <v>1.567942647845882</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.680758350734129</v>
+        <v>3.616289353732228</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.588509389398021</v>
+        <v>3.524040392396119</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.136591286067626</v>
+        <v>-5.179222720773278</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.533516450657223</v>
+        <v>1.451994879773061</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1557658264250857</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.681968885253073</v>
+        <v>3.617499888251171</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.592631131625342</v>
+        <v>3.528162134623441</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.323255414202434</v>
+        <v>-5.365886848908086</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.462972541630621</v>
+        <v>1.381450970746459</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1290268556005258</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.670047244985658</v>
+        <v>3.605578247983757</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.587708984361532</v>
+        <v>3.52323998735963</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.469276101116396</v>
+        <v>-5.511907535822048</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.399642119601226</v>
+        <v>1.318120548717064</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1199437638066689</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.659675242645533</v>
+        <v>3.595206245643632</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.749913041060576</v>
+        <v>3.685444044058674</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.560990110225982</v>
+        <v>-5.603621544931633</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.525160572656436</v>
+        <v>1.443639001772274</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1199437638066689</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.821879299344577</v>
+        <v>3.757410302342676</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.74475967902439</v>
+        <v>3.680290682022489</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.592641769285951</v>
+        <v>-5.641916081773341</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.507346546996262</v>
+        <v>1.423167824999405</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1147753065622287</v>
+        <v>0.1134506693155414</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.813624862961727</v>
+        <v>3.748361083611814</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.754989096592881</v>
+        <v>3.69052009959098</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.674576587554834</v>
+        <v>-5.723850900042224</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.4848020372572</v>
+        <v>1.400623315260343</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1048405609751485</v>
+        <v>0.1035159237284612</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.81789343317797</v>
+        <v>3.752629653828057</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.763914735048783</v>
+        <v>3.699445738046882</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.776552709803242</v>
+        <v>-5.825827022290632</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.452937226813739</v>
+        <v>1.368758504816882</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.002864438726740914</v>
+        <v>0.001539801480053615</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.765633398284828</v>
+        <v>3.700369618934915</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.756067622292959</v>
+        <v>3.691598625291058</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.66654642632602</v>
+        <v>-5.71582073881341</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.489092627448803</v>
+        <v>1.404913905451946</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.02606901064401612</v>
+        <v>0.02474437339732882</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.771709028679369</v>
+        <v>3.706445249329455</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.760317633014933</v>
+        <v>3.695848636013032</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.523486850585094</v>
+        <v>-5.572761163072485</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.550566468467148</v>
+        <v>1.466387746470291</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.0340824372339954</v>
+        <v>0.0327577999873081</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.780767095355331</v>
+        <v>3.715503316005417</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.767578515897469</v>
+        <v>3.703109518895568</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.222040125113256</v>
+        <v>-5.271314437600648</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.678406041538419</v>
+        <v>1.594227319541562</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.3342045254591454</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.968896013520969</v>
+        <v>3.903632234171055</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.76854969365018</v>
+        <v>3.704080696648278</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.24663036934844</v>
+        <v>-5.295904681835832</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.669541121597056</v>
+        <v>1.585362399600199</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.3342045254591454</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.969867191273679</v>
+        <v>3.904603411923766</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.769392598029935</v>
+        <v>3.704923601028034</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.19559199334192</v>
+        <v>-5.244866305829311</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.69079937637942</v>
+        <v>1.606620654382562</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3355291627058327</v>
+        <v>0.3342045254591454</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.970710095653435</v>
+        <v>3.905446316303522</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.788430696904081</v>
+        <v>3.723961699902179</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.154452698475289</v>
+        <v>-5.20372701096268</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.726293193200218</v>
+        <v>1.64211447120336</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3766684575724635</v>
+        <v>0.3753438203257762</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.014431771447559</v>
+        <v>3.949167992097645</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.604614693028015</v>
+        <v>3.540145696026114</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.057817786456649</v>
+        <v>-5.10709209894404</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.581131154131608</v>
+        <v>1.49695243213475</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4733033695911034</v>
+        <v>0.4719787323444161</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.888596714782678</v>
+        <v>3.823332935432764</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.608116737101979</v>
+        <v>3.543647740100078</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.98054850538735</v>
+        <v>-5.237672833474883</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.615540910633292</v>
+        <v>1.448222182396378</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.550572650660402</v>
+        <v>0.3413979978135736</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.938460327498221</v>
+        <v>3.748486538788223</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.592543556178062</v>
+        <v>3.528074559176161</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.816052171196389</v>
+        <v>-5.073176499283921</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.665766263385759</v>
+        <v>1.498447535148845</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7150689848513638</v>
+        <v>0.5058943320045355</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.02158494708888</v>
+        <v>3.831611158378882</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.591731266614492</v>
+        <v>3.52726226961259</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.843422103880821</v>
+        <v>-5.100546431968353</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.654006000748416</v>
+        <v>1.486687272511502</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7150689848513638</v>
+        <v>0.5058943320045355</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.02077265752531</v>
+        <v>3.830798868815312</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.601600045739564</v>
+        <v>3.537131048737663</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.85380729877071</v>
+        <v>-5.110931626858243</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.659720701917533</v>
+        <v>1.492401973680618</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7046837899614745</v>
+        <v>0.4955091371146462</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.024410319716449</v>
+        <v>3.834436531006451</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.672437051515989</v>
+        <v>3.607968054514088</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.872395457492935</v>
+        <v>-5.129519785580468</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.723122444205068</v>
+        <v>1.555803715968154</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6860956312392492</v>
+        <v>0.4769209783924208</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.084094430259539</v>
+        <v>3.894120641549541</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496549</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.669306062334288</v>
+        <v>3.604837065332386</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.872694004188971</v>
+        <v>-5.129818332276503</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.719872036344952</v>
+        <v>1.552553308108038</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6857970845432133</v>
+        <v>0.4766224316963849</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.080784313060215</v>
+        <v>3.890810524350218</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.673836957273679</v>
+        <v>3.609367960271778</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.771870870498543</v>
+        <v>-5.028995198586076</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.764732184760514</v>
+        <v>1.5974134565236</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6982613000275671</v>
+        <v>0.4890866471807387</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.092793737290219</v>
+        <v>3.902819948580222</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.673966210752222</v>
+        <v>3.609497213750321</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.581089509746135</v>
+        <v>-4.838213837833669</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.841173982540021</v>
+        <v>1.673855254303106</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8890426607799745</v>
+        <v>0.6798680079331461</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.207391807220207</v>
+        <v>4.01741801851021</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.653803056489819</v>
+        <v>3.589334059487918</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.562572655704315</v>
+        <v>-4.819696983791848</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.828417569894346</v>
+        <v>1.661098841657431</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9019727902051827</v>
+        <v>0.6927981373583543</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.194986730612928</v>
+        <v>4.005012941902931</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591298</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.688769993101877</v>
+        <v>3.624300996099976</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.507242067802553</v>
+        <v>-4.764366395890086</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.885516741667109</v>
+        <v>1.718198013430194</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9573033781069449</v>
+        <v>0.7481287252601164</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.263152019966045</v>
+        <v>4.073178231256046</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539889</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.682456561003315</v>
+        <v>3.617987564001414</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.49518794088959</v>
+        <v>-4.752312268977123</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.884024960333732</v>
+        <v>1.716706232096817</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9693575050199077</v>
+        <v>0.7601828521730792</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.26407106401526</v>
+        <v>4.074097275305261</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.684337191187451</v>
+        <v>3.61986819418555</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.536343060457811</v>
+        <v>-4.793467388545344</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.869443542690579</v>
+        <v>1.702124814453665</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9282023854516868</v>
+        <v>0.7190277326048583</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.241258622458464</v>
+        <v>4.051284833748465</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382914</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.697188217065333</v>
+        <v>3.632719220063432</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.433462470929218</v>
+        <v>-4.690586799016751</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.923446804379899</v>
+        <v>1.756128076142984</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.03108297498028</v>
+        <v>0.8219083221334512</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.315838002053502</v>
+        <v>4.125864213343503</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64685760776031</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.717390887238928</v>
+        <v>3.652921890237026</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.665062864098719</v>
+        <v>-4.922187192186252</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.851009317285693</v>
+        <v>1.683690589048778</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.03108297498028</v>
+        <v>0.8219083221334512</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.336040672227096</v>
+        <v>4.146066883517097</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.717390887238928</v>
+        <v>3.652921890237026</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.68313537239033</v>
+        <v>-4.940259700477863</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.843780313969048</v>
+        <v>1.676461585732134</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.03108297498028</v>
+        <v>0.8219083221334512</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.336040672227096</v>
+        <v>4.146066883517097</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.677642800832394</v>
+        <v>3.613173803830493</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.858242204966775</v>
+        <v>-5.115366533054308</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.733989494531937</v>
+        <v>1.566670766295022</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.03108297498028</v>
+        <v>0.8219083221334512</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.296292585820562</v>
+        <v>4.106318797110564</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943582</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.684665419829334</v>
+        <v>3.620196422827433</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.82695618442632</v>
+        <v>-5.084080512513853</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.753526521745059</v>
+        <v>1.586207793508144</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.062368995520735</v>
+        <v>0.8531943426739066</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.322086817141775</v>
+        <v>4.132113028431777</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677819</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.783836419402239</v>
+        <v>3.719367422400337</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.673930792313035</v>
+        <v>-4.931055120400568</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.913907678163278</v>
+        <v>1.746588949926363</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.215394387634019</v>
+        <v>1.006219734787191</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.513073051982651</v>
+        <v>4.323099263272653</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.971302644310531</v>
+        <v>3.90683364730863</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.702238106186305</v>
+        <v>-4.959362434273839</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.090050977522261</v>
+        <v>1.922732249285347</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.215394387634019</v>
+        <v>1.006219734787191</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.700539276890942</v>
+        <v>4.510565488180945</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.940705595664613</v>
+        <v>3.876236598662713</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.868831331299828</v>
+        <v>-5.125955659387361</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.992816638830935</v>
+        <v>1.825497910594021</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.048801162520496</v>
+        <v>0.8396265096736684</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.569986293176911</v>
+        <v>4.380012504466914</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.944381998326331</v>
+        <v>3.879913001324431</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.695766951917528</v>
+        <v>-4.952891280005061</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.065718793245573</v>
+        <v>1.898400065008659</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.048801162520496</v>
+        <v>0.8396265096736684</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.573662695838629</v>
+        <v>4.383688907128632</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.942000053449826</v>
+        <v>3.877531056447926</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.666520971461831</v>
+        <v>-4.923645299549364</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.075035240551347</v>
+        <v>1.907716512314433</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.048801162520496</v>
+        <v>0.8396265096736684</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.571280750962124</v>
+        <v>4.381306962252127</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.939293292607461</v>
+        <v>3.874824295605561</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.773446519339682</v>
+        <v>-5.030570847427215</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.029558260557841</v>
+        <v>1.862239532320927</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9418756146426451</v>
+        <v>0.732700961795817</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.504418661393048</v>
+        <v>4.314444872683051</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.940722094750695</v>
+        <v>3.876253097748795</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.918465077846931</v>
+        <v>-5.175589405934464</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.972979639298176</v>
+        <v>1.805660911061262</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7968570561353966</v>
+        <v>0.5876824032885685</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.418836328431934</v>
+        <v>4.228862539721936</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.040653334008448</v>
+        <v>3.976184337006548</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.036806843631648</v>
+        <v>-5.293931171719182</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.025574172242042</v>
+        <v>1.858255444005128</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8075430946982867</v>
+        <v>0.5983684418514585</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.52517919082742</v>
+        <v>4.335205402117423</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073534</v>
+        <v>3.714899237073536</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.038439031134387</v>
+        <v>3.973970034132487</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.088217265952356</v>
+        <v>-5.314701131943193</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.002795700439697</v>
+        <v>1.847733157041462</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8075430946982867</v>
+        <v>0.5983684418514585</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.522964887953359</v>
+        <v>4.332991099243362</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.038342159208677</v>
+        <v>3.973873162206776</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.167636717160108</v>
+        <v>-5.394120583150944</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.970931048030886</v>
+        <v>1.815868504632651</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8075430946982867</v>
+        <v>0.5983684418514585</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.522868016027648</v>
+        <v>4.332894227317651</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.03833605276672</v>
+        <v>3.97386705576482</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.263099715077326</v>
+        <v>-5.489583581068162</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.932739742422042</v>
+        <v>1.777677199023807</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8075430946982867</v>
+        <v>0.5983684418514585</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.522861909585692</v>
+        <v>4.332888120875695</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.036432449329331</v>
+        <v>3.97196345232743</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.303119713121109</v>
+        <v>-5.529603579111946</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.91482813976714</v>
+        <v>1.759765596368905</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7675230966545028</v>
+        <v>0.5583484438076747</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.496946307322032</v>
+        <v>4.306972518612035</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.042166267077057</v>
+        <v>3.977697270075157</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.358488875253303</v>
+        <v>-5.584972741244139</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.898414292661989</v>
+        <v>1.743351749263754</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7675230966545028</v>
+        <v>0.5583484438076747</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.502680125069759</v>
+        <v>4.312706336359762</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.041704630419989</v>
+        <v>3.97723563341809</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.40392665508413</v>
+        <v>-5.630410521074967</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.87977754407259</v>
+        <v>1.724715000674356</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7246781059763432</v>
+        <v>0.5155034531295151</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.476511494005796</v>
+        <v>4.2865377052958</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.061579023270308</v>
+        <v>3.997110026268409</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.320701198236466</v>
+        <v>-5.547185064227302</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.932942119661975</v>
+        <v>1.777879576263741</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7246781059763432</v>
+        <v>0.5155034531295151</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.496385886856115</v>
+        <v>4.306412098146119</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299172</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.045279723795036</v>
+        <v>3.980810726793137</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.144410973631159</v>
+        <v>-5.370894839621995</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.987158910028826</v>
+        <v>1.832096366630592</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7246781059763432</v>
+        <v>0.5155034531295151</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.480086587380843</v>
+        <v>4.290112798670846</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.047710673259082</v>
+        <v>3.983241676257182</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.961199310498063</v>
+        <v>-5.1876831764889</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.062874524746109</v>
+        <v>1.907811981347875</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7246781059763432</v>
+        <v>0.5155034531295151</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.482517536844888</v>
+        <v>4.292543748134891</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.013501859106971</v>
+        <v>3.949032862105072</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.889477863484212</v>
+        <v>-5.115961729475049</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.057354289399539</v>
+        <v>1.902291746001305</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7963995529901938</v>
+        <v>0.5872249001433657</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.491341590901087</v>
+        <v>4.301367802191091</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.960417605028143</v>
+        <v>3.895948608026243</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.01885664612399</v>
+        <v>-5.245340512114827</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.952518522264799</v>
+        <v>1.797455978866565</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7542977802829904</v>
+        <v>0.5451231274361623</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.412996273197937</v>
+        <v>4.223022484487941</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71562763173946</v>
+        <v>3.715627631739463</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.145615809913498</v>
+        <v>4.081146812911599</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.051872942034735</v>
+        <v>-5.278356808025571</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.124510208785857</v>
+        <v>1.969447665387623</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6848604036162389</v>
+        <v>0.4756857507694107</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.556532052083242</v>
+        <v>4.366558263373245</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.834375656590533</v>
+        <v>3.814260545460563</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.47995353794344</v>
+        <v>4.073068038739848</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.064411020296672</v>
+        <v>-5.26580372727559</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.453832705511024</v>
+        <v>1.966390123515865</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7313099497988336</v>
+        <v>0.5369843602324937</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.918739507822741</v>
+        <v>4.395258654879345</v>
       </c>
     </row>
   </sheetData>
